--- a/Desarrollo/Sistema de Control de Peso SISCOP/Analisis/SISCOP-CP.xlsx
+++ b/Desarrollo/Sistema de Control de Peso SISCOP/Analisis/SISCOP-CP.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="179">
   <si>
     <t>CRONOGRAMA DEL PROYECTO</t>
   </si>
@@ -525,13 +525,13 @@
     <t>Hito 4: Pruebas</t>
   </si>
   <si>
-    <t>Recopilar documentación final del proyecto</t>
+    <t>Desplegar el sistema en entornos cloud</t>
   </si>
   <si>
-    <t>Documento recopilatorio final</t>
+    <t>Manual de despliegue</t>
   </si>
   <si>
-    <t>SISCOP-DRF.docx</t>
+    <t>SISCOP-MDD.docx</t>
   </si>
   <si>
     <t>Elaborar material de presentación</t>
@@ -540,13 +540,19 @@
     <t>Presentación del proyecto</t>
   </si>
   <si>
-    <t>SISCOP-PPT.pptx</t>
+    <t>SISCOP-PPT.pdf</t>
   </si>
   <si>
-    <t>Presentar proyecto final</t>
+    <t>Consolidar el cierre del proyecto</t>
   </si>
   <si>
-    <t>Hito 5: Cierre y entrega final</t>
+    <t>Acta de cierre</t>
+  </si>
+  <si>
+    <t>SISCOP-ACI.docx</t>
+  </si>
+  <si>
+    <t>Hito 5: Despligue y cierre</t>
   </si>
 </sst>
 </file>
@@ -722,7 +728,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -835,8 +841,7 @@
     <xf borderId="2" fillId="3" fontId="1" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="6" fillId="3" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -3502,7 +3507,7 @@
         <v>171</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F63" s="18">
         <v>46188.0</v>
@@ -3511,7 +3516,7 @@
         <v>46189.0</v>
       </c>
       <c r="H63" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I63" s="3"/>
       <c r="J63" s="3"/>
@@ -3547,13 +3552,13 @@
         <v>83</v>
       </c>
       <c r="F64" s="18">
-        <v>46188.0</v>
+        <v>46189.0</v>
       </c>
       <c r="G64" s="18">
-        <v>46189.0</v>
+        <v>46190.0</v>
       </c>
       <c r="H64" s="25">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I64" s="3"/>
       <c r="J64" s="3"/>
@@ -3576,22 +3581,26 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="21" t="s">
+      <c r="B65" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="C65" s="21"/>
-      <c r="D65" s="42"/>
-      <c r="E65" s="43" t="s">
-        <v>83</v>
-      </c>
-      <c r="F65" s="22">
+      <c r="C65" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="D65" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="F65" s="38">
         <v>46190.0</v>
       </c>
-      <c r="G65" s="22">
+      <c r="G65" s="38">
         <v>46190.0</v>
       </c>
-      <c r="H65" s="23">
-        <v>0.0</v>
+      <c r="H65" s="41">
+        <v>1.0</v>
       </c>
       <c r="I65" s="3"/>
       <c r="J65" s="3"/>
@@ -3615,7 +3624,7 @@
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
       <c r="B66" s="27" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C66" s="28">
         <v>46190.0</v>
@@ -3648,7 +3657,7 @@
       <c r="A67" s="1"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
-      <c r="D67" s="44"/>
+      <c r="D67" s="43"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
@@ -3673,10 +3682,10 @@
       <c r="Z67" s="3"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="45"/>
+      <c r="A68" s="44"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
-      <c r="D68" s="46"/>
+      <c r="D68" s="45"/>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
@@ -3704,7 +3713,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
-      <c r="D69" s="46"/>
+      <c r="D69" s="45"/>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
@@ -3732,7 +3741,7 @@
       <c r="A70" s="1"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
-      <c r="D70" s="46"/>
+      <c r="D70" s="45"/>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
       <c r="G70" s="3"/>
@@ -3760,7 +3769,7 @@
       <c r="A71" s="1"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
-      <c r="D71" s="46"/>
+      <c r="D71" s="45"/>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="3"/>
@@ -3788,7 +3797,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
-      <c r="D72" s="46"/>
+      <c r="D72" s="45"/>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="3"/>
@@ -3818,7 +3827,7 @@
       </c>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
-      <c r="D73" s="46"/>
+      <c r="D73" s="45"/>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
       <c r="G73" s="3"/>
@@ -3846,7 +3855,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="46"/>
+      <c r="D74" s="45"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
       <c r="G74" s="3"/>
@@ -3874,7 +3883,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
-      <c r="D75" s="46"/>
+      <c r="D75" s="45"/>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="3"/>
@@ -3902,7 +3911,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
-      <c r="D76" s="46"/>
+      <c r="D76" s="45"/>
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="3"/>
@@ -3930,7 +3939,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
-      <c r="D77" s="46"/>
+      <c r="D77" s="45"/>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
       <c r="G77" s="3"/>
@@ -3958,7 +3967,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
-      <c r="D78" s="46"/>
+      <c r="D78" s="45"/>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
       <c r="G78" s="3"/>
@@ -3986,7 +3995,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
-      <c r="D79" s="46"/>
+      <c r="D79" s="45"/>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="3"/>
@@ -4014,7 +4023,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
-      <c r="D80" s="46"/>
+      <c r="D80" s="45"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -4042,7 +4051,7 @@
       <c r="A81" s="1"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
-      <c r="D81" s="46"/>
+      <c r="D81" s="45"/>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
       <c r="G81" s="3"/>
@@ -4070,7 +4079,7 @@
       <c r="A82" s="1"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
-      <c r="D82" s="46"/>
+      <c r="D82" s="45"/>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
       <c r="G82" s="3"/>
@@ -4098,7 +4107,7 @@
       <c r="A83" s="1"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
-      <c r="D83" s="46"/>
+      <c r="D83" s="45"/>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="3"/>
@@ -4126,7 +4135,7 @@
       <c r="A84" s="1"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
-      <c r="D84" s="46"/>
+      <c r="D84" s="45"/>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="3"/>
@@ -4154,7 +4163,7 @@
       <c r="A85" s="1"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
-      <c r="D85" s="46"/>
+      <c r="D85" s="45"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
@@ -4182,7 +4191,7 @@
       <c r="A86" s="1"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
-      <c r="D86" s="46"/>
+      <c r="D86" s="45"/>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
@@ -4210,7 +4219,7 @@
       <c r="A87" s="1"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
-      <c r="D87" s="46"/>
+      <c r="D87" s="45"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -4238,7 +4247,7 @@
       <c r="A88" s="1"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
-      <c r="D88" s="46"/>
+      <c r="D88" s="45"/>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
@@ -4266,7 +4275,7 @@
       <c r="A89" s="1"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
-      <c r="D89" s="46"/>
+      <c r="D89" s="45"/>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
       <c r="G89" s="3"/>
@@ -4294,7 +4303,7 @@
       <c r="A90" s="1"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
-      <c r="D90" s="46"/>
+      <c r="D90" s="45"/>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
       <c r="G90" s="3"/>
@@ -4322,7 +4331,7 @@
       <c r="A91" s="1"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="46"/>
+      <c r="D91" s="45"/>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="3"/>
@@ -4350,7 +4359,7 @@
       <c r="A92" s="1"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
-      <c r="D92" s="46"/>
+      <c r="D92" s="45"/>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="3"/>
@@ -4378,7 +4387,7 @@
       <c r="A93" s="1"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
-      <c r="D93" s="46"/>
+      <c r="D93" s="45"/>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
       <c r="G93" s="3"/>
@@ -4406,7 +4415,7 @@
       <c r="A94" s="1"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
-      <c r="D94" s="46"/>
+      <c r="D94" s="45"/>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -4434,7 +4443,7 @@
       <c r="A95" s="1"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
-      <c r="D95" s="46"/>
+      <c r="D95" s="45"/>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -4462,7 +4471,7 @@
       <c r="A96" s="1"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
-      <c r="D96" s="46"/>
+      <c r="D96" s="45"/>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -4490,7 +4499,7 @@
       <c r="A97" s="1"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
-      <c r="D97" s="46"/>
+      <c r="D97" s="45"/>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -4518,7 +4527,7 @@
       <c r="A98" s="1"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
-      <c r="D98" s="46"/>
+      <c r="D98" s="45"/>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -4546,7 +4555,7 @@
       <c r="A99" s="1"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
-      <c r="D99" s="46"/>
+      <c r="D99" s="45"/>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -4574,7 +4583,7 @@
       <c r="A100" s="1"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
-      <c r="D100" s="46"/>
+      <c r="D100" s="45"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -4602,7 +4611,7 @@
       <c r="A101" s="1"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
-      <c r="D101" s="46"/>
+      <c r="D101" s="45"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -4630,7 +4639,7 @@
       <c r="A102" s="1"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
-      <c r="D102" s="46"/>
+      <c r="D102" s="45"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -4658,7 +4667,7 @@
       <c r="A103" s="1"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
-      <c r="D103" s="46"/>
+      <c r="D103" s="45"/>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
@@ -4686,7 +4695,7 @@
       <c r="A104" s="1"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
-      <c r="D104" s="46"/>
+      <c r="D104" s="45"/>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -4714,7 +4723,7 @@
       <c r="A105" s="1"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
-      <c r="D105" s="46"/>
+      <c r="D105" s="45"/>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
@@ -4742,7 +4751,7 @@
       <c r="A106" s="1"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
-      <c r="D106" s="46"/>
+      <c r="D106" s="45"/>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
       <c r="G106" s="3"/>
@@ -4770,7 +4779,7 @@
       <c r="A107" s="1"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
-      <c r="D107" s="46"/>
+      <c r="D107" s="45"/>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="3"/>
@@ -4798,7 +4807,7 @@
       <c r="A108" s="1"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="46"/>
+      <c r="D108" s="45"/>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="3"/>
@@ -4826,7 +4835,7 @@
       <c r="A109" s="1"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
-      <c r="D109" s="46"/>
+      <c r="D109" s="45"/>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
       <c r="G109" s="3"/>
@@ -4854,7 +4863,7 @@
       <c r="A110" s="1"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
-      <c r="D110" s="46"/>
+      <c r="D110" s="45"/>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
       <c r="G110" s="3"/>
@@ -4882,7 +4891,7 @@
       <c r="A111" s="1"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
-      <c r="D111" s="46"/>
+      <c r="D111" s="45"/>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="3"/>
@@ -4910,7 +4919,7 @@
       <c r="A112" s="1"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
-      <c r="D112" s="46"/>
+      <c r="D112" s="45"/>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
@@ -4938,7 +4947,7 @@
       <c r="A113" s="1"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="46"/>
+      <c r="D113" s="45"/>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
       <c r="G113" s="3"/>
@@ -4966,7 +4975,7 @@
       <c r="A114" s="1"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
-      <c r="D114" s="46"/>
+      <c r="D114" s="45"/>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
       <c r="G114" s="3"/>
@@ -4994,7 +5003,7 @@
       <c r="A115" s="1"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
-      <c r="D115" s="46"/>
+      <c r="D115" s="45"/>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="3"/>
@@ -5022,7 +5031,7 @@
       <c r="A116" s="1"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
-      <c r="D116" s="46"/>
+      <c r="D116" s="45"/>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="3"/>
@@ -5050,7 +5059,7 @@
       <c r="A117" s="1"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
-      <c r="D117" s="46"/>
+      <c r="D117" s="45"/>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
       <c r="G117" s="3"/>
@@ -5078,7 +5087,7 @@
       <c r="A118" s="1"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="46"/>
+      <c r="D118" s="45"/>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
       <c r="G118" s="3"/>
@@ -5106,7 +5115,7 @@
       <c r="A119" s="1"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
-      <c r="D119" s="46"/>
+      <c r="D119" s="45"/>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="3"/>
@@ -5134,7 +5143,7 @@
       <c r="A120" s="1"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
-      <c r="D120" s="46"/>
+      <c r="D120" s="45"/>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="3"/>
@@ -5162,7 +5171,7 @@
       <c r="A121" s="1"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
-      <c r="D121" s="46"/>
+      <c r="D121" s="45"/>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
       <c r="G121" s="3"/>
@@ -5190,7 +5199,7 @@
       <c r="A122" s="1"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
-      <c r="D122" s="46"/>
+      <c r="D122" s="45"/>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
       <c r="G122" s="3"/>
@@ -5218,7 +5227,7 @@
       <c r="A123" s="1"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="46"/>
+      <c r="D123" s="45"/>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="3"/>
@@ -5246,7 +5255,7 @@
       <c r="A124" s="1"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
-      <c r="D124" s="46"/>
+      <c r="D124" s="45"/>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="3"/>
@@ -5274,7 +5283,7 @@
       <c r="A125" s="1"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
-      <c r="D125" s="46"/>
+      <c r="D125" s="45"/>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
       <c r="G125" s="3"/>
@@ -5302,7 +5311,7 @@
       <c r="A126" s="1"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
-      <c r="D126" s="46"/>
+      <c r="D126" s="45"/>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
       <c r="G126" s="3"/>
@@ -5330,7 +5339,7 @@
       <c r="A127" s="1"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
-      <c r="D127" s="46"/>
+      <c r="D127" s="45"/>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
@@ -5358,7 +5367,7 @@
       <c r="A128" s="1"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="46"/>
+      <c r="D128" s="45"/>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="3"/>
@@ -5386,7 +5395,7 @@
       <c r="A129" s="1"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
-      <c r="D129" s="46"/>
+      <c r="D129" s="45"/>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
       <c r="G129" s="3"/>
@@ -5414,7 +5423,7 @@
       <c r="A130" s="1"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
-      <c r="D130" s="46"/>
+      <c r="D130" s="45"/>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
       <c r="G130" s="3"/>
@@ -5442,7 +5451,7 @@
       <c r="A131" s="1"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
-      <c r="D131" s="46"/>
+      <c r="D131" s="45"/>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="3"/>
@@ -5470,7 +5479,7 @@
       <c r="A132" s="1"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
-      <c r="D132" s="46"/>
+      <c r="D132" s="45"/>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="3"/>
@@ -5498,7 +5507,7 @@
       <c r="A133" s="1"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="46"/>
+      <c r="D133" s="45"/>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
       <c r="G133" s="3"/>
@@ -5526,7 +5535,7 @@
       <c r="A134" s="1"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
-      <c r="D134" s="46"/>
+      <c r="D134" s="45"/>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
       <c r="G134" s="3"/>
@@ -5554,7 +5563,7 @@
       <c r="A135" s="1"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
-      <c r="D135" s="46"/>
+      <c r="D135" s="45"/>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="3"/>
@@ -5582,7 +5591,7 @@
       <c r="A136" s="1"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
-      <c r="D136" s="46"/>
+      <c r="D136" s="45"/>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="3"/>
@@ -5610,7 +5619,7 @@
       <c r="A137" s="1"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
-      <c r="D137" s="46"/>
+      <c r="D137" s="45"/>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
       <c r="G137" s="3"/>
@@ -5638,7 +5647,7 @@
       <c r="A138" s="1"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="46"/>
+      <c r="D138" s="45"/>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
       <c r="G138" s="3"/>
@@ -5666,7 +5675,7 @@
       <c r="A139" s="1"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
-      <c r="D139" s="46"/>
+      <c r="D139" s="45"/>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="3"/>
@@ -5694,7 +5703,7 @@
       <c r="A140" s="1"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="46"/>
+      <c r="D140" s="45"/>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="3"/>
@@ -5722,7 +5731,7 @@
       <c r="A141" s="1"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
-      <c r="D141" s="46"/>
+      <c r="D141" s="45"/>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
       <c r="G141" s="3"/>
@@ -5750,7 +5759,7 @@
       <c r="A142" s="1"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="46"/>
+      <c r="D142" s="45"/>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
       <c r="G142" s="3"/>
@@ -5778,7 +5787,7 @@
       <c r="A143" s="1"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
-      <c r="D143" s="46"/>
+      <c r="D143" s="45"/>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="3"/>
@@ -5806,7 +5815,7 @@
       <c r="A144" s="1"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
-      <c r="D144" s="46"/>
+      <c r="D144" s="45"/>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="3"/>
@@ -5834,7 +5843,7 @@
       <c r="A145" s="1"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
-      <c r="D145" s="46"/>
+      <c r="D145" s="45"/>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
       <c r="G145" s="3"/>
@@ -5862,7 +5871,7 @@
       <c r="A146" s="1"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
-      <c r="D146" s="46"/>
+      <c r="D146" s="45"/>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
       <c r="G146" s="3"/>
@@ -5890,7 +5899,7 @@
       <c r="A147" s="1"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="46"/>
+      <c r="D147" s="45"/>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="3"/>
@@ -5918,7 +5927,7 @@
       <c r="A148" s="1"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
-      <c r="D148" s="46"/>
+      <c r="D148" s="45"/>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="3"/>
@@ -5946,7 +5955,7 @@
       <c r="A149" s="1"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
-      <c r="D149" s="46"/>
+      <c r="D149" s="45"/>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
       <c r="G149" s="3"/>
@@ -5974,7 +5983,7 @@
       <c r="A150" s="1"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
-      <c r="D150" s="46"/>
+      <c r="D150" s="45"/>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
       <c r="G150" s="3"/>
@@ -6002,7 +6011,7 @@
       <c r="A151" s="1"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
-      <c r="D151" s="46"/>
+      <c r="D151" s="45"/>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="3"/>
@@ -6030,7 +6039,7 @@
       <c r="A152" s="1"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
-      <c r="D152" s="46"/>
+      <c r="D152" s="45"/>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="3"/>
@@ -6058,7 +6067,7 @@
       <c r="A153" s="1"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
-      <c r="D153" s="46"/>
+      <c r="D153" s="45"/>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
       <c r="G153" s="3"/>
@@ -6086,7 +6095,7 @@
       <c r="A154" s="1"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
-      <c r="D154" s="46"/>
+      <c r="D154" s="45"/>
       <c r="E154" s="3"/>
       <c r="F154" s="3"/>
       <c r="G154" s="3"/>
@@ -6114,7 +6123,7 @@
       <c r="A155" s="1"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
-      <c r="D155" s="46"/>
+      <c r="D155" s="45"/>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="3"/>
@@ -6142,7 +6151,7 @@
       <c r="A156" s="1"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
-      <c r="D156" s="46"/>
+      <c r="D156" s="45"/>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="3"/>
@@ -6170,7 +6179,7 @@
       <c r="A157" s="1"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
-      <c r="D157" s="46"/>
+      <c r="D157" s="45"/>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
       <c r="G157" s="3"/>
@@ -6198,7 +6207,7 @@
       <c r="A158" s="1"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
-      <c r="D158" s="46"/>
+      <c r="D158" s="45"/>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
       <c r="G158" s="3"/>
@@ -6226,7 +6235,7 @@
       <c r="A159" s="1"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="46"/>
+      <c r="D159" s="45"/>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="3"/>
@@ -6254,7 +6263,7 @@
       <c r="A160" s="1"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="46"/>
+      <c r="D160" s="45"/>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="3"/>
@@ -6282,7 +6291,7 @@
       <c r="A161" s="1"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="46"/>
+      <c r="D161" s="45"/>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
       <c r="G161" s="3"/>
@@ -6310,7 +6319,7 @@
       <c r="A162" s="1"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="46"/>
+      <c r="D162" s="45"/>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
       <c r="G162" s="3"/>
@@ -6338,7 +6347,7 @@
       <c r="A163" s="1"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
-      <c r="D163" s="46"/>
+      <c r="D163" s="45"/>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="3"/>
@@ -6366,7 +6375,7 @@
       <c r="A164" s="1"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="46"/>
+      <c r="D164" s="45"/>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="3"/>
@@ -6394,7 +6403,7 @@
       <c r="A165" s="1"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="46"/>
+      <c r="D165" s="45"/>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
@@ -6422,7 +6431,7 @@
       <c r="A166" s="1"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
-      <c r="D166" s="46"/>
+      <c r="D166" s="45"/>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
@@ -6450,7 +6459,7 @@
       <c r="A167" s="1"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
-      <c r="D167" s="46"/>
+      <c r="D167" s="45"/>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
@@ -6478,7 +6487,7 @@
       <c r="A168" s="1"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
-      <c r="D168" s="46"/>
+      <c r="D168" s="45"/>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -6506,7 +6515,7 @@
       <c r="A169" s="1"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
-      <c r="D169" s="46"/>
+      <c r="D169" s="45"/>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
@@ -6534,7 +6543,7 @@
       <c r="A170" s="1"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
-      <c r="D170" s="46"/>
+      <c r="D170" s="45"/>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
@@ -6562,7 +6571,7 @@
       <c r="A171" s="1"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
-      <c r="D171" s="46"/>
+      <c r="D171" s="45"/>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
@@ -6590,7 +6599,7 @@
       <c r="A172" s="1"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
-      <c r="D172" s="46"/>
+      <c r="D172" s="45"/>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
@@ -6618,7 +6627,7 @@
       <c r="A173" s="1"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
-      <c r="D173" s="46"/>
+      <c r="D173" s="45"/>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
@@ -6646,7 +6655,7 @@
       <c r="A174" s="1"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
-      <c r="D174" s="46"/>
+      <c r="D174" s="45"/>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
@@ -6674,7 +6683,7 @@
       <c r="A175" s="1"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="46"/>
+      <c r="D175" s="45"/>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
@@ -6702,7 +6711,7 @@
       <c r="A176" s="1"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="46"/>
+      <c r="D176" s="45"/>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
@@ -6730,7 +6739,7 @@
       <c r="A177" s="1"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="46"/>
+      <c r="D177" s="45"/>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>
@@ -6758,7 +6767,7 @@
       <c r="A178" s="1"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="46"/>
+      <c r="D178" s="45"/>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
@@ -6786,7 +6795,7 @@
       <c r="A179" s="1"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
-      <c r="D179" s="46"/>
+      <c r="D179" s="45"/>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>
@@ -6814,7 +6823,7 @@
       <c r="A180" s="1"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="46"/>
+      <c r="D180" s="45"/>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
@@ -6842,7 +6851,7 @@
       <c r="A181" s="1"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
-      <c r="D181" s="46"/>
+      <c r="D181" s="45"/>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
@@ -6870,7 +6879,7 @@
       <c r="A182" s="1"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="46"/>
+      <c r="D182" s="45"/>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
@@ -6898,7 +6907,7 @@
       <c r="A183" s="1"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
-      <c r="D183" s="46"/>
+      <c r="D183" s="45"/>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
@@ -6926,7 +6935,7 @@
       <c r="A184" s="1"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
-      <c r="D184" s="46"/>
+      <c r="D184" s="45"/>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
@@ -6954,7 +6963,7 @@
       <c r="A185" s="1"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
-      <c r="D185" s="46"/>
+      <c r="D185" s="45"/>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
@@ -6982,7 +6991,7 @@
       <c r="A186" s="1"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
-      <c r="D186" s="46"/>
+      <c r="D186" s="45"/>
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
       <c r="G186" s="3"/>
@@ -7010,7 +7019,7 @@
       <c r="A187" s="1"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
-      <c r="D187" s="46"/>
+      <c r="D187" s="45"/>
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="3"/>
@@ -7038,7 +7047,7 @@
       <c r="A188" s="1"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
-      <c r="D188" s="46"/>
+      <c r="D188" s="45"/>
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="3"/>
@@ -7066,7 +7075,7 @@
       <c r="A189" s="1"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
-      <c r="D189" s="46"/>
+      <c r="D189" s="45"/>
       <c r="E189" s="3"/>
       <c r="F189" s="3"/>
       <c r="G189" s="3"/>
@@ -7094,7 +7103,7 @@
       <c r="A190" s="1"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
-      <c r="D190" s="46"/>
+      <c r="D190" s="45"/>
       <c r="E190" s="3"/>
       <c r="F190" s="3"/>
       <c r="G190" s="3"/>
@@ -7122,7 +7131,7 @@
       <c r="A191" s="1"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
-      <c r="D191" s="46"/>
+      <c r="D191" s="45"/>
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="3"/>
@@ -7150,7 +7159,7 @@
       <c r="A192" s="1"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
-      <c r="D192" s="46"/>
+      <c r="D192" s="45"/>
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="3"/>
@@ -7178,7 +7187,7 @@
       <c r="A193" s="1"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="46"/>
+      <c r="D193" s="45"/>
       <c r="E193" s="3"/>
       <c r="F193" s="3"/>
       <c r="G193" s="3"/>
@@ -7206,7 +7215,7 @@
       <c r="A194" s="1"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
-      <c r="D194" s="46"/>
+      <c r="D194" s="45"/>
       <c r="E194" s="3"/>
       <c r="F194" s="3"/>
       <c r="G194" s="3"/>
@@ -7234,7 +7243,7 @@
       <c r="A195" s="1"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
-      <c r="D195" s="46"/>
+      <c r="D195" s="45"/>
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="3"/>
@@ -7262,7 +7271,7 @@
       <c r="A196" s="1"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
-      <c r="D196" s="46"/>
+      <c r="D196" s="45"/>
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="3"/>
@@ -7290,7 +7299,7 @@
       <c r="A197" s="1"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
-      <c r="D197" s="46"/>
+      <c r="D197" s="45"/>
       <c r="E197" s="3"/>
       <c r="F197" s="3"/>
       <c r="G197" s="3"/>
@@ -7318,7 +7327,7 @@
       <c r="A198" s="1"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
-      <c r="D198" s="46"/>
+      <c r="D198" s="45"/>
       <c r="E198" s="3"/>
       <c r="F198" s="3"/>
       <c r="G198" s="3"/>
@@ -7346,7 +7355,7 @@
       <c r="A199" s="1"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
-      <c r="D199" s="46"/>
+      <c r="D199" s="45"/>
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="3"/>
@@ -7374,7 +7383,7 @@
       <c r="A200" s="1"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
-      <c r="D200" s="46"/>
+      <c r="D200" s="45"/>
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="3"/>
@@ -7402,7 +7411,7 @@
       <c r="A201" s="1"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
-      <c r="D201" s="46"/>
+      <c r="D201" s="45"/>
       <c r="E201" s="3"/>
       <c r="F201" s="3"/>
       <c r="G201" s="3"/>
@@ -7430,7 +7439,7 @@
       <c r="A202" s="1"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
-      <c r="D202" s="46"/>
+      <c r="D202" s="45"/>
       <c r="E202" s="3"/>
       <c r="F202" s="3"/>
       <c r="G202" s="3"/>
@@ -7458,7 +7467,7 @@
       <c r="A203" s="1"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
-      <c r="D203" s="46"/>
+      <c r="D203" s="45"/>
       <c r="E203" s="3"/>
       <c r="F203" s="3"/>
       <c r="G203" s="3"/>
@@ -7486,7 +7495,7 @@
       <c r="A204" s="1"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
-      <c r="D204" s="46"/>
+      <c r="D204" s="45"/>
       <c r="E204" s="3"/>
       <c r="F204" s="3"/>
       <c r="G204" s="3"/>
@@ -7514,7 +7523,7 @@
       <c r="A205" s="1"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
-      <c r="D205" s="46"/>
+      <c r="D205" s="45"/>
       <c r="E205" s="3"/>
       <c r="F205" s="3"/>
       <c r="G205" s="3"/>
@@ -7542,7 +7551,7 @@
       <c r="A206" s="1"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
-      <c r="D206" s="46"/>
+      <c r="D206" s="45"/>
       <c r="E206" s="3"/>
       <c r="F206" s="3"/>
       <c r="G206" s="3"/>
@@ -7570,7 +7579,7 @@
       <c r="A207" s="1"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
-      <c r="D207" s="46"/>
+      <c r="D207" s="45"/>
       <c r="E207" s="3"/>
       <c r="F207" s="3"/>
       <c r="G207" s="3"/>
@@ -7598,7 +7607,7 @@
       <c r="A208" s="1"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
-      <c r="D208" s="46"/>
+      <c r="D208" s="45"/>
       <c r="E208" s="3"/>
       <c r="F208" s="3"/>
       <c r="G208" s="3"/>
@@ -7626,7 +7635,7 @@
       <c r="A209" s="1"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
-      <c r="D209" s="46"/>
+      <c r="D209" s="45"/>
       <c r="E209" s="3"/>
       <c r="F209" s="3"/>
       <c r="G209" s="3"/>
@@ -7654,7 +7663,7 @@
       <c r="A210" s="1"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="46"/>
+      <c r="D210" s="45"/>
       <c r="E210" s="3"/>
       <c r="F210" s="3"/>
       <c r="G210" s="3"/>
@@ -7682,7 +7691,7 @@
       <c r="A211" s="1"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
-      <c r="D211" s="46"/>
+      <c r="D211" s="45"/>
       <c r="E211" s="3"/>
       <c r="F211" s="3"/>
       <c r="G211" s="3"/>
@@ -7710,7 +7719,7 @@
       <c r="A212" s="1"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
-      <c r="D212" s="46"/>
+      <c r="D212" s="45"/>
       <c r="E212" s="3"/>
       <c r="F212" s="3"/>
       <c r="G212" s="3"/>
@@ -7738,7 +7747,7 @@
       <c r="A213" s="1"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
-      <c r="D213" s="46"/>
+      <c r="D213" s="45"/>
       <c r="E213" s="3"/>
       <c r="F213" s="3"/>
       <c r="G213" s="3"/>
@@ -7766,7 +7775,7 @@
       <c r="A214" s="1"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
-      <c r="D214" s="46"/>
+      <c r="D214" s="45"/>
       <c r="E214" s="3"/>
       <c r="F214" s="3"/>
       <c r="G214" s="3"/>
@@ -7794,7 +7803,7 @@
       <c r="A215" s="1"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="46"/>
+      <c r="D215" s="45"/>
       <c r="E215" s="3"/>
       <c r="F215" s="3"/>
       <c r="G215" s="3"/>
@@ -7822,7 +7831,7 @@
       <c r="A216" s="1"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
-      <c r="D216" s="46"/>
+      <c r="D216" s="45"/>
       <c r="E216" s="3"/>
       <c r="F216" s="3"/>
       <c r="G216" s="3"/>
@@ -7850,7 +7859,7 @@
       <c r="A217" s="1"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
-      <c r="D217" s="46"/>
+      <c r="D217" s="45"/>
       <c r="E217" s="3"/>
       <c r="F217" s="3"/>
       <c r="G217" s="3"/>
@@ -7878,7 +7887,7 @@
       <c r="A218" s="1"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
-      <c r="D218" s="46"/>
+      <c r="D218" s="45"/>
       <c r="E218" s="3"/>
       <c r="F218" s="3"/>
       <c r="G218" s="3"/>
@@ -7906,7 +7915,7 @@
       <c r="A219" s="1"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
-      <c r="D219" s="46"/>
+      <c r="D219" s="45"/>
       <c r="E219" s="3"/>
       <c r="F219" s="3"/>
       <c r="G219" s="3"/>
@@ -7934,7 +7943,7 @@
       <c r="A220" s="1"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
-      <c r="D220" s="46"/>
+      <c r="D220" s="45"/>
       <c r="E220" s="3"/>
       <c r="F220" s="3"/>
       <c r="G220" s="3"/>
@@ -7962,7 +7971,7 @@
       <c r="A221" s="1"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
-      <c r="D221" s="46"/>
+      <c r="D221" s="45"/>
       <c r="E221" s="3"/>
       <c r="F221" s="3"/>
       <c r="G221" s="3"/>
@@ -7990,7 +7999,7 @@
       <c r="A222" s="1"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
-      <c r="D222" s="46"/>
+      <c r="D222" s="45"/>
       <c r="E222" s="3"/>
       <c r="F222" s="3"/>
       <c r="G222" s="3"/>
@@ -8018,7 +8027,7 @@
       <c r="A223" s="1"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
-      <c r="D223" s="46"/>
+      <c r="D223" s="45"/>
       <c r="E223" s="3"/>
       <c r="F223" s="3"/>
       <c r="G223" s="3"/>
@@ -8046,7 +8055,7 @@
       <c r="A224" s="1"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
-      <c r="D224" s="46"/>
+      <c r="D224" s="45"/>
       <c r="E224" s="3"/>
       <c r="F224" s="3"/>
       <c r="G224" s="3"/>
@@ -8074,7 +8083,7 @@
       <c r="A225" s="1"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
-      <c r="D225" s="46"/>
+      <c r="D225" s="45"/>
       <c r="E225" s="3"/>
       <c r="F225" s="3"/>
       <c r="G225" s="3"/>
@@ -8102,7 +8111,7 @@
       <c r="A226" s="1"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
-      <c r="D226" s="46"/>
+      <c r="D226" s="45"/>
       <c r="E226" s="3"/>
       <c r="F226" s="3"/>
       <c r="G226" s="3"/>
@@ -8130,7 +8139,7 @@
       <c r="A227" s="1"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
-      <c r="D227" s="46"/>
+      <c r="D227" s="45"/>
       <c r="E227" s="3"/>
       <c r="F227" s="3"/>
       <c r="G227" s="3"/>
@@ -8158,7 +8167,7 @@
       <c r="A228" s="1"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
-      <c r="D228" s="46"/>
+      <c r="D228" s="45"/>
       <c r="E228" s="3"/>
       <c r="F228" s="3"/>
       <c r="G228" s="3"/>
@@ -8186,7 +8195,7 @@
       <c r="A229" s="1"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
-      <c r="D229" s="46"/>
+      <c r="D229" s="45"/>
       <c r="E229" s="3"/>
       <c r="F229" s="3"/>
       <c r="G229" s="3"/>
@@ -8214,7 +8223,7 @@
       <c r="A230" s="1"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
-      <c r="D230" s="46"/>
+      <c r="D230" s="45"/>
       <c r="E230" s="3"/>
       <c r="F230" s="3"/>
       <c r="G230" s="3"/>
@@ -8242,7 +8251,7 @@
       <c r="A231" s="1"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
-      <c r="D231" s="46"/>
+      <c r="D231" s="45"/>
       <c r="E231" s="3"/>
       <c r="F231" s="3"/>
       <c r="G231" s="3"/>
@@ -8270,7 +8279,7 @@
       <c r="A232" s="1"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
-      <c r="D232" s="46"/>
+      <c r="D232" s="45"/>
       <c r="E232" s="3"/>
       <c r="F232" s="3"/>
       <c r="G232" s="3"/>
@@ -8298,7 +8307,7 @@
       <c r="A233" s="1"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
-      <c r="D233" s="46"/>
+      <c r="D233" s="45"/>
       <c r="E233" s="3"/>
       <c r="F233" s="3"/>
       <c r="G233" s="3"/>
@@ -8326,7 +8335,7 @@
       <c r="A234" s="1"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
-      <c r="D234" s="46"/>
+      <c r="D234" s="45"/>
       <c r="E234" s="3"/>
       <c r="F234" s="3"/>
       <c r="G234" s="3"/>
@@ -8354,7 +8363,7 @@
       <c r="A235" s="1"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
-      <c r="D235" s="46"/>
+      <c r="D235" s="45"/>
       <c r="E235" s="3"/>
       <c r="F235" s="3"/>
       <c r="G235" s="3"/>
@@ -8382,7 +8391,7 @@
       <c r="A236" s="1"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
-      <c r="D236" s="46"/>
+      <c r="D236" s="45"/>
       <c r="E236" s="3"/>
       <c r="F236" s="3"/>
       <c r="G236" s="3"/>
@@ -8410,7 +8419,7 @@
       <c r="A237" s="1"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="46"/>
+      <c r="D237" s="45"/>
       <c r="E237" s="3"/>
       <c r="F237" s="3"/>
       <c r="G237" s="3"/>
@@ -8438,7 +8447,7 @@
       <c r="A238" s="1"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
-      <c r="D238" s="46"/>
+      <c r="D238" s="45"/>
       <c r="E238" s="3"/>
       <c r="F238" s="3"/>
       <c r="G238" s="3"/>
@@ -8466,7 +8475,7 @@
       <c r="A239" s="1"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
-      <c r="D239" s="46"/>
+      <c r="D239" s="45"/>
       <c r="E239" s="3"/>
       <c r="F239" s="3"/>
       <c r="G239" s="3"/>
@@ -8494,7 +8503,7 @@
       <c r="A240" s="1"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
-      <c r="D240" s="46"/>
+      <c r="D240" s="45"/>
       <c r="E240" s="3"/>
       <c r="F240" s="3"/>
       <c r="G240" s="3"/>
@@ -8522,7 +8531,7 @@
       <c r="A241" s="1"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="46"/>
+      <c r="D241" s="45"/>
       <c r="E241" s="3"/>
       <c r="F241" s="3"/>
       <c r="G241" s="3"/>
@@ -8550,7 +8559,7 @@
       <c r="A242" s="1"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="46"/>
+      <c r="D242" s="45"/>
       <c r="E242" s="3"/>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -8578,7 +8587,7 @@
       <c r="A243" s="1"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="46"/>
+      <c r="D243" s="45"/>
       <c r="E243" s="3"/>
       <c r="F243" s="3"/>
       <c r="G243" s="3"/>
@@ -8606,7 +8615,7 @@
       <c r="A244" s="1"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
-      <c r="D244" s="46"/>
+      <c r="D244" s="45"/>
       <c r="E244" s="3"/>
       <c r="F244" s="3"/>
       <c r="G244" s="3"/>
@@ -8634,7 +8643,7 @@
       <c r="A245" s="1"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
-      <c r="D245" s="46"/>
+      <c r="D245" s="45"/>
       <c r="E245" s="3"/>
       <c r="F245" s="3"/>
       <c r="G245" s="3"/>
@@ -8662,7 +8671,7 @@
       <c r="A246" s="1"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="46"/>
+      <c r="D246" s="45"/>
       <c r="E246" s="3"/>
       <c r="F246" s="3"/>
       <c r="G246" s="3"/>
@@ -8690,7 +8699,7 @@
       <c r="A247" s="1"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
-      <c r="D247" s="46"/>
+      <c r="D247" s="45"/>
       <c r="E247" s="3"/>
       <c r="F247" s="3"/>
       <c r="G247" s="3"/>
@@ -8718,7 +8727,7 @@
       <c r="A248" s="1"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
-      <c r="D248" s="46"/>
+      <c r="D248" s="45"/>
       <c r="E248" s="3"/>
       <c r="F248" s="3"/>
       <c r="G248" s="3"/>
@@ -8746,7 +8755,7 @@
       <c r="A249" s="1"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
-      <c r="D249" s="46"/>
+      <c r="D249" s="45"/>
       <c r="E249" s="3"/>
       <c r="F249" s="3"/>
       <c r="G249" s="3"/>
@@ -8774,7 +8783,7 @@
       <c r="A250" s="1"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
-      <c r="D250" s="46"/>
+      <c r="D250" s="45"/>
       <c r="E250" s="3"/>
       <c r="F250" s="3"/>
       <c r="G250" s="3"/>
@@ -8802,7 +8811,7 @@
       <c r="A251" s="1"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
-      <c r="D251" s="46"/>
+      <c r="D251" s="45"/>
       <c r="E251" s="3"/>
       <c r="F251" s="3"/>
       <c r="G251" s="3"/>
@@ -8830,7 +8839,7 @@
       <c r="A252" s="1"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
-      <c r="D252" s="46"/>
+      <c r="D252" s="45"/>
       <c r="E252" s="3"/>
       <c r="F252" s="3"/>
       <c r="G252" s="3"/>
@@ -8858,7 +8867,7 @@
       <c r="A253" s="1"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
-      <c r="D253" s="46"/>
+      <c r="D253" s="45"/>
       <c r="E253" s="3"/>
       <c r="F253" s="3"/>
       <c r="G253" s="3"/>
@@ -8886,7 +8895,7 @@
       <c r="A254" s="1"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
-      <c r="D254" s="46"/>
+      <c r="D254" s="45"/>
       <c r="E254" s="3"/>
       <c r="F254" s="3"/>
       <c r="G254" s="3"/>
@@ -8914,7 +8923,7 @@
       <c r="A255" s="1"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
-      <c r="D255" s="46"/>
+      <c r="D255" s="45"/>
       <c r="E255" s="3"/>
       <c r="F255" s="3"/>
       <c r="G255" s="3"/>
@@ -8942,7 +8951,7 @@
       <c r="A256" s="1"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
-      <c r="D256" s="46"/>
+      <c r="D256" s="45"/>
       <c r="E256" s="3"/>
       <c r="F256" s="3"/>
       <c r="G256" s="3"/>
@@ -8970,7 +8979,7 @@
       <c r="A257" s="1"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
-      <c r="D257" s="46"/>
+      <c r="D257" s="45"/>
       <c r="E257" s="3"/>
       <c r="F257" s="3"/>
       <c r="G257" s="3"/>
@@ -8998,7 +9007,7 @@
       <c r="A258" s="1"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
-      <c r="D258" s="46"/>
+      <c r="D258" s="45"/>
       <c r="E258" s="3"/>
       <c r="F258" s="3"/>
       <c r="G258" s="3"/>
@@ -9026,7 +9035,7 @@
       <c r="A259" s="1"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
-      <c r="D259" s="46"/>
+      <c r="D259" s="45"/>
       <c r="E259" s="3"/>
       <c r="F259" s="3"/>
       <c r="G259" s="3"/>
@@ -9054,7 +9063,7 @@
       <c r="A260" s="1"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
-      <c r="D260" s="46"/>
+      <c r="D260" s="45"/>
       <c r="E260" s="3"/>
       <c r="F260" s="3"/>
       <c r="G260" s="3"/>
@@ -9082,7 +9091,7 @@
       <c r="A261" s="1"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
-      <c r="D261" s="46"/>
+      <c r="D261" s="45"/>
       <c r="E261" s="3"/>
       <c r="F261" s="3"/>
       <c r="G261" s="3"/>
@@ -9110,7 +9119,7 @@
       <c r="A262" s="1"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
-      <c r="D262" s="46"/>
+      <c r="D262" s="45"/>
       <c r="E262" s="3"/>
       <c r="F262" s="3"/>
       <c r="G262" s="3"/>
@@ -9138,7 +9147,7 @@
       <c r="A263" s="1"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
-      <c r="D263" s="46"/>
+      <c r="D263" s="45"/>
       <c r="E263" s="3"/>
       <c r="F263" s="3"/>
       <c r="G263" s="3"/>
@@ -9166,7 +9175,7 @@
       <c r="A264" s="1"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
-      <c r="D264" s="46"/>
+      <c r="D264" s="45"/>
       <c r="E264" s="3"/>
       <c r="F264" s="3"/>
       <c r="G264" s="3"/>
@@ -9194,7 +9203,7 @@
       <c r="A265" s="1"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
-      <c r="D265" s="46"/>
+      <c r="D265" s="45"/>
       <c r="E265" s="3"/>
       <c r="F265" s="3"/>
       <c r="G265" s="3"/>
@@ -9222,7 +9231,7 @@
       <c r="A266" s="1"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
-      <c r="D266" s="46"/>
+      <c r="D266" s="45"/>
       <c r="E266" s="3"/>
       <c r="F266" s="3"/>
       <c r="G266" s="3"/>
@@ -9250,7 +9259,7 @@
       <c r="A267" s="1"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
-      <c r="D267" s="46"/>
+      <c r="D267" s="45"/>
       <c r="E267" s="3"/>
       <c r="F267" s="3"/>
       <c r="G267" s="3"/>
@@ -9278,7 +9287,7 @@
       <c r="A268" s="1"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
-      <c r="D268" s="46"/>
+      <c r="D268" s="45"/>
       <c r="E268" s="3"/>
       <c r="F268" s="3"/>
       <c r="G268" s="3"/>
@@ -9306,7 +9315,7 @@
       <c r="A269" s="1"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
-      <c r="D269" s="46"/>
+      <c r="D269" s="45"/>
       <c r="E269" s="3"/>
       <c r="F269" s="3"/>
       <c r="G269" s="3"/>
@@ -9334,7 +9343,7 @@
       <c r="A270" s="1"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
-      <c r="D270" s="46"/>
+      <c r="D270" s="45"/>
       <c r="E270" s="3"/>
       <c r="F270" s="3"/>
       <c r="G270" s="3"/>
@@ -9362,7 +9371,7 @@
       <c r="A271" s="1"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
-      <c r="D271" s="46"/>
+      <c r="D271" s="45"/>
       <c r="E271" s="3"/>
       <c r="F271" s="3"/>
       <c r="G271" s="3"/>
@@ -9390,7 +9399,7 @@
       <c r="A272" s="1"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
-      <c r="D272" s="46"/>
+      <c r="D272" s="45"/>
       <c r="E272" s="3"/>
       <c r="F272" s="3"/>
       <c r="G272" s="3"/>
@@ -9418,7 +9427,7 @@
       <c r="A273" s="1"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
-      <c r="D273" s="46"/>
+      <c r="D273" s="45"/>
       <c r="E273" s="3"/>
       <c r="F273" s="3"/>
       <c r="G273" s="3"/>
@@ -9446,7 +9455,7 @@
       <c r="A274" s="1"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
-      <c r="D274" s="46"/>
+      <c r="D274" s="45"/>
       <c r="E274" s="3"/>
       <c r="F274" s="3"/>
       <c r="G274" s="3"/>
@@ -9474,7 +9483,7 @@
       <c r="A275" s="1"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
-      <c r="D275" s="46"/>
+      <c r="D275" s="45"/>
       <c r="E275" s="3"/>
       <c r="F275" s="3"/>
       <c r="G275" s="3"/>
@@ -9502,7 +9511,7 @@
       <c r="A276" s="1"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
-      <c r="D276" s="46"/>
+      <c r="D276" s="45"/>
       <c r="E276" s="3"/>
       <c r="F276" s="3"/>
       <c r="G276" s="3"/>
@@ -9530,7 +9539,7 @@
       <c r="A277" s="1"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
-      <c r="D277" s="46"/>
+      <c r="D277" s="45"/>
       <c r="E277" s="3"/>
       <c r="F277" s="3"/>
       <c r="G277" s="3"/>
@@ -9558,7 +9567,7 @@
       <c r="A278" s="1"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
-      <c r="D278" s="46"/>
+      <c r="D278" s="45"/>
       <c r="E278" s="3"/>
       <c r="F278" s="3"/>
       <c r="G278" s="3"/>
@@ -9586,7 +9595,7 @@
       <c r="A279" s="1"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
-      <c r="D279" s="46"/>
+      <c r="D279" s="45"/>
       <c r="E279" s="3"/>
       <c r="F279" s="3"/>
       <c r="G279" s="3"/>
@@ -9614,7 +9623,7 @@
       <c r="A280" s="1"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
-      <c r="D280" s="46"/>
+      <c r="D280" s="45"/>
       <c r="E280" s="3"/>
       <c r="F280" s="3"/>
       <c r="G280" s="3"/>
@@ -9642,7 +9651,7 @@
       <c r="A281" s="1"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
-      <c r="D281" s="46"/>
+      <c r="D281" s="45"/>
       <c r="E281" s="3"/>
       <c r="F281" s="3"/>
       <c r="G281" s="3"/>
@@ -9670,7 +9679,7 @@
       <c r="A282" s="1"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
-      <c r="D282" s="46"/>
+      <c r="D282" s="45"/>
       <c r="E282" s="3"/>
       <c r="F282" s="3"/>
       <c r="G282" s="3"/>
@@ -9698,7 +9707,7 @@
       <c r="A283" s="1"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
-      <c r="D283" s="46"/>
+      <c r="D283" s="45"/>
       <c r="E283" s="3"/>
       <c r="F283" s="3"/>
       <c r="G283" s="3"/>
@@ -9726,7 +9735,7 @@
       <c r="A284" s="1"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
-      <c r="D284" s="46"/>
+      <c r="D284" s="45"/>
       <c r="E284" s="3"/>
       <c r="F284" s="3"/>
       <c r="G284" s="3"/>
@@ -9754,7 +9763,7 @@
       <c r="A285" s="1"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
-      <c r="D285" s="46"/>
+      <c r="D285" s="45"/>
       <c r="E285" s="3"/>
       <c r="F285" s="3"/>
       <c r="G285" s="3"/>
@@ -9782,7 +9791,7 @@
       <c r="A286" s="1"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
-      <c r="D286" s="46"/>
+      <c r="D286" s="45"/>
       <c r="E286" s="3"/>
       <c r="F286" s="3"/>
       <c r="G286" s="3"/>
@@ -9810,7 +9819,7 @@
       <c r="A287" s="1"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
-      <c r="D287" s="46"/>
+      <c r="D287" s="45"/>
       <c r="E287" s="3"/>
       <c r="F287" s="3"/>
       <c r="G287" s="3"/>
@@ -9838,7 +9847,7 @@
       <c r="A288" s="1"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
-      <c r="D288" s="46"/>
+      <c r="D288" s="45"/>
       <c r="E288" s="3"/>
       <c r="F288" s="3"/>
       <c r="G288" s="3"/>
@@ -9866,7 +9875,7 @@
       <c r="A289" s="1"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
-      <c r="D289" s="46"/>
+      <c r="D289" s="45"/>
       <c r="E289" s="3"/>
       <c r="F289" s="3"/>
       <c r="G289" s="3"/>
@@ -9894,7 +9903,7 @@
       <c r="A290" s="1"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
-      <c r="D290" s="46"/>
+      <c r="D290" s="45"/>
       <c r="E290" s="3"/>
       <c r="F290" s="3"/>
       <c r="G290" s="3"/>
@@ -9922,7 +9931,7 @@
       <c r="A291" s="1"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
-      <c r="D291" s="46"/>
+      <c r="D291" s="45"/>
       <c r="E291" s="3"/>
       <c r="F291" s="3"/>
       <c r="G291" s="3"/>
@@ -9950,7 +9959,7 @@
       <c r="A292" s="1"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
-      <c r="D292" s="46"/>
+      <c r="D292" s="45"/>
       <c r="E292" s="3"/>
       <c r="F292" s="3"/>
       <c r="G292" s="3"/>
@@ -9978,7 +9987,7 @@
       <c r="A293" s="1"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
-      <c r="D293" s="46"/>
+      <c r="D293" s="45"/>
       <c r="E293" s="3"/>
       <c r="F293" s="3"/>
       <c r="G293" s="3"/>
@@ -10006,7 +10015,7 @@
       <c r="A294" s="1"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
-      <c r="D294" s="46"/>
+      <c r="D294" s="45"/>
       <c r="E294" s="3"/>
       <c r="F294" s="3"/>
       <c r="G294" s="3"/>
@@ -10034,7 +10043,7 @@
       <c r="A295" s="1"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
-      <c r="D295" s="46"/>
+      <c r="D295" s="45"/>
       <c r="E295" s="3"/>
       <c r="F295" s="3"/>
       <c r="G295" s="3"/>
@@ -10062,7 +10071,7 @@
       <c r="A296" s="1"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
-      <c r="D296" s="46"/>
+      <c r="D296" s="45"/>
       <c r="E296" s="3"/>
       <c r="F296" s="3"/>
       <c r="G296" s="3"/>
@@ -10090,7 +10099,7 @@
       <c r="A297" s="1"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
-      <c r="D297" s="46"/>
+      <c r="D297" s="45"/>
       <c r="E297" s="3"/>
       <c r="F297" s="3"/>
       <c r="G297" s="3"/>
@@ -10118,7 +10127,7 @@
       <c r="A298" s="1"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
-      <c r="D298" s="46"/>
+      <c r="D298" s="45"/>
       <c r="E298" s="3"/>
       <c r="F298" s="3"/>
       <c r="G298" s="3"/>
@@ -10146,7 +10155,7 @@
       <c r="A299" s="1"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
-      <c r="D299" s="46"/>
+      <c r="D299" s="45"/>
       <c r="E299" s="3"/>
       <c r="F299" s="3"/>
       <c r="G299" s="3"/>
@@ -10174,7 +10183,7 @@
       <c r="A300" s="1"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
-      <c r="D300" s="46"/>
+      <c r="D300" s="45"/>
       <c r="E300" s="3"/>
       <c r="F300" s="3"/>
       <c r="G300" s="3"/>
@@ -10202,7 +10211,7 @@
       <c r="A301" s="1"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
-      <c r="D301" s="46"/>
+      <c r="D301" s="45"/>
       <c r="E301" s="3"/>
       <c r="F301" s="3"/>
       <c r="G301" s="3"/>
@@ -10230,7 +10239,7 @@
       <c r="A302" s="1"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
-      <c r="D302" s="46"/>
+      <c r="D302" s="45"/>
       <c r="E302" s="3"/>
       <c r="F302" s="3"/>
       <c r="G302" s="3"/>
@@ -10258,7 +10267,7 @@
       <c r="A303" s="1"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
-      <c r="D303" s="46"/>
+      <c r="D303" s="45"/>
       <c r="E303" s="3"/>
       <c r="F303" s="3"/>
       <c r="G303" s="3"/>
@@ -10286,7 +10295,7 @@
       <c r="A304" s="1"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
-      <c r="D304" s="46"/>
+      <c r="D304" s="45"/>
       <c r="E304" s="3"/>
       <c r="F304" s="3"/>
       <c r="G304" s="3"/>
@@ -10314,7 +10323,7 @@
       <c r="A305" s="1"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
-      <c r="D305" s="46"/>
+      <c r="D305" s="45"/>
       <c r="E305" s="3"/>
       <c r="F305" s="3"/>
       <c r="G305" s="3"/>
@@ -10342,7 +10351,7 @@
       <c r="A306" s="1"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
-      <c r="D306" s="46"/>
+      <c r="D306" s="45"/>
       <c r="E306" s="3"/>
       <c r="F306" s="3"/>
       <c r="G306" s="3"/>
@@ -10370,7 +10379,7 @@
       <c r="A307" s="1"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
-      <c r="D307" s="46"/>
+      <c r="D307" s="45"/>
       <c r="E307" s="3"/>
       <c r="F307" s="3"/>
       <c r="G307" s="3"/>
@@ -10398,7 +10407,7 @@
       <c r="A308" s="1"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
-      <c r="D308" s="46"/>
+      <c r="D308" s="45"/>
       <c r="E308" s="3"/>
       <c r="F308" s="3"/>
       <c r="G308" s="3"/>
@@ -10426,7 +10435,7 @@
       <c r="A309" s="1"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
-      <c r="D309" s="46"/>
+      <c r="D309" s="45"/>
       <c r="E309" s="3"/>
       <c r="F309" s="3"/>
       <c r="G309" s="3"/>
@@ -10454,7 +10463,7 @@
       <c r="A310" s="1"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
-      <c r="D310" s="46"/>
+      <c r="D310" s="45"/>
       <c r="E310" s="3"/>
       <c r="F310" s="3"/>
       <c r="G310" s="3"/>
@@ -10482,7 +10491,7 @@
       <c r="A311" s="1"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
-      <c r="D311" s="46"/>
+      <c r="D311" s="45"/>
       <c r="E311" s="3"/>
       <c r="F311" s="3"/>
       <c r="G311" s="3"/>
@@ -10510,7 +10519,7 @@
       <c r="A312" s="1"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
-      <c r="D312" s="46"/>
+      <c r="D312" s="45"/>
       <c r="E312" s="3"/>
       <c r="F312" s="3"/>
       <c r="G312" s="3"/>
@@ -10538,7 +10547,7 @@
       <c r="A313" s="1"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
-      <c r="D313" s="46"/>
+      <c r="D313" s="45"/>
       <c r="E313" s="3"/>
       <c r="F313" s="3"/>
       <c r="G313" s="3"/>
@@ -10566,7 +10575,7 @@
       <c r="A314" s="1"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
-      <c r="D314" s="46"/>
+      <c r="D314" s="45"/>
       <c r="E314" s="3"/>
       <c r="F314" s="3"/>
       <c r="G314" s="3"/>
@@ -10594,7 +10603,7 @@
       <c r="A315" s="1"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
-      <c r="D315" s="46"/>
+      <c r="D315" s="45"/>
       <c r="E315" s="3"/>
       <c r="F315" s="3"/>
       <c r="G315" s="3"/>
@@ -10622,7 +10631,7 @@
       <c r="A316" s="1"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
-      <c r="D316" s="46"/>
+      <c r="D316" s="45"/>
       <c r="E316" s="3"/>
       <c r="F316" s="3"/>
       <c r="G316" s="3"/>
@@ -10650,7 +10659,7 @@
       <c r="A317" s="1"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
-      <c r="D317" s="46"/>
+      <c r="D317" s="45"/>
       <c r="E317" s="3"/>
       <c r="F317" s="3"/>
       <c r="G317" s="3"/>
@@ -10678,7 +10687,7 @@
       <c r="A318" s="1"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
-      <c r="D318" s="46"/>
+      <c r="D318" s="45"/>
       <c r="E318" s="3"/>
       <c r="F318" s="3"/>
       <c r="G318" s="3"/>
@@ -10706,7 +10715,7 @@
       <c r="A319" s="1"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
-      <c r="D319" s="46"/>
+      <c r="D319" s="45"/>
       <c r="E319" s="3"/>
       <c r="F319" s="3"/>
       <c r="G319" s="3"/>
@@ -10734,7 +10743,7 @@
       <c r="A320" s="1"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
-      <c r="D320" s="46"/>
+      <c r="D320" s="45"/>
       <c r="E320" s="3"/>
       <c r="F320" s="3"/>
       <c r="G320" s="3"/>
@@ -10762,7 +10771,7 @@
       <c r="A321" s="1"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
-      <c r="D321" s="46"/>
+      <c r="D321" s="45"/>
       <c r="E321" s="3"/>
       <c r="F321" s="3"/>
       <c r="G321" s="3"/>
@@ -10790,7 +10799,7 @@
       <c r="A322" s="1"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
-      <c r="D322" s="46"/>
+      <c r="D322" s="45"/>
       <c r="E322" s="3"/>
       <c r="F322" s="3"/>
       <c r="G322" s="3"/>
@@ -10818,7 +10827,7 @@
       <c r="A323" s="1"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
-      <c r="D323" s="46"/>
+      <c r="D323" s="45"/>
       <c r="E323" s="3"/>
       <c r="F323" s="3"/>
       <c r="G323" s="3"/>
@@ -10846,7 +10855,7 @@
       <c r="A324" s="1"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
-      <c r="D324" s="46"/>
+      <c r="D324" s="45"/>
       <c r="E324" s="3"/>
       <c r="F324" s="3"/>
       <c r="G324" s="3"/>
@@ -10874,7 +10883,7 @@
       <c r="A325" s="1"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
-      <c r="D325" s="46"/>
+      <c r="D325" s="45"/>
       <c r="E325" s="3"/>
       <c r="F325" s="3"/>
       <c r="G325" s="3"/>
@@ -10902,7 +10911,7 @@
       <c r="A326" s="1"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
-      <c r="D326" s="46"/>
+      <c r="D326" s="45"/>
       <c r="E326" s="3"/>
       <c r="F326" s="3"/>
       <c r="G326" s="3"/>
@@ -10930,7 +10939,7 @@
       <c r="A327" s="1"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
-      <c r="D327" s="46"/>
+      <c r="D327" s="45"/>
       <c r="E327" s="3"/>
       <c r="F327" s="3"/>
       <c r="G327" s="3"/>
@@ -10958,7 +10967,7 @@
       <c r="A328" s="1"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
-      <c r="D328" s="46"/>
+      <c r="D328" s="45"/>
       <c r="E328" s="3"/>
       <c r="F328" s="3"/>
       <c r="G328" s="3"/>
@@ -10986,7 +10995,7 @@
       <c r="A329" s="1"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
-      <c r="D329" s="46"/>
+      <c r="D329" s="45"/>
       <c r="E329" s="3"/>
       <c r="F329" s="3"/>
       <c r="G329" s="3"/>
@@ -11014,7 +11023,7 @@
       <c r="A330" s="1"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
-      <c r="D330" s="46"/>
+      <c r="D330" s="45"/>
       <c r="E330" s="3"/>
       <c r="F330" s="3"/>
       <c r="G330" s="3"/>
@@ -11042,7 +11051,7 @@
       <c r="A331" s="1"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
-      <c r="D331" s="46"/>
+      <c r="D331" s="45"/>
       <c r="E331" s="3"/>
       <c r="F331" s="3"/>
       <c r="G331" s="3"/>
@@ -11070,7 +11079,7 @@
       <c r="A332" s="1"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
-      <c r="D332" s="46"/>
+      <c r="D332" s="45"/>
       <c r="E332" s="3"/>
       <c r="F332" s="3"/>
       <c r="G332" s="3"/>
@@ -11098,7 +11107,7 @@
       <c r="A333" s="1"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
-      <c r="D333" s="46"/>
+      <c r="D333" s="45"/>
       <c r="E333" s="3"/>
       <c r="F333" s="3"/>
       <c r="G333" s="3"/>
@@ -11126,7 +11135,7 @@
       <c r="A334" s="1"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
-      <c r="D334" s="46"/>
+      <c r="D334" s="45"/>
       <c r="E334" s="3"/>
       <c r="F334" s="3"/>
       <c r="G334" s="3"/>
@@ -11154,7 +11163,7 @@
       <c r="A335" s="1"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
-      <c r="D335" s="46"/>
+      <c r="D335" s="45"/>
       <c r="E335" s="3"/>
       <c r="F335" s="3"/>
       <c r="G335" s="3"/>
@@ -11182,7 +11191,7 @@
       <c r="A336" s="1"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
-      <c r="D336" s="46"/>
+      <c r="D336" s="45"/>
       <c r="E336" s="3"/>
       <c r="F336" s="3"/>
       <c r="G336" s="3"/>
@@ -11210,7 +11219,7 @@
       <c r="A337" s="1"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
-      <c r="D337" s="46"/>
+      <c r="D337" s="45"/>
       <c r="E337" s="3"/>
       <c r="F337" s="3"/>
       <c r="G337" s="3"/>
@@ -11238,7 +11247,7 @@
       <c r="A338" s="1"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
-      <c r="D338" s="46"/>
+      <c r="D338" s="45"/>
       <c r="E338" s="3"/>
       <c r="F338" s="3"/>
       <c r="G338" s="3"/>
@@ -11266,7 +11275,7 @@
       <c r="A339" s="1"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
-      <c r="D339" s="46"/>
+      <c r="D339" s="45"/>
       <c r="E339" s="3"/>
       <c r="F339" s="3"/>
       <c r="G339" s="3"/>
@@ -11294,7 +11303,7 @@
       <c r="A340" s="1"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
-      <c r="D340" s="46"/>
+      <c r="D340" s="45"/>
       <c r="E340" s="3"/>
       <c r="F340" s="3"/>
       <c r="G340" s="3"/>
@@ -11322,7 +11331,7 @@
       <c r="A341" s="1"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
-      <c r="D341" s="46"/>
+      <c r="D341" s="45"/>
       <c r="E341" s="3"/>
       <c r="F341" s="3"/>
       <c r="G341" s="3"/>
@@ -11350,7 +11359,7 @@
       <c r="A342" s="1"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
-      <c r="D342" s="46"/>
+      <c r="D342" s="45"/>
       <c r="E342" s="3"/>
       <c r="F342" s="3"/>
       <c r="G342" s="3"/>
@@ -11378,7 +11387,7 @@
       <c r="A343" s="1"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
-      <c r="D343" s="46"/>
+      <c r="D343" s="45"/>
       <c r="E343" s="3"/>
       <c r="F343" s="3"/>
       <c r="G343" s="3"/>
@@ -11406,7 +11415,7 @@
       <c r="A344" s="1"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
-      <c r="D344" s="46"/>
+      <c r="D344" s="45"/>
       <c r="E344" s="3"/>
       <c r="F344" s="3"/>
       <c r="G344" s="3"/>
@@ -11434,7 +11443,7 @@
       <c r="A345" s="1"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
-      <c r="D345" s="46"/>
+      <c r="D345" s="45"/>
       <c r="E345" s="3"/>
       <c r="F345" s="3"/>
       <c r="G345" s="3"/>
@@ -11462,7 +11471,7 @@
       <c r="A346" s="1"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
-      <c r="D346" s="46"/>
+      <c r="D346" s="45"/>
       <c r="E346" s="3"/>
       <c r="F346" s="3"/>
       <c r="G346" s="3"/>
@@ -11490,7 +11499,7 @@
       <c r="A347" s="1"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
-      <c r="D347" s="46"/>
+      <c r="D347" s="45"/>
       <c r="E347" s="3"/>
       <c r="F347" s="3"/>
       <c r="G347" s="3"/>
@@ -11518,7 +11527,7 @@
       <c r="A348" s="1"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
-      <c r="D348" s="46"/>
+      <c r="D348" s="45"/>
       <c r="E348" s="3"/>
       <c r="F348" s="3"/>
       <c r="G348" s="3"/>
@@ -11546,7 +11555,7 @@
       <c r="A349" s="1"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
-      <c r="D349" s="46"/>
+      <c r="D349" s="45"/>
       <c r="E349" s="3"/>
       <c r="F349" s="3"/>
       <c r="G349" s="3"/>
@@ -11574,7 +11583,7 @@
       <c r="A350" s="1"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
-      <c r="D350" s="46"/>
+      <c r="D350" s="45"/>
       <c r="E350" s="3"/>
       <c r="F350" s="3"/>
       <c r="G350" s="3"/>
@@ -11602,7 +11611,7 @@
       <c r="A351" s="1"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
-      <c r="D351" s="46"/>
+      <c r="D351" s="45"/>
       <c r="E351" s="3"/>
       <c r="F351" s="3"/>
       <c r="G351" s="3"/>
@@ -11630,7 +11639,7 @@
       <c r="A352" s="1"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
-      <c r="D352" s="46"/>
+      <c r="D352" s="45"/>
       <c r="E352" s="3"/>
       <c r="F352" s="3"/>
       <c r="G352" s="3"/>
@@ -11658,7 +11667,7 @@
       <c r="A353" s="1"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
-      <c r="D353" s="46"/>
+      <c r="D353" s="45"/>
       <c r="E353" s="3"/>
       <c r="F353" s="3"/>
       <c r="G353" s="3"/>
@@ -11686,7 +11695,7 @@
       <c r="A354" s="1"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
-      <c r="D354" s="46"/>
+      <c r="D354" s="45"/>
       <c r="E354" s="3"/>
       <c r="F354" s="3"/>
       <c r="G354" s="3"/>
@@ -11714,7 +11723,7 @@
       <c r="A355" s="1"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
-      <c r="D355" s="46"/>
+      <c r="D355" s="45"/>
       <c r="E355" s="3"/>
       <c r="F355" s="3"/>
       <c r="G355" s="3"/>
@@ -11742,7 +11751,7 @@
       <c r="A356" s="1"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
-      <c r="D356" s="46"/>
+      <c r="D356" s="45"/>
       <c r="E356" s="3"/>
       <c r="F356" s="3"/>
       <c r="G356" s="3"/>
@@ -11770,7 +11779,7 @@
       <c r="A357" s="1"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
-      <c r="D357" s="46"/>
+      <c r="D357" s="45"/>
       <c r="E357" s="3"/>
       <c r="F357" s="3"/>
       <c r="G357" s="3"/>
@@ -11798,7 +11807,7 @@
       <c r="A358" s="1"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
-      <c r="D358" s="46"/>
+      <c r="D358" s="45"/>
       <c r="E358" s="3"/>
       <c r="F358" s="3"/>
       <c r="G358" s="3"/>
@@ -11826,7 +11835,7 @@
       <c r="A359" s="1"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
-      <c r="D359" s="46"/>
+      <c r="D359" s="45"/>
       <c r="E359" s="3"/>
       <c r="F359" s="3"/>
       <c r="G359" s="3"/>
@@ -11854,7 +11863,7 @@
       <c r="A360" s="1"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
-      <c r="D360" s="46"/>
+      <c r="D360" s="45"/>
       <c r="E360" s="3"/>
       <c r="F360" s="3"/>
       <c r="G360" s="3"/>
@@ -11882,7 +11891,7 @@
       <c r="A361" s="1"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
-      <c r="D361" s="46"/>
+      <c r="D361" s="45"/>
       <c r="E361" s="3"/>
       <c r="F361" s="3"/>
       <c r="G361" s="3"/>
@@ -11910,7 +11919,7 @@
       <c r="A362" s="1"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
-      <c r="D362" s="46"/>
+      <c r="D362" s="45"/>
       <c r="E362" s="3"/>
       <c r="F362" s="3"/>
       <c r="G362" s="3"/>
@@ -11938,7 +11947,7 @@
       <c r="A363" s="1"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
-      <c r="D363" s="46"/>
+      <c r="D363" s="45"/>
       <c r="E363" s="3"/>
       <c r="F363" s="3"/>
       <c r="G363" s="3"/>
@@ -11966,7 +11975,7 @@
       <c r="A364" s="1"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
-      <c r="D364" s="46"/>
+      <c r="D364" s="45"/>
       <c r="E364" s="3"/>
       <c r="F364" s="3"/>
       <c r="G364" s="3"/>
@@ -11994,7 +12003,7 @@
       <c r="A365" s="1"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
-      <c r="D365" s="46"/>
+      <c r="D365" s="45"/>
       <c r="E365" s="3"/>
       <c r="F365" s="3"/>
       <c r="G365" s="3"/>
@@ -12022,7 +12031,7 @@
       <c r="A366" s="1"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
-      <c r="D366" s="46"/>
+      <c r="D366" s="45"/>
       <c r="E366" s="3"/>
       <c r="F366" s="3"/>
       <c r="G366" s="3"/>
@@ -12050,7 +12059,7 @@
       <c r="A367" s="1"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
-      <c r="D367" s="46"/>
+      <c r="D367" s="45"/>
       <c r="E367" s="3"/>
       <c r="F367" s="3"/>
       <c r="G367" s="3"/>
@@ -12078,7 +12087,7 @@
       <c r="A368" s="1"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="46"/>
+      <c r="D368" s="45"/>
       <c r="E368" s="3"/>
       <c r="F368" s="3"/>
       <c r="G368" s="3"/>
@@ -12106,7 +12115,7 @@
       <c r="A369" s="1"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
-      <c r="D369" s="46"/>
+      <c r="D369" s="45"/>
       <c r="E369" s="3"/>
       <c r="F369" s="3"/>
       <c r="G369" s="3"/>
@@ -12134,7 +12143,7 @@
       <c r="A370" s="1"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
-      <c r="D370" s="46"/>
+      <c r="D370" s="45"/>
       <c r="E370" s="3"/>
       <c r="F370" s="3"/>
       <c r="G370" s="3"/>
@@ -12162,7 +12171,7 @@
       <c r="A371" s="1"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
-      <c r="D371" s="46"/>
+      <c r="D371" s="45"/>
       <c r="E371" s="3"/>
       <c r="F371" s="3"/>
       <c r="G371" s="3"/>
@@ -12190,7 +12199,7 @@
       <c r="A372" s="1"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
-      <c r="D372" s="46"/>
+      <c r="D372" s="45"/>
       <c r="E372" s="3"/>
       <c r="F372" s="3"/>
       <c r="G372" s="3"/>
@@ -12218,7 +12227,7 @@
       <c r="A373" s="1"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
-      <c r="D373" s="46"/>
+      <c r="D373" s="45"/>
       <c r="E373" s="3"/>
       <c r="F373" s="3"/>
       <c r="G373" s="3"/>
@@ -12246,7 +12255,7 @@
       <c r="A374" s="1"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
-      <c r="D374" s="46"/>
+      <c r="D374" s="45"/>
       <c r="E374" s="3"/>
       <c r="F374" s="3"/>
       <c r="G374" s="3"/>
@@ -12274,7 +12283,7 @@
       <c r="A375" s="1"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
-      <c r="D375" s="46"/>
+      <c r="D375" s="45"/>
       <c r="E375" s="3"/>
       <c r="F375" s="3"/>
       <c r="G375" s="3"/>
@@ -12302,7 +12311,7 @@
       <c r="A376" s="1"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
-      <c r="D376" s="46"/>
+      <c r="D376" s="45"/>
       <c r="E376" s="3"/>
       <c r="F376" s="3"/>
       <c r="G376" s="3"/>
@@ -12330,7 +12339,7 @@
       <c r="A377" s="1"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
-      <c r="D377" s="46"/>
+      <c r="D377" s="45"/>
       <c r="E377" s="3"/>
       <c r="F377" s="3"/>
       <c r="G377" s="3"/>
@@ -12358,7 +12367,7 @@
       <c r="A378" s="1"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
-      <c r="D378" s="46"/>
+      <c r="D378" s="45"/>
       <c r="E378" s="3"/>
       <c r="F378" s="3"/>
       <c r="G378" s="3"/>
@@ -12386,7 +12395,7 @@
       <c r="A379" s="1"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
-      <c r="D379" s="46"/>
+      <c r="D379" s="45"/>
       <c r="E379" s="3"/>
       <c r="F379" s="3"/>
       <c r="G379" s="3"/>
@@ -12414,7 +12423,7 @@
       <c r="A380" s="1"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
-      <c r="D380" s="46"/>
+      <c r="D380" s="45"/>
       <c r="E380" s="3"/>
       <c r="F380" s="3"/>
       <c r="G380" s="3"/>
@@ -12442,7 +12451,7 @@
       <c r="A381" s="1"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
-      <c r="D381" s="46"/>
+      <c r="D381" s="45"/>
       <c r="E381" s="3"/>
       <c r="F381" s="3"/>
       <c r="G381" s="3"/>
@@ -12470,7 +12479,7 @@
       <c r="A382" s="1"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
-      <c r="D382" s="46"/>
+      <c r="D382" s="45"/>
       <c r="E382" s="3"/>
       <c r="F382" s="3"/>
       <c r="G382" s="3"/>
@@ -12498,7 +12507,7 @@
       <c r="A383" s="1"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
-      <c r="D383" s="46"/>
+      <c r="D383" s="45"/>
       <c r="E383" s="3"/>
       <c r="F383" s="3"/>
       <c r="G383" s="3"/>
@@ -12526,7 +12535,7 @@
       <c r="A384" s="1"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
-      <c r="D384" s="46"/>
+      <c r="D384" s="45"/>
       <c r="E384" s="3"/>
       <c r="F384" s="3"/>
       <c r="G384" s="3"/>
@@ -12554,7 +12563,7 @@
       <c r="A385" s="1"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
-      <c r="D385" s="46"/>
+      <c r="D385" s="45"/>
       <c r="E385" s="3"/>
       <c r="F385" s="3"/>
       <c r="G385" s="3"/>
@@ -12582,7 +12591,7 @@
       <c r="A386" s="1"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
-      <c r="D386" s="46"/>
+      <c r="D386" s="45"/>
       <c r="E386" s="3"/>
       <c r="F386" s="3"/>
       <c r="G386" s="3"/>
@@ -12610,7 +12619,7 @@
       <c r="A387" s="1"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
-      <c r="D387" s="46"/>
+      <c r="D387" s="45"/>
       <c r="E387" s="3"/>
       <c r="F387" s="3"/>
       <c r="G387" s="3"/>
@@ -12638,7 +12647,7 @@
       <c r="A388" s="1"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
-      <c r="D388" s="46"/>
+      <c r="D388" s="45"/>
       <c r="E388" s="3"/>
       <c r="F388" s="3"/>
       <c r="G388" s="3"/>
@@ -12666,7 +12675,7 @@
       <c r="A389" s="1"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
-      <c r="D389" s="46"/>
+      <c r="D389" s="45"/>
       <c r="E389" s="3"/>
       <c r="F389" s="3"/>
       <c r="G389" s="3"/>
@@ -12694,7 +12703,7 @@
       <c r="A390" s="1"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
-      <c r="D390" s="46"/>
+      <c r="D390" s="45"/>
       <c r="E390" s="3"/>
       <c r="F390" s="3"/>
       <c r="G390" s="3"/>
@@ -12722,7 +12731,7 @@
       <c r="A391" s="1"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
-      <c r="D391" s="46"/>
+      <c r="D391" s="45"/>
       <c r="E391" s="3"/>
       <c r="F391" s="3"/>
       <c r="G391" s="3"/>
@@ -12750,7 +12759,7 @@
       <c r="A392" s="1"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
-      <c r="D392" s="46"/>
+      <c r="D392" s="45"/>
       <c r="E392" s="3"/>
       <c r="F392" s="3"/>
       <c r="G392" s="3"/>
@@ -12778,7 +12787,7 @@
       <c r="A393" s="1"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
-      <c r="D393" s="46"/>
+      <c r="D393" s="45"/>
       <c r="E393" s="3"/>
       <c r="F393" s="3"/>
       <c r="G393" s="3"/>
@@ -12806,7 +12815,7 @@
       <c r="A394" s="1"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
-      <c r="D394" s="46"/>
+      <c r="D394" s="45"/>
       <c r="E394" s="3"/>
       <c r="F394" s="3"/>
       <c r="G394" s="3"/>
@@ -12834,7 +12843,7 @@
       <c r="A395" s="1"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
-      <c r="D395" s="46"/>
+      <c r="D395" s="45"/>
       <c r="E395" s="3"/>
       <c r="F395" s="3"/>
       <c r="G395" s="3"/>
@@ -12862,7 +12871,7 @@
       <c r="A396" s="1"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
-      <c r="D396" s="46"/>
+      <c r="D396" s="45"/>
       <c r="E396" s="3"/>
       <c r="F396" s="3"/>
       <c r="G396" s="3"/>
@@ -12890,7 +12899,7 @@
       <c r="A397" s="1"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
-      <c r="D397" s="46"/>
+      <c r="D397" s="45"/>
       <c r="E397" s="3"/>
       <c r="F397" s="3"/>
       <c r="G397" s="3"/>
@@ -12918,7 +12927,7 @@
       <c r="A398" s="1"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
-      <c r="D398" s="46"/>
+      <c r="D398" s="45"/>
       <c r="E398" s="3"/>
       <c r="F398" s="3"/>
       <c r="G398" s="3"/>
@@ -12946,7 +12955,7 @@
       <c r="A399" s="1"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
-      <c r="D399" s="46"/>
+      <c r="D399" s="45"/>
       <c r="E399" s="3"/>
       <c r="F399" s="3"/>
       <c r="G399" s="3"/>
@@ -12974,7 +12983,7 @@
       <c r="A400" s="1"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
-      <c r="D400" s="46"/>
+      <c r="D400" s="45"/>
       <c r="E400" s="3"/>
       <c r="F400" s="3"/>
       <c r="G400" s="3"/>
@@ -13002,7 +13011,7 @@
       <c r="A401" s="1"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
-      <c r="D401" s="46"/>
+      <c r="D401" s="45"/>
       <c r="E401" s="3"/>
       <c r="F401" s="3"/>
       <c r="G401" s="3"/>
@@ -13030,7 +13039,7 @@
       <c r="A402" s="1"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
-      <c r="D402" s="46"/>
+      <c r="D402" s="45"/>
       <c r="E402" s="3"/>
       <c r="F402" s="3"/>
       <c r="G402" s="3"/>
@@ -13058,7 +13067,7 @@
       <c r="A403" s="1"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
-      <c r="D403" s="46"/>
+      <c r="D403" s="45"/>
       <c r="E403" s="3"/>
       <c r="F403" s="3"/>
       <c r="G403" s="3"/>
@@ -13086,7 +13095,7 @@
       <c r="A404" s="1"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
-      <c r="D404" s="46"/>
+      <c r="D404" s="45"/>
       <c r="E404" s="3"/>
       <c r="F404" s="3"/>
       <c r="G404" s="3"/>
@@ -13114,7 +13123,7 @@
       <c r="A405" s="1"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
-      <c r="D405" s="46"/>
+      <c r="D405" s="45"/>
       <c r="E405" s="3"/>
       <c r="F405" s="3"/>
       <c r="G405" s="3"/>
@@ -13142,7 +13151,7 @@
       <c r="A406" s="1"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
-      <c r="D406" s="46"/>
+      <c r="D406" s="45"/>
       <c r="E406" s="3"/>
       <c r="F406" s="3"/>
       <c r="G406" s="3"/>
@@ -13170,7 +13179,7 @@
       <c r="A407" s="1"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
-      <c r="D407" s="46"/>
+      <c r="D407" s="45"/>
       <c r="E407" s="3"/>
       <c r="F407" s="3"/>
       <c r="G407" s="3"/>
@@ -13198,7 +13207,7 @@
       <c r="A408" s="1"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
-      <c r="D408" s="46"/>
+      <c r="D408" s="45"/>
       <c r="E408" s="3"/>
       <c r="F408" s="3"/>
       <c r="G408" s="3"/>
@@ -13226,7 +13235,7 @@
       <c r="A409" s="1"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
-      <c r="D409" s="46"/>
+      <c r="D409" s="45"/>
       <c r="E409" s="3"/>
       <c r="F409" s="3"/>
       <c r="G409" s="3"/>
@@ -13254,7 +13263,7 @@
       <c r="A410" s="1"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
-      <c r="D410" s="46"/>
+      <c r="D410" s="45"/>
       <c r="E410" s="3"/>
       <c r="F410" s="3"/>
       <c r="G410" s="3"/>
@@ -13282,7 +13291,7 @@
       <c r="A411" s="1"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
-      <c r="D411" s="46"/>
+      <c r="D411" s="45"/>
       <c r="E411" s="3"/>
       <c r="F411" s="3"/>
       <c r="G411" s="3"/>
@@ -13310,7 +13319,7 @@
       <c r="A412" s="1"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
-      <c r="D412" s="46"/>
+      <c r="D412" s="45"/>
       <c r="E412" s="3"/>
       <c r="F412" s="3"/>
       <c r="G412" s="3"/>
@@ -13338,7 +13347,7 @@
       <c r="A413" s="1"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
-      <c r="D413" s="46"/>
+      <c r="D413" s="45"/>
       <c r="E413" s="3"/>
       <c r="F413" s="3"/>
       <c r="G413" s="3"/>
@@ -13366,7 +13375,7 @@
       <c r="A414" s="1"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
-      <c r="D414" s="46"/>
+      <c r="D414" s="45"/>
       <c r="E414" s="3"/>
       <c r="F414" s="3"/>
       <c r="G414" s="3"/>
@@ -13394,7 +13403,7 @@
       <c r="A415" s="1"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
-      <c r="D415" s="46"/>
+      <c r="D415" s="45"/>
       <c r="E415" s="3"/>
       <c r="F415" s="3"/>
       <c r="G415" s="3"/>
@@ -13422,7 +13431,7 @@
       <c r="A416" s="1"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
-      <c r="D416" s="46"/>
+      <c r="D416" s="45"/>
       <c r="E416" s="3"/>
       <c r="F416" s="3"/>
       <c r="G416" s="3"/>
@@ -13450,7 +13459,7 @@
       <c r="A417" s="1"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
-      <c r="D417" s="46"/>
+      <c r="D417" s="45"/>
       <c r="E417" s="3"/>
       <c r="F417" s="3"/>
       <c r="G417" s="3"/>
@@ -13478,7 +13487,7 @@
       <c r="A418" s="1"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
-      <c r="D418" s="46"/>
+      <c r="D418" s="45"/>
       <c r="E418" s="3"/>
       <c r="F418" s="3"/>
       <c r="G418" s="3"/>
@@ -13506,7 +13515,7 @@
       <c r="A419" s="1"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
-      <c r="D419" s="46"/>
+      <c r="D419" s="45"/>
       <c r="E419" s="3"/>
       <c r="F419" s="3"/>
       <c r="G419" s="3"/>
@@ -13534,7 +13543,7 @@
       <c r="A420" s="1"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
-      <c r="D420" s="46"/>
+      <c r="D420" s="45"/>
       <c r="E420" s="3"/>
       <c r="F420" s="3"/>
       <c r="G420" s="3"/>
@@ -13562,7 +13571,7 @@
       <c r="A421" s="1"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
-      <c r="D421" s="46"/>
+      <c r="D421" s="45"/>
       <c r="E421" s="3"/>
       <c r="F421" s="3"/>
       <c r="G421" s="3"/>
@@ -13590,7 +13599,7 @@
       <c r="A422" s="1"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
-      <c r="D422" s="46"/>
+      <c r="D422" s="45"/>
       <c r="E422" s="3"/>
       <c r="F422" s="3"/>
       <c r="G422" s="3"/>
@@ -13618,7 +13627,7 @@
       <c r="A423" s="1"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
-      <c r="D423" s="46"/>
+      <c r="D423" s="45"/>
       <c r="E423" s="3"/>
       <c r="F423" s="3"/>
       <c r="G423" s="3"/>
@@ -13646,7 +13655,7 @@
       <c r="A424" s="1"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
-      <c r="D424" s="46"/>
+      <c r="D424" s="45"/>
       <c r="E424" s="3"/>
       <c r="F424" s="3"/>
       <c r="G424" s="3"/>
@@ -13674,7 +13683,7 @@
       <c r="A425" s="1"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
-      <c r="D425" s="46"/>
+      <c r="D425" s="45"/>
       <c r="E425" s="3"/>
       <c r="F425" s="3"/>
       <c r="G425" s="3"/>
@@ -13702,7 +13711,7 @@
       <c r="A426" s="1"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
-      <c r="D426" s="46"/>
+      <c r="D426" s="45"/>
       <c r="E426" s="3"/>
       <c r="F426" s="3"/>
       <c r="G426" s="3"/>
@@ -13730,7 +13739,7 @@
       <c r="A427" s="1"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
-      <c r="D427" s="46"/>
+      <c r="D427" s="45"/>
       <c r="E427" s="3"/>
       <c r="F427" s="3"/>
       <c r="G427" s="3"/>
@@ -13758,7 +13767,7 @@
       <c r="A428" s="1"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
-      <c r="D428" s="46"/>
+      <c r="D428" s="45"/>
       <c r="E428" s="3"/>
       <c r="F428" s="3"/>
       <c r="G428" s="3"/>
@@ -13786,7 +13795,7 @@
       <c r="A429" s="1"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
-      <c r="D429" s="46"/>
+      <c r="D429" s="45"/>
       <c r="E429" s="3"/>
       <c r="F429" s="3"/>
       <c r="G429" s="3"/>
@@ -13814,7 +13823,7 @@
       <c r="A430" s="1"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
-      <c r="D430" s="46"/>
+      <c r="D430" s="45"/>
       <c r="E430" s="3"/>
       <c r="F430" s="3"/>
       <c r="G430" s="3"/>
@@ -13842,7 +13851,7 @@
       <c r="A431" s="1"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
-      <c r="D431" s="46"/>
+      <c r="D431" s="45"/>
       <c r="E431" s="3"/>
       <c r="F431" s="3"/>
       <c r="G431" s="3"/>
@@ -13870,7 +13879,7 @@
       <c r="A432" s="1"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
-      <c r="D432" s="46"/>
+      <c r="D432" s="45"/>
       <c r="E432" s="3"/>
       <c r="F432" s="3"/>
       <c r="G432" s="3"/>
@@ -13898,7 +13907,7 @@
       <c r="A433" s="1"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
-      <c r="D433" s="46"/>
+      <c r="D433" s="45"/>
       <c r="E433" s="3"/>
       <c r="F433" s="3"/>
       <c r="G433" s="3"/>
@@ -13926,7 +13935,7 @@
       <c r="A434" s="1"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
-      <c r="D434" s="46"/>
+      <c r="D434" s="45"/>
       <c r="E434" s="3"/>
       <c r="F434" s="3"/>
       <c r="G434" s="3"/>
@@ -13954,7 +13963,7 @@
       <c r="A435" s="1"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
-      <c r="D435" s="46"/>
+      <c r="D435" s="45"/>
       <c r="E435" s="3"/>
       <c r="F435" s="3"/>
       <c r="G435" s="3"/>
@@ -13982,7 +13991,7 @@
       <c r="A436" s="1"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
-      <c r="D436" s="46"/>
+      <c r="D436" s="45"/>
       <c r="E436" s="3"/>
       <c r="F436" s="3"/>
       <c r="G436" s="3"/>
@@ -14010,7 +14019,7 @@
       <c r="A437" s="1"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
-      <c r="D437" s="46"/>
+      <c r="D437" s="45"/>
       <c r="E437" s="3"/>
       <c r="F437" s="3"/>
       <c r="G437" s="3"/>
@@ -14038,7 +14047,7 @@
       <c r="A438" s="1"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
-      <c r="D438" s="46"/>
+      <c r="D438" s="45"/>
       <c r="E438" s="3"/>
       <c r="F438" s="3"/>
       <c r="G438" s="3"/>
@@ -14066,7 +14075,7 @@
       <c r="A439" s="1"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
-      <c r="D439" s="46"/>
+      <c r="D439" s="45"/>
       <c r="E439" s="3"/>
       <c r="F439" s="3"/>
       <c r="G439" s="3"/>
@@ -14094,7 +14103,7 @@
       <c r="A440" s="1"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
-      <c r="D440" s="46"/>
+      <c r="D440" s="45"/>
       <c r="E440" s="3"/>
       <c r="F440" s="3"/>
       <c r="G440" s="3"/>
@@ -14122,7 +14131,7 @@
       <c r="A441" s="1"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
-      <c r="D441" s="46"/>
+      <c r="D441" s="45"/>
       <c r="E441" s="3"/>
       <c r="F441" s="3"/>
       <c r="G441" s="3"/>
@@ -14150,7 +14159,7 @@
       <c r="A442" s="1"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
-      <c r="D442" s="46"/>
+      <c r="D442" s="45"/>
       <c r="E442" s="3"/>
       <c r="F442" s="3"/>
       <c r="G442" s="3"/>
@@ -14178,7 +14187,7 @@
       <c r="A443" s="1"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
-      <c r="D443" s="46"/>
+      <c r="D443" s="45"/>
       <c r="E443" s="3"/>
       <c r="F443" s="3"/>
       <c r="G443" s="3"/>
@@ -14206,7 +14215,7 @@
       <c r="A444" s="1"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
-      <c r="D444" s="46"/>
+      <c r="D444" s="45"/>
       <c r="E444" s="3"/>
       <c r="F444" s="3"/>
       <c r="G444" s="3"/>
@@ -14234,7 +14243,7 @@
       <c r="A445" s="1"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
-      <c r="D445" s="46"/>
+      <c r="D445" s="45"/>
       <c r="E445" s="3"/>
       <c r="F445" s="3"/>
       <c r="G445" s="3"/>
@@ -14262,7 +14271,7 @@
       <c r="A446" s="1"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
-      <c r="D446" s="46"/>
+      <c r="D446" s="45"/>
       <c r="E446" s="3"/>
       <c r="F446" s="3"/>
       <c r="G446" s="3"/>
@@ -14290,7 +14299,7 @@
       <c r="A447" s="1"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
-      <c r="D447" s="46"/>
+      <c r="D447" s="45"/>
       <c r="E447" s="3"/>
       <c r="F447" s="3"/>
       <c r="G447" s="3"/>
@@ -14318,7 +14327,7 @@
       <c r="A448" s="1"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
-      <c r="D448" s="46"/>
+      <c r="D448" s="45"/>
       <c r="E448" s="3"/>
       <c r="F448" s="3"/>
       <c r="G448" s="3"/>
@@ -14346,7 +14355,7 @@
       <c r="A449" s="1"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
-      <c r="D449" s="46"/>
+      <c r="D449" s="45"/>
       <c r="E449" s="3"/>
       <c r="F449" s="3"/>
       <c r="G449" s="3"/>
@@ -14374,7 +14383,7 @@
       <c r="A450" s="1"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
-      <c r="D450" s="46"/>
+      <c r="D450" s="45"/>
       <c r="E450" s="3"/>
       <c r="F450" s="3"/>
       <c r="G450" s="3"/>
@@ -14402,7 +14411,7 @@
       <c r="A451" s="1"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
-      <c r="D451" s="46"/>
+      <c r="D451" s="45"/>
       <c r="E451" s="3"/>
       <c r="F451" s="3"/>
       <c r="G451" s="3"/>
@@ -14430,7 +14439,7 @@
       <c r="A452" s="1"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
-      <c r="D452" s="46"/>
+      <c r="D452" s="45"/>
       <c r="E452" s="3"/>
       <c r="F452" s="3"/>
       <c r="G452" s="3"/>
@@ -14458,7 +14467,7 @@
       <c r="A453" s="1"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
-      <c r="D453" s="46"/>
+      <c r="D453" s="45"/>
       <c r="E453" s="3"/>
       <c r="F453" s="3"/>
       <c r="G453" s="3"/>
@@ -14486,7 +14495,7 @@
       <c r="A454" s="1"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
-      <c r="D454" s="46"/>
+      <c r="D454" s="45"/>
       <c r="E454" s="3"/>
       <c r="F454" s="3"/>
       <c r="G454" s="3"/>
@@ -14514,7 +14523,7 @@
       <c r="A455" s="1"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
-      <c r="D455" s="46"/>
+      <c r="D455" s="45"/>
       <c r="E455" s="3"/>
       <c r="F455" s="3"/>
       <c r="G455" s="3"/>
@@ -14542,7 +14551,7 @@
       <c r="A456" s="1"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
-      <c r="D456" s="46"/>
+      <c r="D456" s="45"/>
       <c r="E456" s="3"/>
       <c r="F456" s="3"/>
       <c r="G456" s="3"/>
@@ -14570,7 +14579,7 @@
       <c r="A457" s="1"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
-      <c r="D457" s="46"/>
+      <c r="D457" s="45"/>
       <c r="E457" s="3"/>
       <c r="F457" s="3"/>
       <c r="G457" s="3"/>
@@ -14598,7 +14607,7 @@
       <c r="A458" s="1"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
-      <c r="D458" s="46"/>
+      <c r="D458" s="45"/>
       <c r="E458" s="3"/>
       <c r="F458" s="3"/>
       <c r="G458" s="3"/>
@@ -14626,7 +14635,7 @@
       <c r="A459" s="1"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
-      <c r="D459" s="46"/>
+      <c r="D459" s="45"/>
       <c r="E459" s="3"/>
       <c r="F459" s="3"/>
       <c r="G459" s="3"/>
@@ -14654,7 +14663,7 @@
       <c r="A460" s="1"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
-      <c r="D460" s="46"/>
+      <c r="D460" s="45"/>
       <c r="E460" s="3"/>
       <c r="F460" s="3"/>
       <c r="G460" s="3"/>
@@ -14682,7 +14691,7 @@
       <c r="A461" s="1"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
-      <c r="D461" s="46"/>
+      <c r="D461" s="45"/>
       <c r="E461" s="3"/>
       <c r="F461" s="3"/>
       <c r="G461" s="3"/>
@@ -14710,7 +14719,7 @@
       <c r="A462" s="1"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
-      <c r="D462" s="46"/>
+      <c r="D462" s="45"/>
       <c r="E462" s="3"/>
       <c r="F462" s="3"/>
       <c r="G462" s="3"/>
@@ -14738,7 +14747,7 @@
       <c r="A463" s="1"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
-      <c r="D463" s="46"/>
+      <c r="D463" s="45"/>
       <c r="E463" s="3"/>
       <c r="F463" s="3"/>
       <c r="G463" s="3"/>
@@ -14766,7 +14775,7 @@
       <c r="A464" s="1"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
-      <c r="D464" s="46"/>
+      <c r="D464" s="45"/>
       <c r="E464" s="3"/>
       <c r="F464" s="3"/>
       <c r="G464" s="3"/>
@@ -14794,7 +14803,7 @@
       <c r="A465" s="1"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
-      <c r="D465" s="46"/>
+      <c r="D465" s="45"/>
       <c r="E465" s="3"/>
       <c r="F465" s="3"/>
       <c r="G465" s="3"/>
@@ -14822,7 +14831,7 @@
       <c r="A466" s="1"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
-      <c r="D466" s="46"/>
+      <c r="D466" s="45"/>
       <c r="E466" s="3"/>
       <c r="F466" s="3"/>
       <c r="G466" s="3"/>
@@ -14850,7 +14859,7 @@
       <c r="A467" s="1"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
-      <c r="D467" s="46"/>
+      <c r="D467" s="45"/>
       <c r="E467" s="3"/>
       <c r="F467" s="3"/>
       <c r="G467" s="3"/>
@@ -14878,7 +14887,7 @@
       <c r="A468" s="1"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
-      <c r="D468" s="46"/>
+      <c r="D468" s="45"/>
       <c r="E468" s="3"/>
       <c r="F468" s="3"/>
       <c r="G468" s="3"/>
@@ -14906,7 +14915,7 @@
       <c r="A469" s="1"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
-      <c r="D469" s="46"/>
+      <c r="D469" s="45"/>
       <c r="E469" s="3"/>
       <c r="F469" s="3"/>
       <c r="G469" s="3"/>
@@ -14934,7 +14943,7 @@
       <c r="A470" s="1"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
-      <c r="D470" s="46"/>
+      <c r="D470" s="45"/>
       <c r="E470" s="3"/>
       <c r="F470" s="3"/>
       <c r="G470" s="3"/>
@@ -14962,7 +14971,7 @@
       <c r="A471" s="1"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
-      <c r="D471" s="46"/>
+      <c r="D471" s="45"/>
       <c r="E471" s="3"/>
       <c r="F471" s="3"/>
       <c r="G471" s="3"/>
@@ -14990,7 +14999,7 @@
       <c r="A472" s="1"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
-      <c r="D472" s="46"/>
+      <c r="D472" s="45"/>
       <c r="E472" s="3"/>
       <c r="F472" s="3"/>
       <c r="G472" s="3"/>
@@ -15018,7 +15027,7 @@
       <c r="A473" s="1"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
-      <c r="D473" s="46"/>
+      <c r="D473" s="45"/>
       <c r="E473" s="3"/>
       <c r="F473" s="3"/>
       <c r="G473" s="3"/>
@@ -15046,7 +15055,7 @@
       <c r="A474" s="1"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
-      <c r="D474" s="46"/>
+      <c r="D474" s="45"/>
       <c r="E474" s="3"/>
       <c r="F474" s="3"/>
       <c r="G474" s="3"/>
@@ -15074,7 +15083,7 @@
       <c r="A475" s="1"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
-      <c r="D475" s="46"/>
+      <c r="D475" s="45"/>
       <c r="E475" s="3"/>
       <c r="F475" s="3"/>
       <c r="G475" s="3"/>
@@ -15102,7 +15111,7 @@
       <c r="A476" s="1"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
-      <c r="D476" s="46"/>
+      <c r="D476" s="45"/>
       <c r="E476" s="3"/>
       <c r="F476" s="3"/>
       <c r="G476" s="3"/>
@@ -15130,7 +15139,7 @@
       <c r="A477" s="1"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
-      <c r="D477" s="46"/>
+      <c r="D477" s="45"/>
       <c r="E477" s="3"/>
       <c r="F477" s="3"/>
       <c r="G477" s="3"/>
@@ -15158,7 +15167,7 @@
       <c r="A478" s="1"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
-      <c r="D478" s="46"/>
+      <c r="D478" s="45"/>
       <c r="E478" s="3"/>
       <c r="F478" s="3"/>
       <c r="G478" s="3"/>
@@ -15186,7 +15195,7 @@
       <c r="A479" s="1"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
-      <c r="D479" s="46"/>
+      <c r="D479" s="45"/>
       <c r="E479" s="3"/>
       <c r="F479" s="3"/>
       <c r="G479" s="3"/>
@@ -15214,7 +15223,7 @@
       <c r="A480" s="1"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
-      <c r="D480" s="46"/>
+      <c r="D480" s="45"/>
       <c r="E480" s="3"/>
       <c r="F480" s="3"/>
       <c r="G480" s="3"/>
@@ -15242,7 +15251,7 @@
       <c r="A481" s="1"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
-      <c r="D481" s="46"/>
+      <c r="D481" s="45"/>
       <c r="E481" s="3"/>
       <c r="F481" s="3"/>
       <c r="G481" s="3"/>
@@ -15270,7 +15279,7 @@
       <c r="A482" s="1"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
-      <c r="D482" s="46"/>
+      <c r="D482" s="45"/>
       <c r="E482" s="3"/>
       <c r="F482" s="3"/>
       <c r="G482" s="3"/>
@@ -15298,7 +15307,7 @@
       <c r="A483" s="1"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
-      <c r="D483" s="46"/>
+      <c r="D483" s="45"/>
       <c r="E483" s="3"/>
       <c r="F483" s="3"/>
       <c r="G483" s="3"/>
@@ -15326,7 +15335,7 @@
       <c r="A484" s="1"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
-      <c r="D484" s="46"/>
+      <c r="D484" s="45"/>
       <c r="E484" s="3"/>
       <c r="F484" s="3"/>
       <c r="G484" s="3"/>
@@ -15354,7 +15363,7 @@
       <c r="A485" s="1"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
-      <c r="D485" s="46"/>
+      <c r="D485" s="45"/>
       <c r="E485" s="3"/>
       <c r="F485" s="3"/>
       <c r="G485" s="3"/>
@@ -15382,7 +15391,7 @@
       <c r="A486" s="1"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
-      <c r="D486" s="46"/>
+      <c r="D486" s="45"/>
       <c r="E486" s="3"/>
       <c r="F486" s="3"/>
       <c r="G486" s="3"/>
@@ -15410,7 +15419,7 @@
       <c r="A487" s="1"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
-      <c r="D487" s="46"/>
+      <c r="D487" s="45"/>
       <c r="E487" s="3"/>
       <c r="F487" s="3"/>
       <c r="G487" s="3"/>
@@ -15438,7 +15447,7 @@
       <c r="A488" s="1"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
-      <c r="D488" s="46"/>
+      <c r="D488" s="45"/>
       <c r="E488" s="3"/>
       <c r="F488" s="3"/>
       <c r="G488" s="3"/>
@@ -15466,7 +15475,7 @@
       <c r="A489" s="1"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
-      <c r="D489" s="46"/>
+      <c r="D489" s="45"/>
       <c r="E489" s="3"/>
       <c r="F489" s="3"/>
       <c r="G489" s="3"/>
@@ -15494,7 +15503,7 @@
       <c r="A490" s="1"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
-      <c r="D490" s="46"/>
+      <c r="D490" s="45"/>
       <c r="E490" s="3"/>
       <c r="F490" s="3"/>
       <c r="G490" s="3"/>
@@ -15522,7 +15531,7 @@
       <c r="A491" s="1"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
-      <c r="D491" s="46"/>
+      <c r="D491" s="45"/>
       <c r="E491" s="3"/>
       <c r="F491" s="3"/>
       <c r="G491" s="3"/>
@@ -15550,7 +15559,7 @@
       <c r="A492" s="1"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
-      <c r="D492" s="46"/>
+      <c r="D492" s="45"/>
       <c r="E492" s="3"/>
       <c r="F492" s="3"/>
       <c r="G492" s="3"/>
@@ -15578,7 +15587,7 @@
       <c r="A493" s="1"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
-      <c r="D493" s="46"/>
+      <c r="D493" s="45"/>
       <c r="E493" s="3"/>
       <c r="F493" s="3"/>
       <c r="G493" s="3"/>
@@ -15606,7 +15615,7 @@
       <c r="A494" s="1"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
-      <c r="D494" s="46"/>
+      <c r="D494" s="45"/>
       <c r="E494" s="3"/>
       <c r="F494" s="3"/>
       <c r="G494" s="3"/>
@@ -15634,7 +15643,7 @@
       <c r="A495" s="1"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
-      <c r="D495" s="46"/>
+      <c r="D495" s="45"/>
       <c r="E495" s="3"/>
       <c r="F495" s="3"/>
       <c r="G495" s="3"/>
@@ -15662,7 +15671,7 @@
       <c r="A496" s="1"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
-      <c r="D496" s="46"/>
+      <c r="D496" s="45"/>
       <c r="E496" s="3"/>
       <c r="F496" s="3"/>
       <c r="G496" s="3"/>
@@ -15690,7 +15699,7 @@
       <c r="A497" s="1"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
-      <c r="D497" s="46"/>
+      <c r="D497" s="45"/>
       <c r="E497" s="3"/>
       <c r="F497" s="3"/>
       <c r="G497" s="3"/>
@@ -15718,7 +15727,7 @@
       <c r="A498" s="1"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
-      <c r="D498" s="46"/>
+      <c r="D498" s="45"/>
       <c r="E498" s="3"/>
       <c r="F498" s="3"/>
       <c r="G498" s="3"/>
@@ -15746,7 +15755,7 @@
       <c r="A499" s="1"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
-      <c r="D499" s="46"/>
+      <c r="D499" s="45"/>
       <c r="E499" s="3"/>
       <c r="F499" s="3"/>
       <c r="G499" s="3"/>
@@ -15774,7 +15783,7 @@
       <c r="A500" s="1"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
-      <c r="D500" s="46"/>
+      <c r="D500" s="45"/>
       <c r="E500" s="3"/>
       <c r="F500" s="3"/>
       <c r="G500" s="3"/>
@@ -15802,7 +15811,7 @@
       <c r="A501" s="1"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
-      <c r="D501" s="46"/>
+      <c r="D501" s="45"/>
       <c r="E501" s="3"/>
       <c r="F501" s="3"/>
       <c r="G501" s="3"/>
@@ -15830,7 +15839,7 @@
       <c r="A502" s="1"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
-      <c r="D502" s="46"/>
+      <c r="D502" s="45"/>
       <c r="E502" s="3"/>
       <c r="F502" s="3"/>
       <c r="G502" s="3"/>
@@ -15858,7 +15867,7 @@
       <c r="A503" s="1"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
-      <c r="D503" s="46"/>
+      <c r="D503" s="45"/>
       <c r="E503" s="3"/>
       <c r="F503" s="3"/>
       <c r="G503" s="3"/>
@@ -15886,7 +15895,7 @@
       <c r="A504" s="1"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
-      <c r="D504" s="46"/>
+      <c r="D504" s="45"/>
       <c r="E504" s="3"/>
       <c r="F504" s="3"/>
       <c r="G504" s="3"/>
@@ -15914,7 +15923,7 @@
       <c r="A505" s="1"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
-      <c r="D505" s="46"/>
+      <c r="D505" s="45"/>
       <c r="E505" s="3"/>
       <c r="F505" s="3"/>
       <c r="G505" s="3"/>
@@ -15942,7 +15951,7 @@
       <c r="A506" s="1"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
-      <c r="D506" s="46"/>
+      <c r="D506" s="45"/>
       <c r="E506" s="3"/>
       <c r="F506" s="3"/>
       <c r="G506" s="3"/>
@@ -15970,7 +15979,7 @@
       <c r="A507" s="1"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
-      <c r="D507" s="46"/>
+      <c r="D507" s="45"/>
       <c r="E507" s="3"/>
       <c r="F507" s="3"/>
       <c r="G507" s="3"/>
@@ -15998,7 +16007,7 @@
       <c r="A508" s="1"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
-      <c r="D508" s="46"/>
+      <c r="D508" s="45"/>
       <c r="E508" s="3"/>
       <c r="F508" s="3"/>
       <c r="G508" s="3"/>
@@ -16026,7 +16035,7 @@
       <c r="A509" s="1"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
-      <c r="D509" s="46"/>
+      <c r="D509" s="45"/>
       <c r="E509" s="3"/>
       <c r="F509" s="3"/>
       <c r="G509" s="3"/>
@@ -16054,7 +16063,7 @@
       <c r="A510" s="1"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
-      <c r="D510" s="46"/>
+      <c r="D510" s="45"/>
       <c r="E510" s="3"/>
       <c r="F510" s="3"/>
       <c r="G510" s="3"/>
@@ -16082,7 +16091,7 @@
       <c r="A511" s="1"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
-      <c r="D511" s="46"/>
+      <c r="D511" s="45"/>
       <c r="E511" s="3"/>
       <c r="F511" s="3"/>
       <c r="G511" s="3"/>
@@ -16110,7 +16119,7 @@
       <c r="A512" s="1"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
-      <c r="D512" s="46"/>
+      <c r="D512" s="45"/>
       <c r="E512" s="3"/>
       <c r="F512" s="3"/>
       <c r="G512" s="3"/>
@@ -16138,7 +16147,7 @@
       <c r="A513" s="1"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
-      <c r="D513" s="46"/>
+      <c r="D513" s="45"/>
       <c r="E513" s="3"/>
       <c r="F513" s="3"/>
       <c r="G513" s="3"/>
@@ -16166,7 +16175,7 @@
       <c r="A514" s="1"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
-      <c r="D514" s="46"/>
+      <c r="D514" s="45"/>
       <c r="E514" s="3"/>
       <c r="F514" s="3"/>
       <c r="G514" s="3"/>
@@ -16194,7 +16203,7 @@
       <c r="A515" s="1"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
-      <c r="D515" s="46"/>
+      <c r="D515" s="45"/>
       <c r="E515" s="3"/>
       <c r="F515" s="3"/>
       <c r="G515" s="3"/>
@@ -16222,7 +16231,7 @@
       <c r="A516" s="1"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
-      <c r="D516" s="46"/>
+      <c r="D516" s="45"/>
       <c r="E516" s="3"/>
       <c r="F516" s="3"/>
       <c r="G516" s="3"/>
@@ -16250,7 +16259,7 @@
       <c r="A517" s="1"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
-      <c r="D517" s="46"/>
+      <c r="D517" s="45"/>
       <c r="E517" s="3"/>
       <c r="F517" s="3"/>
       <c r="G517" s="3"/>
@@ -16278,7 +16287,7 @@
       <c r="A518" s="1"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
-      <c r="D518" s="46"/>
+      <c r="D518" s="45"/>
       <c r="E518" s="3"/>
       <c r="F518" s="3"/>
       <c r="G518" s="3"/>
@@ -16306,7 +16315,7 @@
       <c r="A519" s="1"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
-      <c r="D519" s="46"/>
+      <c r="D519" s="45"/>
       <c r="E519" s="3"/>
       <c r="F519" s="3"/>
       <c r="G519" s="3"/>
@@ -16334,7 +16343,7 @@
       <c r="A520" s="1"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
-      <c r="D520" s="46"/>
+      <c r="D520" s="45"/>
       <c r="E520" s="3"/>
       <c r="F520" s="3"/>
       <c r="G520" s="3"/>
@@ -16362,7 +16371,7 @@
       <c r="A521" s="1"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
-      <c r="D521" s="46"/>
+      <c r="D521" s="45"/>
       <c r="E521" s="3"/>
       <c r="F521" s="3"/>
       <c r="G521" s="3"/>
@@ -16390,7 +16399,7 @@
       <c r="A522" s="1"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
-      <c r="D522" s="46"/>
+      <c r="D522" s="45"/>
       <c r="E522" s="3"/>
       <c r="F522" s="3"/>
       <c r="G522" s="3"/>
@@ -16418,7 +16427,7 @@
       <c r="A523" s="1"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
-      <c r="D523" s="46"/>
+      <c r="D523" s="45"/>
       <c r="E523" s="3"/>
       <c r="F523" s="3"/>
       <c r="G523" s="3"/>
@@ -16446,7 +16455,7 @@
       <c r="A524" s="1"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
-      <c r="D524" s="46"/>
+      <c r="D524" s="45"/>
       <c r="E524" s="3"/>
       <c r="F524" s="3"/>
       <c r="G524" s="3"/>
@@ -16474,7 +16483,7 @@
       <c r="A525" s="1"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
-      <c r="D525" s="46"/>
+      <c r="D525" s="45"/>
       <c r="E525" s="3"/>
       <c r="F525" s="3"/>
       <c r="G525" s="3"/>
@@ -16502,7 +16511,7 @@
       <c r="A526" s="1"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
-      <c r="D526" s="46"/>
+      <c r="D526" s="45"/>
       <c r="E526" s="3"/>
       <c r="F526" s="3"/>
       <c r="G526" s="3"/>
@@ -16530,7 +16539,7 @@
       <c r="A527" s="1"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
-      <c r="D527" s="46"/>
+      <c r="D527" s="45"/>
       <c r="E527" s="3"/>
       <c r="F527" s="3"/>
       <c r="G527" s="3"/>
@@ -16558,7 +16567,7 @@
       <c r="A528" s="1"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
-      <c r="D528" s="46"/>
+      <c r="D528" s="45"/>
       <c r="E528" s="3"/>
       <c r="F528" s="3"/>
       <c r="G528" s="3"/>
@@ -16586,7 +16595,7 @@
       <c r="A529" s="1"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
-      <c r="D529" s="46"/>
+      <c r="D529" s="45"/>
       <c r="E529" s="3"/>
       <c r="F529" s="3"/>
       <c r="G529" s="3"/>
@@ -16614,7 +16623,7 @@
       <c r="A530" s="1"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
-      <c r="D530" s="46"/>
+      <c r="D530" s="45"/>
       <c r="E530" s="3"/>
       <c r="F530" s="3"/>
       <c r="G530" s="3"/>
@@ -16642,7 +16651,7 @@
       <c r="A531" s="1"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
-      <c r="D531" s="46"/>
+      <c r="D531" s="45"/>
       <c r="E531" s="3"/>
       <c r="F531" s="3"/>
       <c r="G531" s="3"/>
@@ -16670,7 +16679,7 @@
       <c r="A532" s="1"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
-      <c r="D532" s="46"/>
+      <c r="D532" s="45"/>
       <c r="E532" s="3"/>
       <c r="F532" s="3"/>
       <c r="G532" s="3"/>
@@ -16698,7 +16707,7 @@
       <c r="A533" s="1"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
-      <c r="D533" s="46"/>
+      <c r="D533" s="45"/>
       <c r="E533" s="3"/>
       <c r="F533" s="3"/>
       <c r="G533" s="3"/>
@@ -16726,7 +16735,7 @@
       <c r="A534" s="1"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
-      <c r="D534" s="46"/>
+      <c r="D534" s="45"/>
       <c r="E534" s="3"/>
       <c r="F534" s="3"/>
       <c r="G534" s="3"/>
@@ -16754,7 +16763,7 @@
       <c r="A535" s="1"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
-      <c r="D535" s="46"/>
+      <c r="D535" s="45"/>
       <c r="E535" s="3"/>
       <c r="F535" s="3"/>
       <c r="G535" s="3"/>
@@ -16782,7 +16791,7 @@
       <c r="A536" s="1"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
-      <c r="D536" s="46"/>
+      <c r="D536" s="45"/>
       <c r="E536" s="3"/>
       <c r="F536" s="3"/>
       <c r="G536" s="3"/>
@@ -16810,7 +16819,7 @@
       <c r="A537" s="1"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
-      <c r="D537" s="46"/>
+      <c r="D537" s="45"/>
       <c r="E537" s="3"/>
       <c r="F537" s="3"/>
       <c r="G537" s="3"/>
@@ -16838,7 +16847,7 @@
       <c r="A538" s="1"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
-      <c r="D538" s="46"/>
+      <c r="D538" s="45"/>
       <c r="E538" s="3"/>
       <c r="F538" s="3"/>
       <c r="G538" s="3"/>
@@ -16866,7 +16875,7 @@
       <c r="A539" s="1"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
-      <c r="D539" s="46"/>
+      <c r="D539" s="45"/>
       <c r="E539" s="3"/>
       <c r="F539" s="3"/>
       <c r="G539" s="3"/>
@@ -16894,7 +16903,7 @@
       <c r="A540" s="1"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
-      <c r="D540" s="46"/>
+      <c r="D540" s="45"/>
       <c r="E540" s="3"/>
       <c r="F540" s="3"/>
       <c r="G540" s="3"/>
@@ -16922,7 +16931,7 @@
       <c r="A541" s="1"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
-      <c r="D541" s="46"/>
+      <c r="D541" s="45"/>
       <c r="E541" s="3"/>
       <c r="F541" s="3"/>
       <c r="G541" s="3"/>
@@ -16950,7 +16959,7 @@
       <c r="A542" s="1"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
-      <c r="D542" s="46"/>
+      <c r="D542" s="45"/>
       <c r="E542" s="3"/>
       <c r="F542" s="3"/>
       <c r="G542" s="3"/>
@@ -16978,7 +16987,7 @@
       <c r="A543" s="1"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
-      <c r="D543" s="46"/>
+      <c r="D543" s="45"/>
       <c r="E543" s="3"/>
       <c r="F543" s="3"/>
       <c r="G543" s="3"/>
@@ -17006,7 +17015,7 @@
       <c r="A544" s="1"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
-      <c r="D544" s="46"/>
+      <c r="D544" s="45"/>
       <c r="E544" s="3"/>
       <c r="F544" s="3"/>
       <c r="G544" s="3"/>
@@ -17034,7 +17043,7 @@
       <c r="A545" s="1"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
-      <c r="D545" s="46"/>
+      <c r="D545" s="45"/>
       <c r="E545" s="3"/>
       <c r="F545" s="3"/>
       <c r="G545" s="3"/>
@@ -17062,7 +17071,7 @@
       <c r="A546" s="1"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
-      <c r="D546" s="46"/>
+      <c r="D546" s="45"/>
       <c r="E546" s="3"/>
       <c r="F546" s="3"/>
       <c r="G546" s="3"/>
@@ -17090,7 +17099,7 @@
       <c r="A547" s="1"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
-      <c r="D547" s="46"/>
+      <c r="D547" s="45"/>
       <c r="E547" s="3"/>
       <c r="F547" s="3"/>
       <c r="G547" s="3"/>
@@ -17118,7 +17127,7 @@
       <c r="A548" s="1"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
-      <c r="D548" s="46"/>
+      <c r="D548" s="45"/>
       <c r="E548" s="3"/>
       <c r="F548" s="3"/>
       <c r="G548" s="3"/>
@@ -17146,7 +17155,7 @@
       <c r="A549" s="1"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
-      <c r="D549" s="46"/>
+      <c r="D549" s="45"/>
       <c r="E549" s="3"/>
       <c r="F549" s="3"/>
       <c r="G549" s="3"/>
@@ -17174,7 +17183,7 @@
       <c r="A550" s="1"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
-      <c r="D550" s="46"/>
+      <c r="D550" s="45"/>
       <c r="E550" s="3"/>
       <c r="F550" s="3"/>
       <c r="G550" s="3"/>
@@ -17202,7 +17211,7 @@
       <c r="A551" s="1"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
-      <c r="D551" s="46"/>
+      <c r="D551" s="45"/>
       <c r="E551" s="3"/>
       <c r="F551" s="3"/>
       <c r="G551" s="3"/>
@@ -17230,7 +17239,7 @@
       <c r="A552" s="1"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
-      <c r="D552" s="46"/>
+      <c r="D552" s="45"/>
       <c r="E552" s="3"/>
       <c r="F552" s="3"/>
       <c r="G552" s="3"/>
@@ -17258,7 +17267,7 @@
       <c r="A553" s="1"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
-      <c r="D553" s="46"/>
+      <c r="D553" s="45"/>
       <c r="E553" s="3"/>
       <c r="F553" s="3"/>
       <c r="G553" s="3"/>
@@ -17286,7 +17295,7 @@
       <c r="A554" s="1"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
-      <c r="D554" s="46"/>
+      <c r="D554" s="45"/>
       <c r="E554" s="3"/>
       <c r="F554" s="3"/>
       <c r="G554" s="3"/>
@@ -17314,7 +17323,7 @@
       <c r="A555" s="1"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
-      <c r="D555" s="46"/>
+      <c r="D555" s="45"/>
       <c r="E555" s="3"/>
       <c r="F555" s="3"/>
       <c r="G555" s="3"/>
@@ -17342,7 +17351,7 @@
       <c r="A556" s="1"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
-      <c r="D556" s="46"/>
+      <c r="D556" s="45"/>
       <c r="E556" s="3"/>
       <c r="F556" s="3"/>
       <c r="G556" s="3"/>
@@ -17370,7 +17379,7 @@
       <c r="A557" s="1"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
-      <c r="D557" s="46"/>
+      <c r="D557" s="45"/>
       <c r="E557" s="3"/>
       <c r="F557" s="3"/>
       <c r="G557" s="3"/>
@@ -17398,7 +17407,7 @@
       <c r="A558" s="1"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
-      <c r="D558" s="46"/>
+      <c r="D558" s="45"/>
       <c r="E558" s="3"/>
       <c r="F558" s="3"/>
       <c r="G558" s="3"/>
@@ -17426,7 +17435,7 @@
       <c r="A559" s="1"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
-      <c r="D559" s="46"/>
+      <c r="D559" s="45"/>
       <c r="E559" s="3"/>
       <c r="F559" s="3"/>
       <c r="G559" s="3"/>
@@ -17454,7 +17463,7 @@
       <c r="A560" s="1"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
-      <c r="D560" s="46"/>
+      <c r="D560" s="45"/>
       <c r="E560" s="3"/>
       <c r="F560" s="3"/>
       <c r="G560" s="3"/>
@@ -17482,7 +17491,7 @@
       <c r="A561" s="1"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
-      <c r="D561" s="46"/>
+      <c r="D561" s="45"/>
       <c r="E561" s="3"/>
       <c r="F561" s="3"/>
       <c r="G561" s="3"/>
@@ -17510,7 +17519,7 @@
       <c r="A562" s="1"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
-      <c r="D562" s="46"/>
+      <c r="D562" s="45"/>
       <c r="E562" s="3"/>
       <c r="F562" s="3"/>
       <c r="G562" s="3"/>
@@ -17538,7 +17547,7 @@
       <c r="A563" s="1"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
-      <c r="D563" s="46"/>
+      <c r="D563" s="45"/>
       <c r="E563" s="3"/>
       <c r="F563" s="3"/>
       <c r="G563" s="3"/>
@@ -17566,7 +17575,7 @@
       <c r="A564" s="1"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
-      <c r="D564" s="46"/>
+      <c r="D564" s="45"/>
       <c r="E564" s="3"/>
       <c r="F564" s="3"/>
       <c r="G564" s="3"/>
@@ -17594,7 +17603,7 @@
       <c r="A565" s="1"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
-      <c r="D565" s="46"/>
+      <c r="D565" s="45"/>
       <c r="E565" s="3"/>
       <c r="F565" s="3"/>
       <c r="G565" s="3"/>
@@ -17622,7 +17631,7 @@
       <c r="A566" s="1"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
-      <c r="D566" s="46"/>
+      <c r="D566" s="45"/>
       <c r="E566" s="3"/>
       <c r="F566" s="3"/>
       <c r="G566" s="3"/>
@@ -17650,7 +17659,7 @@
       <c r="A567" s="1"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
-      <c r="D567" s="46"/>
+      <c r="D567" s="45"/>
       <c r="E567" s="3"/>
       <c r="F567" s="3"/>
       <c r="G567" s="3"/>
@@ -17678,7 +17687,7 @@
       <c r="A568" s="1"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
-      <c r="D568" s="46"/>
+      <c r="D568" s="45"/>
       <c r="E568" s="3"/>
       <c r="F568" s="3"/>
       <c r="G568" s="3"/>
@@ -17706,7 +17715,7 @@
       <c r="A569" s="1"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
-      <c r="D569" s="46"/>
+      <c r="D569" s="45"/>
       <c r="E569" s="3"/>
       <c r="F569" s="3"/>
       <c r="G569" s="3"/>
@@ -17734,7 +17743,7 @@
       <c r="A570" s="1"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
-      <c r="D570" s="46"/>
+      <c r="D570" s="45"/>
       <c r="E570" s="3"/>
       <c r="F570" s="3"/>
       <c r="G570" s="3"/>
@@ -17762,7 +17771,7 @@
       <c r="A571" s="1"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
-      <c r="D571" s="46"/>
+      <c r="D571" s="45"/>
       <c r="E571" s="3"/>
       <c r="F571" s="3"/>
       <c r="G571" s="3"/>
@@ -17790,7 +17799,7 @@
       <c r="A572" s="1"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
-      <c r="D572" s="46"/>
+      <c r="D572" s="45"/>
       <c r="E572" s="3"/>
       <c r="F572" s="3"/>
       <c r="G572" s="3"/>
@@ -17818,7 +17827,7 @@
       <c r="A573" s="1"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
-      <c r="D573" s="46"/>
+      <c r="D573" s="45"/>
       <c r="E573" s="3"/>
       <c r="F573" s="3"/>
       <c r="G573" s="3"/>
@@ -17846,7 +17855,7 @@
       <c r="A574" s="1"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
-      <c r="D574" s="46"/>
+      <c r="D574" s="45"/>
       <c r="E574" s="3"/>
       <c r="F574" s="3"/>
       <c r="G574" s="3"/>
@@ -17874,7 +17883,7 @@
       <c r="A575" s="1"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
-      <c r="D575" s="46"/>
+      <c r="D575" s="45"/>
       <c r="E575" s="3"/>
       <c r="F575" s="3"/>
       <c r="G575" s="3"/>
@@ -17902,7 +17911,7 @@
       <c r="A576" s="1"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
-      <c r="D576" s="46"/>
+      <c r="D576" s="45"/>
       <c r="E576" s="3"/>
       <c r="F576" s="3"/>
       <c r="G576" s="3"/>
@@ -17930,7 +17939,7 @@
       <c r="A577" s="1"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
-      <c r="D577" s="46"/>
+      <c r="D577" s="45"/>
       <c r="E577" s="3"/>
       <c r="F577" s="3"/>
       <c r="G577" s="3"/>
@@ -17958,7 +17967,7 @@
       <c r="A578" s="1"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
-      <c r="D578" s="46"/>
+      <c r="D578" s="45"/>
       <c r="E578" s="3"/>
       <c r="F578" s="3"/>
       <c r="G578" s="3"/>
@@ -17986,7 +17995,7 @@
       <c r="A579" s="1"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
-      <c r="D579" s="46"/>
+      <c r="D579" s="45"/>
       <c r="E579" s="3"/>
       <c r="F579" s="3"/>
       <c r="G579" s="3"/>
@@ -18014,7 +18023,7 @@
       <c r="A580" s="1"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
-      <c r="D580" s="46"/>
+      <c r="D580" s="45"/>
       <c r="E580" s="3"/>
       <c r="F580" s="3"/>
       <c r="G580" s="3"/>
@@ -18042,7 +18051,7 @@
       <c r="A581" s="1"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
-      <c r="D581" s="46"/>
+      <c r="D581" s="45"/>
       <c r="E581" s="3"/>
       <c r="F581" s="3"/>
       <c r="G581" s="3"/>
@@ -18070,7 +18079,7 @@
       <c r="A582" s="1"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
-      <c r="D582" s="46"/>
+      <c r="D582" s="45"/>
       <c r="E582" s="3"/>
       <c r="F582" s="3"/>
       <c r="G582" s="3"/>
@@ -18098,7 +18107,7 @@
       <c r="A583" s="1"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
-      <c r="D583" s="46"/>
+      <c r="D583" s="45"/>
       <c r="E583" s="3"/>
       <c r="F583" s="3"/>
       <c r="G583" s="3"/>
@@ -18126,7 +18135,7 @@
       <c r="A584" s="1"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
-      <c r="D584" s="46"/>
+      <c r="D584" s="45"/>
       <c r="E584" s="3"/>
       <c r="F584" s="3"/>
       <c r="G584" s="3"/>
@@ -18154,7 +18163,7 @@
       <c r="A585" s="1"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
-      <c r="D585" s="46"/>
+      <c r="D585" s="45"/>
       <c r="E585" s="3"/>
       <c r="F585" s="3"/>
       <c r="G585" s="3"/>
@@ -18182,7 +18191,7 @@
       <c r="A586" s="1"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
-      <c r="D586" s="46"/>
+      <c r="D586" s="45"/>
       <c r="E586" s="3"/>
       <c r="F586" s="3"/>
       <c r="G586" s="3"/>
@@ -18210,7 +18219,7 @@
       <c r="A587" s="1"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
-      <c r="D587" s="46"/>
+      <c r="D587" s="45"/>
       <c r="E587" s="3"/>
       <c r="F587" s="3"/>
       <c r="G587" s="3"/>
@@ -18238,7 +18247,7 @@
       <c r="A588" s="1"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
-      <c r="D588" s="46"/>
+      <c r="D588" s="45"/>
       <c r="E588" s="3"/>
       <c r="F588" s="3"/>
       <c r="G588" s="3"/>
@@ -18266,7 +18275,7 @@
       <c r="A589" s="1"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
-      <c r="D589" s="46"/>
+      <c r="D589" s="45"/>
       <c r="E589" s="3"/>
       <c r="F589" s="3"/>
       <c r="G589" s="3"/>
@@ -18294,7 +18303,7 @@
       <c r="A590" s="1"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
-      <c r="D590" s="46"/>
+      <c r="D590" s="45"/>
       <c r="E590" s="3"/>
       <c r="F590" s="3"/>
       <c r="G590" s="3"/>
@@ -18322,7 +18331,7 @@
       <c r="A591" s="1"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
-      <c r="D591" s="46"/>
+      <c r="D591" s="45"/>
       <c r="E591" s="3"/>
       <c r="F591" s="3"/>
       <c r="G591" s="3"/>
@@ -18350,7 +18359,7 @@
       <c r="A592" s="1"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
-      <c r="D592" s="46"/>
+      <c r="D592" s="45"/>
       <c r="E592" s="3"/>
       <c r="F592" s="3"/>
       <c r="G592" s="3"/>
@@ -18378,7 +18387,7 @@
       <c r="A593" s="1"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
-      <c r="D593" s="46"/>
+      <c r="D593" s="45"/>
       <c r="E593" s="3"/>
       <c r="F593" s="3"/>
       <c r="G593" s="3"/>
@@ -18406,7 +18415,7 @@
       <c r="A594" s="1"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
-      <c r="D594" s="46"/>
+      <c r="D594" s="45"/>
       <c r="E594" s="3"/>
       <c r="F594" s="3"/>
       <c r="G594" s="3"/>
@@ -18434,7 +18443,7 @@
       <c r="A595" s="1"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
-      <c r="D595" s="46"/>
+      <c r="D595" s="45"/>
       <c r="E595" s="3"/>
       <c r="F595" s="3"/>
       <c r="G595" s="3"/>
@@ -18462,7 +18471,7 @@
       <c r="A596" s="1"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
-      <c r="D596" s="46"/>
+      <c r="D596" s="45"/>
       <c r="E596" s="3"/>
       <c r="F596" s="3"/>
       <c r="G596" s="3"/>
@@ -18490,7 +18499,7 @@
       <c r="A597" s="1"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
-      <c r="D597" s="46"/>
+      <c r="D597" s="45"/>
       <c r="E597" s="3"/>
       <c r="F597" s="3"/>
       <c r="G597" s="3"/>
@@ -18518,7 +18527,7 @@
       <c r="A598" s="1"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
-      <c r="D598" s="46"/>
+      <c r="D598" s="45"/>
       <c r="E598" s="3"/>
       <c r="F598" s="3"/>
       <c r="G598" s="3"/>
@@ -18546,7 +18555,7 @@
       <c r="A599" s="1"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
-      <c r="D599" s="46"/>
+      <c r="D599" s="45"/>
       <c r="E599" s="3"/>
       <c r="F599" s="3"/>
       <c r="G599" s="3"/>
@@ -18574,7 +18583,7 @@
       <c r="A600" s="1"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
-      <c r="D600" s="46"/>
+      <c r="D600" s="45"/>
       <c r="E600" s="3"/>
       <c r="F600" s="3"/>
       <c r="G600" s="3"/>
@@ -18602,7 +18611,7 @@
       <c r="A601" s="1"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
-      <c r="D601" s="46"/>
+      <c r="D601" s="45"/>
       <c r="E601" s="3"/>
       <c r="F601" s="3"/>
       <c r="G601" s="3"/>
@@ -18630,7 +18639,7 @@
       <c r="A602" s="1"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
-      <c r="D602" s="46"/>
+      <c r="D602" s="45"/>
       <c r="E602" s="3"/>
       <c r="F602" s="3"/>
       <c r="G602" s="3"/>
@@ -18658,7 +18667,7 @@
       <c r="A603" s="1"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
-      <c r="D603" s="46"/>
+      <c r="D603" s="45"/>
       <c r="E603" s="3"/>
       <c r="F603" s="3"/>
       <c r="G603" s="3"/>
@@ -18686,7 +18695,7 @@
       <c r="A604" s="1"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
-      <c r="D604" s="46"/>
+      <c r="D604" s="45"/>
       <c r="E604" s="3"/>
       <c r="F604" s="3"/>
       <c r="G604" s="3"/>
@@ -18714,7 +18723,7 @@
       <c r="A605" s="1"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
-      <c r="D605" s="46"/>
+      <c r="D605" s="45"/>
       <c r="E605" s="3"/>
       <c r="F605" s="3"/>
       <c r="G605" s="3"/>
@@ -18742,7 +18751,7 @@
       <c r="A606" s="1"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
-      <c r="D606" s="46"/>
+      <c r="D606" s="45"/>
       <c r="E606" s="3"/>
       <c r="F606" s="3"/>
       <c r="G606" s="3"/>
@@ -18770,7 +18779,7 @@
       <c r="A607" s="1"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
-      <c r="D607" s="46"/>
+      <c r="D607" s="45"/>
       <c r="E607" s="3"/>
       <c r="F607" s="3"/>
       <c r="G607" s="3"/>
@@ -18798,7 +18807,7 @@
       <c r="A608" s="1"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
-      <c r="D608" s="46"/>
+      <c r="D608" s="45"/>
       <c r="E608" s="3"/>
       <c r="F608" s="3"/>
       <c r="G608" s="3"/>
@@ -18826,7 +18835,7 @@
       <c r="A609" s="1"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
-      <c r="D609" s="46"/>
+      <c r="D609" s="45"/>
       <c r="E609" s="3"/>
       <c r="F609" s="3"/>
       <c r="G609" s="3"/>
@@ -18854,7 +18863,7 @@
       <c r="A610" s="1"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
-      <c r="D610" s="46"/>
+      <c r="D610" s="45"/>
       <c r="E610" s="3"/>
       <c r="F610" s="3"/>
       <c r="G610" s="3"/>
@@ -18882,7 +18891,7 @@
       <c r="A611" s="1"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
-      <c r="D611" s="46"/>
+      <c r="D611" s="45"/>
       <c r="E611" s="3"/>
       <c r="F611" s="3"/>
       <c r="G611" s="3"/>
@@ -18910,7 +18919,7 @@
       <c r="A612" s="1"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
-      <c r="D612" s="46"/>
+      <c r="D612" s="45"/>
       <c r="E612" s="3"/>
       <c r="F612" s="3"/>
       <c r="G612" s="3"/>
@@ -18938,7 +18947,7 @@
       <c r="A613" s="1"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
-      <c r="D613" s="46"/>
+      <c r="D613" s="45"/>
       <c r="E613" s="3"/>
       <c r="F613" s="3"/>
       <c r="G613" s="3"/>
@@ -18966,7 +18975,7 @@
       <c r="A614" s="1"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
-      <c r="D614" s="46"/>
+      <c r="D614" s="45"/>
       <c r="E614" s="3"/>
       <c r="F614" s="3"/>
       <c r="G614" s="3"/>
@@ -18994,7 +19003,7 @@
       <c r="A615" s="1"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
-      <c r="D615" s="46"/>
+      <c r="D615" s="45"/>
       <c r="E615" s="3"/>
       <c r="F615" s="3"/>
       <c r="G615" s="3"/>
@@ -19022,7 +19031,7 @@
       <c r="A616" s="1"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
-      <c r="D616" s="46"/>
+      <c r="D616" s="45"/>
       <c r="E616" s="3"/>
       <c r="F616" s="3"/>
       <c r="G616" s="3"/>
@@ -19050,7 +19059,7 @@
       <c r="A617" s="1"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
-      <c r="D617" s="46"/>
+      <c r="D617" s="45"/>
       <c r="E617" s="3"/>
       <c r="F617" s="3"/>
       <c r="G617" s="3"/>
@@ -19078,7 +19087,7 @@
       <c r="A618" s="1"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
-      <c r="D618" s="46"/>
+      <c r="D618" s="45"/>
       <c r="E618" s="3"/>
       <c r="F618" s="3"/>
       <c r="G618" s="3"/>
@@ -19106,7 +19115,7 @@
       <c r="A619" s="1"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
-      <c r="D619" s="46"/>
+      <c r="D619" s="45"/>
       <c r="E619" s="3"/>
       <c r="F619" s="3"/>
       <c r="G619" s="3"/>
@@ -19134,7 +19143,7 @@
       <c r="A620" s="1"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
-      <c r="D620" s="46"/>
+      <c r="D620" s="45"/>
       <c r="E620" s="3"/>
       <c r="F620" s="3"/>
       <c r="G620" s="3"/>
@@ -19162,7 +19171,7 @@
       <c r="A621" s="1"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
-      <c r="D621" s="46"/>
+      <c r="D621" s="45"/>
       <c r="E621" s="3"/>
       <c r="F621" s="3"/>
       <c r="G621" s="3"/>
@@ -19190,7 +19199,7 @@
       <c r="A622" s="1"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
-      <c r="D622" s="46"/>
+      <c r="D622" s="45"/>
       <c r="E622" s="3"/>
       <c r="F622" s="3"/>
       <c r="G622" s="3"/>
@@ -19218,7 +19227,7 @@
       <c r="A623" s="1"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
-      <c r="D623" s="46"/>
+      <c r="D623" s="45"/>
       <c r="E623" s="3"/>
       <c r="F623" s="3"/>
       <c r="G623" s="3"/>
@@ -19246,7 +19255,7 @@
       <c r="A624" s="1"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
-      <c r="D624" s="46"/>
+      <c r="D624" s="45"/>
       <c r="E624" s="3"/>
       <c r="F624" s="3"/>
       <c r="G624" s="3"/>
@@ -19274,7 +19283,7 @@
       <c r="A625" s="1"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
-      <c r="D625" s="46"/>
+      <c r="D625" s="45"/>
       <c r="E625" s="3"/>
       <c r="F625" s="3"/>
       <c r="G625" s="3"/>
@@ -19302,7 +19311,7 @@
       <c r="A626" s="1"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
-      <c r="D626" s="46"/>
+      <c r="D626" s="45"/>
       <c r="E626" s="3"/>
       <c r="F626" s="3"/>
       <c r="G626" s="3"/>
@@ -19330,7 +19339,7 @@
       <c r="A627" s="1"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
-      <c r="D627" s="46"/>
+      <c r="D627" s="45"/>
       <c r="E627" s="3"/>
       <c r="F627" s="3"/>
       <c r="G627" s="3"/>
@@ -19358,7 +19367,7 @@
       <c r="A628" s="1"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
-      <c r="D628" s="46"/>
+      <c r="D628" s="45"/>
       <c r="E628" s="3"/>
       <c r="F628" s="3"/>
       <c r="G628" s="3"/>
@@ -19386,7 +19395,7 @@
       <c r="A629" s="1"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
-      <c r="D629" s="46"/>
+      <c r="D629" s="45"/>
       <c r="E629" s="3"/>
       <c r="F629" s="3"/>
       <c r="G629" s="3"/>
@@ -19414,7 +19423,7 @@
       <c r="A630" s="1"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
-      <c r="D630" s="46"/>
+      <c r="D630" s="45"/>
       <c r="E630" s="3"/>
       <c r="F630" s="3"/>
       <c r="G630" s="3"/>
@@ -19442,7 +19451,7 @@
       <c r="A631" s="1"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
-      <c r="D631" s="46"/>
+      <c r="D631" s="45"/>
       <c r="E631" s="3"/>
       <c r="F631" s="3"/>
       <c r="G631" s="3"/>
@@ -19470,7 +19479,7 @@
       <c r="A632" s="1"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
-      <c r="D632" s="46"/>
+      <c r="D632" s="45"/>
       <c r="E632" s="3"/>
       <c r="F632" s="3"/>
       <c r="G632" s="3"/>
@@ -19498,7 +19507,7 @@
       <c r="A633" s="1"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
-      <c r="D633" s="46"/>
+      <c r="D633" s="45"/>
       <c r="E633" s="3"/>
       <c r="F633" s="3"/>
       <c r="G633" s="3"/>
@@ -19526,7 +19535,7 @@
       <c r="A634" s="1"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
-      <c r="D634" s="46"/>
+      <c r="D634" s="45"/>
       <c r="E634" s="3"/>
       <c r="F634" s="3"/>
       <c r="G634" s="3"/>
@@ -19554,7 +19563,7 @@
       <c r="A635" s="1"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
-      <c r="D635" s="46"/>
+      <c r="D635" s="45"/>
       <c r="E635" s="3"/>
       <c r="F635" s="3"/>
       <c r="G635" s="3"/>
@@ -19582,7 +19591,7 @@
       <c r="A636" s="1"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
-      <c r="D636" s="46"/>
+      <c r="D636" s="45"/>
       <c r="E636" s="3"/>
       <c r="F636" s="3"/>
       <c r="G636" s="3"/>
@@ -19610,7 +19619,7 @@
       <c r="A637" s="1"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
-      <c r="D637" s="46"/>
+      <c r="D637" s="45"/>
       <c r="E637" s="3"/>
       <c r="F637" s="3"/>
       <c r="G637" s="3"/>
@@ -19638,7 +19647,7 @@
       <c r="A638" s="1"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
-      <c r="D638" s="46"/>
+      <c r="D638" s="45"/>
       <c r="E638" s="3"/>
       <c r="F638" s="3"/>
       <c r="G638" s="3"/>
@@ -19666,7 +19675,7 @@
       <c r="A639" s="1"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
-      <c r="D639" s="46"/>
+      <c r="D639" s="45"/>
       <c r="E639" s="3"/>
       <c r="F639" s="3"/>
       <c r="G639" s="3"/>
@@ -19694,7 +19703,7 @@
       <c r="A640" s="1"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
-      <c r="D640" s="46"/>
+      <c r="D640" s="45"/>
       <c r="E640" s="3"/>
       <c r="F640" s="3"/>
       <c r="G640" s="3"/>
@@ -19722,7 +19731,7 @@
       <c r="A641" s="1"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
-      <c r="D641" s="46"/>
+      <c r="D641" s="45"/>
       <c r="E641" s="3"/>
       <c r="F641" s="3"/>
       <c r="G641" s="3"/>
@@ -19750,7 +19759,7 @@
       <c r="A642" s="1"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
-      <c r="D642" s="46"/>
+      <c r="D642" s="45"/>
       <c r="E642" s="3"/>
       <c r="F642" s="3"/>
       <c r="G642" s="3"/>
@@ -19778,7 +19787,7 @@
       <c r="A643" s="1"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
-      <c r="D643" s="46"/>
+      <c r="D643" s="45"/>
       <c r="E643" s="3"/>
       <c r="F643" s="3"/>
       <c r="G643" s="3"/>
@@ -19806,7 +19815,7 @@
       <c r="A644" s="1"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
-      <c r="D644" s="46"/>
+      <c r="D644" s="45"/>
       <c r="E644" s="3"/>
       <c r="F644" s="3"/>
       <c r="G644" s="3"/>
@@ -19834,7 +19843,7 @@
       <c r="A645" s="1"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
-      <c r="D645" s="46"/>
+      <c r="D645" s="45"/>
       <c r="E645" s="3"/>
       <c r="F645" s="3"/>
       <c r="G645" s="3"/>
@@ -19862,7 +19871,7 @@
       <c r="A646" s="1"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
-      <c r="D646" s="46"/>
+      <c r="D646" s="45"/>
       <c r="E646" s="3"/>
       <c r="F646" s="3"/>
       <c r="G646" s="3"/>
@@ -19890,7 +19899,7 @@
       <c r="A647" s="1"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
-      <c r="D647" s="46"/>
+      <c r="D647" s="45"/>
       <c r="E647" s="3"/>
       <c r="F647" s="3"/>
       <c r="G647" s="3"/>
@@ -19918,7 +19927,7 @@
       <c r="A648" s="1"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
-      <c r="D648" s="46"/>
+      <c r="D648" s="45"/>
       <c r="E648" s="3"/>
       <c r="F648" s="3"/>
       <c r="G648" s="3"/>
@@ -19946,7 +19955,7 @@
       <c r="A649" s="1"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
-      <c r="D649" s="46"/>
+      <c r="D649" s="45"/>
       <c r="E649" s="3"/>
       <c r="F649" s="3"/>
       <c r="G649" s="3"/>
@@ -19974,7 +19983,7 @@
       <c r="A650" s="1"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
-      <c r="D650" s="46"/>
+      <c r="D650" s="45"/>
       <c r="E650" s="3"/>
       <c r="F650" s="3"/>
       <c r="G650" s="3"/>
@@ -20002,7 +20011,7 @@
       <c r="A651" s="1"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
-      <c r="D651" s="46"/>
+      <c r="D651" s="45"/>
       <c r="E651" s="3"/>
       <c r="F651" s="3"/>
       <c r="G651" s="3"/>
@@ -20030,7 +20039,7 @@
       <c r="A652" s="1"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
-      <c r="D652" s="46"/>
+      <c r="D652" s="45"/>
       <c r="E652" s="3"/>
       <c r="F652" s="3"/>
       <c r="G652" s="3"/>
@@ -20058,7 +20067,7 @@
       <c r="A653" s="1"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
-      <c r="D653" s="46"/>
+      <c r="D653" s="45"/>
       <c r="E653" s="3"/>
       <c r="F653" s="3"/>
       <c r="G653" s="3"/>
@@ -20086,7 +20095,7 @@
       <c r="A654" s="1"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
-      <c r="D654" s="46"/>
+      <c r="D654" s="45"/>
       <c r="E654" s="3"/>
       <c r="F654" s="3"/>
       <c r="G654" s="3"/>
@@ -20114,7 +20123,7 @@
       <c r="A655" s="1"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
-      <c r="D655" s="46"/>
+      <c r="D655" s="45"/>
       <c r="E655" s="3"/>
       <c r="F655" s="3"/>
       <c r="G655" s="3"/>
@@ -20142,7 +20151,7 @@
       <c r="A656" s="1"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
-      <c r="D656" s="46"/>
+      <c r="D656" s="45"/>
       <c r="E656" s="3"/>
       <c r="F656" s="3"/>
       <c r="G656" s="3"/>
@@ -20170,7 +20179,7 @@
       <c r="A657" s="1"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
-      <c r="D657" s="46"/>
+      <c r="D657" s="45"/>
       <c r="E657" s="3"/>
       <c r="F657" s="3"/>
       <c r="G657" s="3"/>
@@ -20198,7 +20207,7 @@
       <c r="A658" s="1"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
-      <c r="D658" s="46"/>
+      <c r="D658" s="45"/>
       <c r="E658" s="3"/>
       <c r="F658" s="3"/>
       <c r="G658" s="3"/>
@@ -20226,7 +20235,7 @@
       <c r="A659" s="1"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
-      <c r="D659" s="46"/>
+      <c r="D659" s="45"/>
       <c r="E659" s="3"/>
       <c r="F659" s="3"/>
       <c r="G659" s="3"/>
@@ -20254,7 +20263,7 @@
       <c r="A660" s="1"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
-      <c r="D660" s="46"/>
+      <c r="D660" s="45"/>
       <c r="E660" s="3"/>
       <c r="F660" s="3"/>
       <c r="G660" s="3"/>
@@ -20282,7 +20291,7 @@
       <c r="A661" s="1"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
-      <c r="D661" s="46"/>
+      <c r="D661" s="45"/>
       <c r="E661" s="3"/>
       <c r="F661" s="3"/>
       <c r="G661" s="3"/>
@@ -20310,7 +20319,7 @@
       <c r="A662" s="1"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
-      <c r="D662" s="46"/>
+      <c r="D662" s="45"/>
       <c r="E662" s="3"/>
       <c r="F662" s="3"/>
       <c r="G662" s="3"/>
@@ -20338,7 +20347,7 @@
       <c r="A663" s="1"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
-      <c r="D663" s="46"/>
+      <c r="D663" s="45"/>
       <c r="E663" s="3"/>
       <c r="F663" s="3"/>
       <c r="G663" s="3"/>
@@ -20366,7 +20375,7 @@
       <c r="A664" s="1"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
-      <c r="D664" s="46"/>
+      <c r="D664" s="45"/>
       <c r="E664" s="3"/>
       <c r="F664" s="3"/>
       <c r="G664" s="3"/>
@@ -20394,7 +20403,7 @@
       <c r="A665" s="1"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
-      <c r="D665" s="46"/>
+      <c r="D665" s="45"/>
       <c r="E665" s="3"/>
       <c r="F665" s="3"/>
       <c r="G665" s="3"/>
@@ -20422,7 +20431,7 @@
       <c r="A666" s="1"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
-      <c r="D666" s="46"/>
+      <c r="D666" s="45"/>
       <c r="E666" s="3"/>
       <c r="F666" s="3"/>
       <c r="G666" s="3"/>
@@ -20450,7 +20459,7 @@
       <c r="A667" s="1"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
-      <c r="D667" s="46"/>
+      <c r="D667" s="45"/>
       <c r="E667" s="3"/>
       <c r="F667" s="3"/>
       <c r="G667" s="3"/>
@@ -20478,7 +20487,7 @@
       <c r="A668" s="1"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
-      <c r="D668" s="46"/>
+      <c r="D668" s="45"/>
       <c r="E668" s="3"/>
       <c r="F668" s="3"/>
       <c r="G668" s="3"/>
@@ -20506,7 +20515,7 @@
       <c r="A669" s="1"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
-      <c r="D669" s="46"/>
+      <c r="D669" s="45"/>
       <c r="E669" s="3"/>
       <c r="F669" s="3"/>
       <c r="G669" s="3"/>
@@ -20534,7 +20543,7 @@
       <c r="A670" s="1"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
-      <c r="D670" s="46"/>
+      <c r="D670" s="45"/>
       <c r="E670" s="3"/>
       <c r="F670" s="3"/>
       <c r="G670" s="3"/>
@@ -20562,7 +20571,7 @@
       <c r="A671" s="1"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
-      <c r="D671" s="46"/>
+      <c r="D671" s="45"/>
       <c r="E671" s="3"/>
       <c r="F671" s="3"/>
       <c r="G671" s="3"/>
@@ -20590,7 +20599,7 @@
       <c r="A672" s="1"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
-      <c r="D672" s="46"/>
+      <c r="D672" s="45"/>
       <c r="E672" s="3"/>
       <c r="F672" s="3"/>
       <c r="G672" s="3"/>
@@ -20618,7 +20627,7 @@
       <c r="A673" s="1"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
-      <c r="D673" s="46"/>
+      <c r="D673" s="45"/>
       <c r="E673" s="3"/>
       <c r="F673" s="3"/>
       <c r="G673" s="3"/>
@@ -20646,7 +20655,7 @@
       <c r="A674" s="1"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
-      <c r="D674" s="46"/>
+      <c r="D674" s="45"/>
       <c r="E674" s="3"/>
       <c r="F674" s="3"/>
       <c r="G674" s="3"/>
@@ -20674,7 +20683,7 @@
       <c r="A675" s="1"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
-      <c r="D675" s="46"/>
+      <c r="D675" s="45"/>
       <c r="E675" s="3"/>
       <c r="F675" s="3"/>
       <c r="G675" s="3"/>
@@ -20702,7 +20711,7 @@
       <c r="A676" s="1"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
-      <c r="D676" s="46"/>
+      <c r="D676" s="45"/>
       <c r="E676" s="3"/>
       <c r="F676" s="3"/>
       <c r="G676" s="3"/>
@@ -20730,7 +20739,7 @@
       <c r="A677" s="1"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
-      <c r="D677" s="46"/>
+      <c r="D677" s="45"/>
       <c r="E677" s="3"/>
       <c r="F677" s="3"/>
       <c r="G677" s="3"/>
@@ -20758,7 +20767,7 @@
       <c r="A678" s="1"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
-      <c r="D678" s="46"/>
+      <c r="D678" s="45"/>
       <c r="E678" s="3"/>
       <c r="F678" s="3"/>
       <c r="G678" s="3"/>
@@ -20786,7 +20795,7 @@
       <c r="A679" s="1"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
-      <c r="D679" s="46"/>
+      <c r="D679" s="45"/>
       <c r="E679" s="3"/>
       <c r="F679" s="3"/>
       <c r="G679" s="3"/>
@@ -20814,7 +20823,7 @@
       <c r="A680" s="1"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
-      <c r="D680" s="46"/>
+      <c r="D680" s="45"/>
       <c r="E680" s="3"/>
       <c r="F680" s="3"/>
       <c r="G680" s="3"/>
@@ -20842,7 +20851,7 @@
       <c r="A681" s="1"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
-      <c r="D681" s="46"/>
+      <c r="D681" s="45"/>
       <c r="E681" s="3"/>
       <c r="F681" s="3"/>
       <c r="G681" s="3"/>
@@ -20870,7 +20879,7 @@
       <c r="A682" s="1"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
-      <c r="D682" s="46"/>
+      <c r="D682" s="45"/>
       <c r="E682" s="3"/>
       <c r="F682" s="3"/>
       <c r="G682" s="3"/>
@@ -20898,7 +20907,7 @@
       <c r="A683" s="1"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
-      <c r="D683" s="46"/>
+      <c r="D683" s="45"/>
       <c r="E683" s="3"/>
       <c r="F683" s="3"/>
       <c r="G683" s="3"/>
@@ -20926,7 +20935,7 @@
       <c r="A684" s="1"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
-      <c r="D684" s="46"/>
+      <c r="D684" s="45"/>
       <c r="E684" s="3"/>
       <c r="F684" s="3"/>
       <c r="G684" s="3"/>
@@ -20954,7 +20963,7 @@
       <c r="A685" s="1"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
-      <c r="D685" s="46"/>
+      <c r="D685" s="45"/>
       <c r="E685" s="3"/>
       <c r="F685" s="3"/>
       <c r="G685" s="3"/>
@@ -20982,7 +20991,7 @@
       <c r="A686" s="1"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
-      <c r="D686" s="46"/>
+      <c r="D686" s="45"/>
       <c r="E686" s="3"/>
       <c r="F686" s="3"/>
       <c r="G686" s="3"/>
@@ -21010,7 +21019,7 @@
       <c r="A687" s="1"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
-      <c r="D687" s="46"/>
+      <c r="D687" s="45"/>
       <c r="E687" s="3"/>
       <c r="F687" s="3"/>
       <c r="G687" s="3"/>
@@ -21038,7 +21047,7 @@
       <c r="A688" s="1"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
-      <c r="D688" s="46"/>
+      <c r="D688" s="45"/>
       <c r="E688" s="3"/>
       <c r="F688" s="3"/>
       <c r="G688" s="3"/>
@@ -21066,7 +21075,7 @@
       <c r="A689" s="1"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
-      <c r="D689" s="46"/>
+      <c r="D689" s="45"/>
       <c r="E689" s="3"/>
       <c r="F689" s="3"/>
       <c r="G689" s="3"/>
@@ -21094,7 +21103,7 @@
       <c r="A690" s="1"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
-      <c r="D690" s="46"/>
+      <c r="D690" s="45"/>
       <c r="E690" s="3"/>
       <c r="F690" s="3"/>
       <c r="G690" s="3"/>
@@ -21122,7 +21131,7 @@
       <c r="A691" s="1"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
-      <c r="D691" s="46"/>
+      <c r="D691" s="45"/>
       <c r="E691" s="3"/>
       <c r="F691" s="3"/>
       <c r="G691" s="3"/>
@@ -21150,7 +21159,7 @@
       <c r="A692" s="1"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
-      <c r="D692" s="46"/>
+      <c r="D692" s="45"/>
       <c r="E692" s="3"/>
       <c r="F692" s="3"/>
       <c r="G692" s="3"/>
@@ -21178,7 +21187,7 @@
       <c r="A693" s="1"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
-      <c r="D693" s="46"/>
+      <c r="D693" s="45"/>
       <c r="E693" s="3"/>
       <c r="F693" s="3"/>
       <c r="G693" s="3"/>
@@ -21206,7 +21215,7 @@
       <c r="A694" s="1"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
-      <c r="D694" s="46"/>
+      <c r="D694" s="45"/>
       <c r="E694" s="3"/>
       <c r="F694" s="3"/>
       <c r="G694" s="3"/>
@@ -21234,7 +21243,7 @@
       <c r="A695" s="1"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
-      <c r="D695" s="46"/>
+      <c r="D695" s="45"/>
       <c r="E695" s="3"/>
       <c r="F695" s="3"/>
       <c r="G695" s="3"/>
@@ -21262,7 +21271,7 @@
       <c r="A696" s="1"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
-      <c r="D696" s="46"/>
+      <c r="D696" s="45"/>
       <c r="E696" s="3"/>
       <c r="F696" s="3"/>
       <c r="G696" s="3"/>
@@ -21290,7 +21299,7 @@
       <c r="A697" s="1"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
-      <c r="D697" s="46"/>
+      <c r="D697" s="45"/>
       <c r="E697" s="3"/>
       <c r="F697" s="3"/>
       <c r="G697" s="3"/>
@@ -21318,7 +21327,7 @@
       <c r="A698" s="1"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
-      <c r="D698" s="46"/>
+      <c r="D698" s="45"/>
       <c r="E698" s="3"/>
       <c r="F698" s="3"/>
       <c r="G698" s="3"/>
@@ -21346,7 +21355,7 @@
       <c r="A699" s="1"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
-      <c r="D699" s="46"/>
+      <c r="D699" s="45"/>
       <c r="E699" s="3"/>
       <c r="F699" s="3"/>
       <c r="G699" s="3"/>
@@ -21374,7 +21383,7 @@
       <c r="A700" s="1"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
-      <c r="D700" s="46"/>
+      <c r="D700" s="45"/>
       <c r="E700" s="3"/>
       <c r="F700" s="3"/>
       <c r="G700" s="3"/>
@@ -21402,7 +21411,7 @@
       <c r="A701" s="1"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
-      <c r="D701" s="46"/>
+      <c r="D701" s="45"/>
       <c r="E701" s="3"/>
       <c r="F701" s="3"/>
       <c r="G701" s="3"/>
@@ -21430,7 +21439,7 @@
       <c r="A702" s="1"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
-      <c r="D702" s="46"/>
+      <c r="D702" s="45"/>
       <c r="E702" s="3"/>
       <c r="F702" s="3"/>
       <c r="G702" s="3"/>
@@ -21458,7 +21467,7 @@
       <c r="A703" s="1"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
-      <c r="D703" s="46"/>
+      <c r="D703" s="45"/>
       <c r="E703" s="3"/>
       <c r="F703" s="3"/>
       <c r="G703" s="3"/>
@@ -21486,7 +21495,7 @@
       <c r="A704" s="1"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
-      <c r="D704" s="46"/>
+      <c r="D704" s="45"/>
       <c r="E704" s="3"/>
       <c r="F704" s="3"/>
       <c r="G704" s="3"/>
@@ -21514,7 +21523,7 @@
       <c r="A705" s="1"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
-      <c r="D705" s="46"/>
+      <c r="D705" s="45"/>
       <c r="E705" s="3"/>
       <c r="F705" s="3"/>
       <c r="G705" s="3"/>
@@ -21542,7 +21551,7 @@
       <c r="A706" s="1"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
-      <c r="D706" s="46"/>
+      <c r="D706" s="45"/>
       <c r="E706" s="3"/>
       <c r="F706" s="3"/>
       <c r="G706" s="3"/>
@@ -21570,7 +21579,7 @@
       <c r="A707" s="1"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
-      <c r="D707" s="46"/>
+      <c r="D707" s="45"/>
       <c r="E707" s="3"/>
       <c r="F707" s="3"/>
       <c r="G707" s="3"/>
@@ -21598,7 +21607,7 @@
       <c r="A708" s="1"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
-      <c r="D708" s="46"/>
+      <c r="D708" s="45"/>
       <c r="E708" s="3"/>
       <c r="F708" s="3"/>
       <c r="G708" s="3"/>
@@ -21626,7 +21635,7 @@
       <c r="A709" s="1"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
-      <c r="D709" s="46"/>
+      <c r="D709" s="45"/>
       <c r="E709" s="3"/>
       <c r="F709" s="3"/>
       <c r="G709" s="3"/>
@@ -21654,7 +21663,7 @@
       <c r="A710" s="1"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
-      <c r="D710" s="46"/>
+      <c r="D710" s="45"/>
       <c r="E710" s="3"/>
       <c r="F710" s="3"/>
       <c r="G710" s="3"/>
@@ -21682,7 +21691,7 @@
       <c r="A711" s="1"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
-      <c r="D711" s="46"/>
+      <c r="D711" s="45"/>
       <c r="E711" s="3"/>
       <c r="F711" s="3"/>
       <c r="G711" s="3"/>
@@ -21710,7 +21719,7 @@
       <c r="A712" s="1"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
-      <c r="D712" s="46"/>
+      <c r="D712" s="45"/>
       <c r="E712" s="3"/>
       <c r="F712" s="3"/>
       <c r="G712" s="3"/>
@@ -21738,7 +21747,7 @@
       <c r="A713" s="1"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
-      <c r="D713" s="46"/>
+      <c r="D713" s="45"/>
       <c r="E713" s="3"/>
       <c r="F713" s="3"/>
       <c r="G713" s="3"/>
@@ -21766,7 +21775,7 @@
       <c r="A714" s="1"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
-      <c r="D714" s="46"/>
+      <c r="D714" s="45"/>
       <c r="E714" s="3"/>
       <c r="F714" s="3"/>
       <c r="G714" s="3"/>
@@ -21794,7 +21803,7 @@
       <c r="A715" s="1"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
-      <c r="D715" s="46"/>
+      <c r="D715" s="45"/>
       <c r="E715" s="3"/>
       <c r="F715" s="3"/>
       <c r="G715" s="3"/>
@@ -21822,7 +21831,7 @@
       <c r="A716" s="1"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
-      <c r="D716" s="46"/>
+      <c r="D716" s="45"/>
       <c r="E716" s="3"/>
       <c r="F716" s="3"/>
       <c r="G716" s="3"/>
@@ -21850,7 +21859,7 @@
       <c r="A717" s="1"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
-      <c r="D717" s="46"/>
+      <c r="D717" s="45"/>
       <c r="E717" s="3"/>
       <c r="F717" s="3"/>
       <c r="G717" s="3"/>
@@ -21878,7 +21887,7 @@
       <c r="A718" s="1"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
-      <c r="D718" s="46"/>
+      <c r="D718" s="45"/>
       <c r="E718" s="3"/>
       <c r="F718" s="3"/>
       <c r="G718" s="3"/>
@@ -21906,7 +21915,7 @@
       <c r="A719" s="1"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
-      <c r="D719" s="46"/>
+      <c r="D719" s="45"/>
       <c r="E719" s="3"/>
       <c r="F719" s="3"/>
       <c r="G719" s="3"/>
@@ -21934,7 +21943,7 @@
       <c r="A720" s="1"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
-      <c r="D720" s="46"/>
+      <c r="D720" s="45"/>
       <c r="E720" s="3"/>
       <c r="F720" s="3"/>
       <c r="G720" s="3"/>
@@ -21962,7 +21971,7 @@
       <c r="A721" s="1"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
-      <c r="D721" s="46"/>
+      <c r="D721" s="45"/>
       <c r="E721" s="3"/>
       <c r="F721" s="3"/>
       <c r="G721" s="3"/>
@@ -21990,7 +21999,7 @@
       <c r="A722" s="1"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
-      <c r="D722" s="46"/>
+      <c r="D722" s="45"/>
       <c r="E722" s="3"/>
       <c r="F722" s="3"/>
       <c r="G722" s="3"/>
@@ -22018,7 +22027,7 @@
       <c r="A723" s="1"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
-      <c r="D723" s="46"/>
+      <c r="D723" s="45"/>
       <c r="E723" s="3"/>
       <c r="F723" s="3"/>
       <c r="G723" s="3"/>
@@ -22046,7 +22055,7 @@
       <c r="A724" s="1"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
-      <c r="D724" s="46"/>
+      <c r="D724" s="45"/>
       <c r="E724" s="3"/>
       <c r="F724" s="3"/>
       <c r="G724" s="3"/>
@@ -22074,7 +22083,7 @@
       <c r="A725" s="1"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
-      <c r="D725" s="46"/>
+      <c r="D725" s="45"/>
       <c r="E725" s="3"/>
       <c r="F725" s="3"/>
       <c r="G725" s="3"/>
@@ -22102,7 +22111,7 @@
       <c r="A726" s="1"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
-      <c r="D726" s="46"/>
+      <c r="D726" s="45"/>
       <c r="E726" s="3"/>
       <c r="F726" s="3"/>
       <c r="G726" s="3"/>
@@ -22130,7 +22139,7 @@
       <c r="A727" s="1"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
-      <c r="D727" s="46"/>
+      <c r="D727" s="45"/>
       <c r="E727" s="3"/>
       <c r="F727" s="3"/>
       <c r="G727" s="3"/>
@@ -22158,7 +22167,7 @@
       <c r="A728" s="1"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
-      <c r="D728" s="46"/>
+      <c r="D728" s="45"/>
       <c r="E728" s="3"/>
       <c r="F728" s="3"/>
       <c r="G728" s="3"/>
@@ -22186,7 +22195,7 @@
       <c r="A729" s="1"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
-      <c r="D729" s="46"/>
+      <c r="D729" s="45"/>
       <c r="E729" s="3"/>
       <c r="F729" s="3"/>
       <c r="G729" s="3"/>
@@ -22214,7 +22223,7 @@
       <c r="A730" s="1"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
-      <c r="D730" s="46"/>
+      <c r="D730" s="45"/>
       <c r="E730" s="3"/>
       <c r="F730" s="3"/>
       <c r="G730" s="3"/>
@@ -22242,7 +22251,7 @@
       <c r="A731" s="1"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
-      <c r="D731" s="46"/>
+      <c r="D731" s="45"/>
       <c r="E731" s="3"/>
       <c r="F731" s="3"/>
       <c r="G731" s="3"/>
@@ -22270,7 +22279,7 @@
       <c r="A732" s="1"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
-      <c r="D732" s="46"/>
+      <c r="D732" s="45"/>
       <c r="E732" s="3"/>
       <c r="F732" s="3"/>
       <c r="G732" s="3"/>
@@ -22298,7 +22307,7 @@
       <c r="A733" s="1"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
-      <c r="D733" s="46"/>
+      <c r="D733" s="45"/>
       <c r="E733" s="3"/>
       <c r="F733" s="3"/>
       <c r="G733" s="3"/>
@@ -22326,7 +22335,7 @@
       <c r="A734" s="1"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
-      <c r="D734" s="46"/>
+      <c r="D734" s="45"/>
       <c r="E734" s="3"/>
       <c r="F734" s="3"/>
       <c r="G734" s="3"/>
@@ -22354,7 +22363,7 @@
       <c r="A735" s="1"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
-      <c r="D735" s="46"/>
+      <c r="D735" s="45"/>
       <c r="E735" s="3"/>
       <c r="F735" s="3"/>
       <c r="G735" s="3"/>
@@ -22382,7 +22391,7 @@
       <c r="A736" s="1"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
-      <c r="D736" s="46"/>
+      <c r="D736" s="45"/>
       <c r="E736" s="3"/>
       <c r="F736" s="3"/>
       <c r="G736" s="3"/>
@@ -22410,7 +22419,7 @@
       <c r="A737" s="1"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
-      <c r="D737" s="46"/>
+      <c r="D737" s="45"/>
       <c r="E737" s="3"/>
       <c r="F737" s="3"/>
       <c r="G737" s="3"/>
@@ -22438,7 +22447,7 @@
       <c r="A738" s="1"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
-      <c r="D738" s="46"/>
+      <c r="D738" s="45"/>
       <c r="E738" s="3"/>
       <c r="F738" s="3"/>
       <c r="G738" s="3"/>
@@ -22466,7 +22475,7 @@
       <c r="A739" s="1"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
-      <c r="D739" s="46"/>
+      <c r="D739" s="45"/>
       <c r="E739" s="3"/>
       <c r="F739" s="3"/>
       <c r="G739" s="3"/>
@@ -22494,7 +22503,7 @@
       <c r="A740" s="1"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
-      <c r="D740" s="46"/>
+      <c r="D740" s="45"/>
       <c r="E740" s="3"/>
       <c r="F740" s="3"/>
       <c r="G740" s="3"/>
@@ -22522,7 +22531,7 @@
       <c r="A741" s="1"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
-      <c r="D741" s="46"/>
+      <c r="D741" s="45"/>
       <c r="E741" s="3"/>
       <c r="F741" s="3"/>
       <c r="G741" s="3"/>
@@ -22550,7 +22559,7 @@
       <c r="A742" s="1"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
-      <c r="D742" s="46"/>
+      <c r="D742" s="45"/>
       <c r="E742" s="3"/>
       <c r="F742" s="3"/>
       <c r="G742" s="3"/>
@@ -22578,7 +22587,7 @@
       <c r="A743" s="1"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
-      <c r="D743" s="46"/>
+      <c r="D743" s="45"/>
       <c r="E743" s="3"/>
       <c r="F743" s="3"/>
       <c r="G743" s="3"/>
@@ -22606,7 +22615,7 @@
       <c r="A744" s="1"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
-      <c r="D744" s="46"/>
+      <c r="D744" s="45"/>
       <c r="E744" s="3"/>
       <c r="F744" s="3"/>
       <c r="G744" s="3"/>
@@ -22634,7 +22643,7 @@
       <c r="A745" s="1"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
-      <c r="D745" s="46"/>
+      <c r="D745" s="45"/>
       <c r="E745" s="3"/>
       <c r="F745" s="3"/>
       <c r="G745" s="3"/>
@@ -22662,7 +22671,7 @@
       <c r="A746" s="1"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
-      <c r="D746" s="46"/>
+      <c r="D746" s="45"/>
       <c r="E746" s="3"/>
       <c r="F746" s="3"/>
       <c r="G746" s="3"/>
@@ -22690,7 +22699,7 @@
       <c r="A747" s="1"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
-      <c r="D747" s="46"/>
+      <c r="D747" s="45"/>
       <c r="E747" s="3"/>
       <c r="F747" s="3"/>
       <c r="G747" s="3"/>
@@ -22718,7 +22727,7 @@
       <c r="A748" s="1"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
-      <c r="D748" s="46"/>
+      <c r="D748" s="45"/>
       <c r="E748" s="3"/>
       <c r="F748" s="3"/>
       <c r="G748" s="3"/>
@@ -22746,7 +22755,7 @@
       <c r="A749" s="1"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
-      <c r="D749" s="46"/>
+      <c r="D749" s="45"/>
       <c r="E749" s="3"/>
       <c r="F749" s="3"/>
       <c r="G749" s="3"/>
@@ -22774,7 +22783,7 @@
       <c r="A750" s="1"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
-      <c r="D750" s="46"/>
+      <c r="D750" s="45"/>
       <c r="E750" s="3"/>
       <c r="F750" s="3"/>
       <c r="G750" s="3"/>
@@ -22802,7 +22811,7 @@
       <c r="A751" s="1"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
-      <c r="D751" s="46"/>
+      <c r="D751" s="45"/>
       <c r="E751" s="3"/>
       <c r="F751" s="3"/>
       <c r="G751" s="3"/>
@@ -22830,7 +22839,7 @@
       <c r="A752" s="1"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
-      <c r="D752" s="46"/>
+      <c r="D752" s="45"/>
       <c r="E752" s="3"/>
       <c r="F752" s="3"/>
       <c r="G752" s="3"/>
@@ -22858,7 +22867,7 @@
       <c r="A753" s="1"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
-      <c r="D753" s="46"/>
+      <c r="D753" s="45"/>
       <c r="E753" s="3"/>
       <c r="F753" s="3"/>
       <c r="G753" s="3"/>
@@ -22886,7 +22895,7 @@
       <c r="A754" s="1"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
-      <c r="D754" s="46"/>
+      <c r="D754" s="45"/>
       <c r="E754" s="3"/>
       <c r="F754" s="3"/>
       <c r="G754" s="3"/>
@@ -22914,7 +22923,7 @@
       <c r="A755" s="1"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
-      <c r="D755" s="46"/>
+      <c r="D755" s="45"/>
       <c r="E755" s="3"/>
       <c r="F755" s="3"/>
       <c r="G755" s="3"/>
@@ -22942,7 +22951,7 @@
       <c r="A756" s="1"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
-      <c r="D756" s="46"/>
+      <c r="D756" s="45"/>
       <c r="E756" s="3"/>
       <c r="F756" s="3"/>
       <c r="G756" s="3"/>
@@ -22970,7 +22979,7 @@
       <c r="A757" s="1"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
-      <c r="D757" s="46"/>
+      <c r="D757" s="45"/>
       <c r="E757" s="3"/>
       <c r="F757" s="3"/>
       <c r="G757" s="3"/>
@@ -22998,7 +23007,7 @@
       <c r="A758" s="1"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
-      <c r="D758" s="46"/>
+      <c r="D758" s="45"/>
       <c r="E758" s="3"/>
       <c r="F758" s="3"/>
       <c r="G758" s="3"/>
@@ -23026,7 +23035,7 @@
       <c r="A759" s="1"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
-      <c r="D759" s="46"/>
+      <c r="D759" s="45"/>
       <c r="E759" s="3"/>
       <c r="F759" s="3"/>
       <c r="G759" s="3"/>
@@ -23054,7 +23063,7 @@
       <c r="A760" s="1"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
-      <c r="D760" s="46"/>
+      <c r="D760" s="45"/>
       <c r="E760" s="3"/>
       <c r="F760" s="3"/>
       <c r="G760" s="3"/>
@@ -23082,7 +23091,7 @@
       <c r="A761" s="1"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
-      <c r="D761" s="46"/>
+      <c r="D761" s="45"/>
       <c r="E761" s="3"/>
       <c r="F761" s="3"/>
       <c r="G761" s="3"/>
@@ -23110,7 +23119,7 @@
       <c r="A762" s="1"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
-      <c r="D762" s="46"/>
+      <c r="D762" s="45"/>
       <c r="E762" s="3"/>
       <c r="F762" s="3"/>
       <c r="G762" s="3"/>
@@ -23138,7 +23147,7 @@
       <c r="A763" s="1"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
-      <c r="D763" s="46"/>
+      <c r="D763" s="45"/>
       <c r="E763" s="3"/>
       <c r="F763" s="3"/>
       <c r="G763" s="3"/>
@@ -23166,7 +23175,7 @@
       <c r="A764" s="1"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
-      <c r="D764" s="46"/>
+      <c r="D764" s="45"/>
       <c r="E764" s="3"/>
       <c r="F764" s="3"/>
       <c r="G764" s="3"/>
@@ -23194,7 +23203,7 @@
       <c r="A765" s="1"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
-      <c r="D765" s="46"/>
+      <c r="D765" s="45"/>
       <c r="E765" s="3"/>
       <c r="F765" s="3"/>
       <c r="G765" s="3"/>
@@ -23222,7 +23231,7 @@
       <c r="A766" s="1"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
-      <c r="D766" s="46"/>
+      <c r="D766" s="45"/>
       <c r="E766" s="3"/>
       <c r="F766" s="3"/>
       <c r="G766" s="3"/>
@@ -23250,7 +23259,7 @@
       <c r="A767" s="1"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
-      <c r="D767" s="46"/>
+      <c r="D767" s="45"/>
       <c r="E767" s="3"/>
       <c r="F767" s="3"/>
       <c r="G767" s="3"/>
@@ -23278,7 +23287,7 @@
       <c r="A768" s="1"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
-      <c r="D768" s="46"/>
+      <c r="D768" s="45"/>
       <c r="E768" s="3"/>
       <c r="F768" s="3"/>
       <c r="G768" s="3"/>
@@ -23306,7 +23315,7 @@
       <c r="A769" s="1"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
-      <c r="D769" s="46"/>
+      <c r="D769" s="45"/>
       <c r="E769" s="3"/>
       <c r="F769" s="3"/>
       <c r="G769" s="3"/>
@@ -23334,7 +23343,7 @@
       <c r="A770" s="1"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
-      <c r="D770" s="46"/>
+      <c r="D770" s="45"/>
       <c r="E770" s="3"/>
       <c r="F770" s="3"/>
       <c r="G770" s="3"/>
@@ -23362,7 +23371,7 @@
       <c r="A771" s="1"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
-      <c r="D771" s="46"/>
+      <c r="D771" s="45"/>
       <c r="E771" s="3"/>
       <c r="F771" s="3"/>
       <c r="G771" s="3"/>
@@ -23390,7 +23399,7 @@
       <c r="A772" s="1"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
-      <c r="D772" s="46"/>
+      <c r="D772" s="45"/>
       <c r="E772" s="3"/>
       <c r="F772" s="3"/>
       <c r="G772" s="3"/>
@@ -23418,7 +23427,7 @@
       <c r="A773" s="1"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
-      <c r="D773" s="46"/>
+      <c r="D773" s="45"/>
       <c r="E773" s="3"/>
       <c r="F773" s="3"/>
       <c r="G773" s="3"/>
@@ -23446,7 +23455,7 @@
       <c r="A774" s="1"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
-      <c r="D774" s="46"/>
+      <c r="D774" s="45"/>
       <c r="E774" s="3"/>
       <c r="F774" s="3"/>
       <c r="G774" s="3"/>
@@ -23474,7 +23483,7 @@
       <c r="A775" s="1"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
-      <c r="D775" s="46"/>
+      <c r="D775" s="45"/>
       <c r="E775" s="3"/>
       <c r="F775" s="3"/>
       <c r="G775" s="3"/>
@@ -23502,7 +23511,7 @@
       <c r="A776" s="1"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
-      <c r="D776" s="46"/>
+      <c r="D776" s="45"/>
       <c r="E776" s="3"/>
       <c r="F776" s="3"/>
       <c r="G776" s="3"/>
@@ -23530,7 +23539,7 @@
       <c r="A777" s="1"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
-      <c r="D777" s="46"/>
+      <c r="D777" s="45"/>
       <c r="E777" s="3"/>
       <c r="F777" s="3"/>
       <c r="G777" s="3"/>
@@ -23558,7 +23567,7 @@
       <c r="A778" s="1"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
-      <c r="D778" s="46"/>
+      <c r="D778" s="45"/>
       <c r="E778" s="3"/>
       <c r="F778" s="3"/>
       <c r="G778" s="3"/>
@@ -23586,7 +23595,7 @@
       <c r="A779" s="1"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
-      <c r="D779" s="46"/>
+      <c r="D779" s="45"/>
       <c r="E779" s="3"/>
       <c r="F779" s="3"/>
       <c r="G779" s="3"/>
@@ -23614,7 +23623,7 @@
       <c r="A780" s="1"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
-      <c r="D780" s="46"/>
+      <c r="D780" s="45"/>
       <c r="E780" s="3"/>
       <c r="F780" s="3"/>
       <c r="G780" s="3"/>
@@ -23642,7 +23651,7 @@
       <c r="A781" s="1"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
-      <c r="D781" s="46"/>
+      <c r="D781" s="45"/>
       <c r="E781" s="3"/>
       <c r="F781" s="3"/>
       <c r="G781" s="3"/>
@@ -23670,7 +23679,7 @@
       <c r="A782" s="1"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
-      <c r="D782" s="46"/>
+      <c r="D782" s="45"/>
       <c r="E782" s="3"/>
       <c r="F782" s="3"/>
       <c r="G782" s="3"/>
@@ -23698,7 +23707,7 @@
       <c r="A783" s="1"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
-      <c r="D783" s="46"/>
+      <c r="D783" s="45"/>
       <c r="E783" s="3"/>
       <c r="F783" s="3"/>
       <c r="G783" s="3"/>
@@ -23726,7 +23735,7 @@
       <c r="A784" s="1"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
-      <c r="D784" s="46"/>
+      <c r="D784" s="45"/>
       <c r="E784" s="3"/>
       <c r="F784" s="3"/>
       <c r="G784" s="3"/>
@@ -23754,7 +23763,7 @@
       <c r="A785" s="1"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
-      <c r="D785" s="46"/>
+      <c r="D785" s="45"/>
       <c r="E785" s="3"/>
       <c r="F785" s="3"/>
       <c r="G785" s="3"/>
@@ -23782,7 +23791,7 @@
       <c r="A786" s="1"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
-      <c r="D786" s="46"/>
+      <c r="D786" s="45"/>
       <c r="E786" s="3"/>
       <c r="F786" s="3"/>
       <c r="G786" s="3"/>
@@ -23810,7 +23819,7 @@
       <c r="A787" s="1"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
-      <c r="D787" s="46"/>
+      <c r="D787" s="45"/>
       <c r="E787" s="3"/>
       <c r="F787" s="3"/>
       <c r="G787" s="3"/>
@@ -23838,7 +23847,7 @@
       <c r="A788" s="1"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
-      <c r="D788" s="46"/>
+      <c r="D788" s="45"/>
       <c r="E788" s="3"/>
       <c r="F788" s="3"/>
       <c r="G788" s="3"/>
@@ -23866,7 +23875,7 @@
       <c r="A789" s="1"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
-      <c r="D789" s="46"/>
+      <c r="D789" s="45"/>
       <c r="E789" s="3"/>
       <c r="F789" s="3"/>
       <c r="G789" s="3"/>
@@ -23894,7 +23903,7 @@
       <c r="A790" s="1"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
-      <c r="D790" s="46"/>
+      <c r="D790" s="45"/>
       <c r="E790" s="3"/>
       <c r="F790" s="3"/>
       <c r="G790" s="3"/>
@@ -23922,7 +23931,7 @@
       <c r="A791" s="1"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
-      <c r="D791" s="46"/>
+      <c r="D791" s="45"/>
       <c r="E791" s="3"/>
       <c r="F791" s="3"/>
       <c r="G791" s="3"/>
@@ -23950,7 +23959,7 @@
       <c r="A792" s="1"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
-      <c r="D792" s="46"/>
+      <c r="D792" s="45"/>
       <c r="E792" s="3"/>
       <c r="F792" s="3"/>
       <c r="G792" s="3"/>
@@ -23978,7 +23987,7 @@
       <c r="A793" s="1"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
-      <c r="D793" s="46"/>
+      <c r="D793" s="45"/>
       <c r="E793" s="3"/>
       <c r="F793" s="3"/>
       <c r="G793" s="3"/>
@@ -24006,7 +24015,7 @@
       <c r="A794" s="1"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
-      <c r="D794" s="46"/>
+      <c r="D794" s="45"/>
       <c r="E794" s="3"/>
       <c r="F794" s="3"/>
       <c r="G794" s="3"/>
@@ -24034,7 +24043,7 @@
       <c r="A795" s="1"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
-      <c r="D795" s="46"/>
+      <c r="D795" s="45"/>
       <c r="E795" s="3"/>
       <c r="F795" s="3"/>
       <c r="G795" s="3"/>
@@ -24062,7 +24071,7 @@
       <c r="A796" s="1"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
-      <c r="D796" s="46"/>
+      <c r="D796" s="45"/>
       <c r="E796" s="3"/>
       <c r="F796" s="3"/>
       <c r="G796" s="3"/>
@@ -24090,7 +24099,7 @@
       <c r="A797" s="1"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
-      <c r="D797" s="46"/>
+      <c r="D797" s="45"/>
       <c r="E797" s="3"/>
       <c r="F797" s="3"/>
       <c r="G797" s="3"/>
@@ -24118,7 +24127,7 @@
       <c r="A798" s="1"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
-      <c r="D798" s="46"/>
+      <c r="D798" s="45"/>
       <c r="E798" s="3"/>
       <c r="F798" s="3"/>
       <c r="G798" s="3"/>
@@ -24146,7 +24155,7 @@
       <c r="A799" s="1"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
-      <c r="D799" s="46"/>
+      <c r="D799" s="45"/>
       <c r="E799" s="3"/>
       <c r="F799" s="3"/>
       <c r="G799" s="3"/>
@@ -24174,7 +24183,7 @@
       <c r="A800" s="1"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
-      <c r="D800" s="46"/>
+      <c r="D800" s="45"/>
       <c r="E800" s="3"/>
       <c r="F800" s="3"/>
       <c r="G800" s="3"/>
@@ -24202,7 +24211,7 @@
       <c r="A801" s="1"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
-      <c r="D801" s="46"/>
+      <c r="D801" s="45"/>
       <c r="E801" s="3"/>
       <c r="F801" s="3"/>
       <c r="G801" s="3"/>
@@ -24230,7 +24239,7 @@
       <c r="A802" s="1"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
-      <c r="D802" s="46"/>
+      <c r="D802" s="45"/>
       <c r="E802" s="3"/>
       <c r="F802" s="3"/>
       <c r="G802" s="3"/>
@@ -24258,7 +24267,7 @@
       <c r="A803" s="1"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
-      <c r="D803" s="46"/>
+      <c r="D803" s="45"/>
       <c r="E803" s="3"/>
       <c r="F803" s="3"/>
       <c r="G803" s="3"/>
@@ -24286,7 +24295,7 @@
       <c r="A804" s="1"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
-      <c r="D804" s="46"/>
+      <c r="D804" s="45"/>
       <c r="E804" s="3"/>
       <c r="F804" s="3"/>
       <c r="G804" s="3"/>
@@ -24314,7 +24323,7 @@
       <c r="A805" s="1"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
-      <c r="D805" s="46"/>
+      <c r="D805" s="45"/>
       <c r="E805" s="3"/>
       <c r="F805" s="3"/>
       <c r="G805" s="3"/>
@@ -24342,7 +24351,7 @@
       <c r="A806" s="1"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
-      <c r="D806" s="46"/>
+      <c r="D806" s="45"/>
       <c r="E806" s="3"/>
       <c r="F806" s="3"/>
       <c r="G806" s="3"/>
@@ -24370,7 +24379,7 @@
       <c r="A807" s="1"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
-      <c r="D807" s="46"/>
+      <c r="D807" s="45"/>
       <c r="E807" s="3"/>
       <c r="F807" s="3"/>
       <c r="G807" s="3"/>
@@ -24398,7 +24407,7 @@
       <c r="A808" s="1"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
-      <c r="D808" s="46"/>
+      <c r="D808" s="45"/>
       <c r="E808" s="3"/>
       <c r="F808" s="3"/>
       <c r="G808" s="3"/>
@@ -24426,7 +24435,7 @@
       <c r="A809" s="1"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
-      <c r="D809" s="46"/>
+      <c r="D809" s="45"/>
       <c r="E809" s="3"/>
       <c r="F809" s="3"/>
       <c r="G809" s="3"/>
@@ -24454,7 +24463,7 @@
       <c r="A810" s="1"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
-      <c r="D810" s="46"/>
+      <c r="D810" s="45"/>
       <c r="E810" s="3"/>
       <c r="F810" s="3"/>
       <c r="G810" s="3"/>
@@ -24482,7 +24491,7 @@
       <c r="A811" s="1"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
-      <c r="D811" s="46"/>
+      <c r="D811" s="45"/>
       <c r="E811" s="3"/>
       <c r="F811" s="3"/>
       <c r="G811" s="3"/>
@@ -24510,7 +24519,7 @@
       <c r="A812" s="1"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
-      <c r="D812" s="46"/>
+      <c r="D812" s="45"/>
       <c r="E812" s="3"/>
       <c r="F812" s="3"/>
       <c r="G812" s="3"/>
@@ -24538,7 +24547,7 @@
       <c r="A813" s="1"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
-      <c r="D813" s="46"/>
+      <c r="D813" s="45"/>
       <c r="E813" s="3"/>
       <c r="F813" s="3"/>
       <c r="G813" s="3"/>
@@ -24566,7 +24575,7 @@
       <c r="A814" s="1"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
-      <c r="D814" s="46"/>
+      <c r="D814" s="45"/>
       <c r="E814" s="3"/>
       <c r="F814" s="3"/>
       <c r="G814" s="3"/>
@@ -24594,7 +24603,7 @@
       <c r="A815" s="1"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
-      <c r="D815" s="46"/>
+      <c r="D815" s="45"/>
       <c r="E815" s="3"/>
       <c r="F815" s="3"/>
       <c r="G815" s="3"/>
@@ -24622,7 +24631,7 @@
       <c r="A816" s="1"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
-      <c r="D816" s="46"/>
+      <c r="D816" s="45"/>
       <c r="E816" s="3"/>
       <c r="F816" s="3"/>
       <c r="G816" s="3"/>
@@ -24650,7 +24659,7 @@
       <c r="A817" s="1"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
-      <c r="D817" s="46"/>
+      <c r="D817" s="45"/>
       <c r="E817" s="3"/>
       <c r="F817" s="3"/>
       <c r="G817" s="3"/>
@@ -24678,7 +24687,7 @@
       <c r="A818" s="1"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
-      <c r="D818" s="46"/>
+      <c r="D818" s="45"/>
       <c r="E818" s="3"/>
       <c r="F818" s="3"/>
       <c r="G818" s="3"/>
@@ -24706,7 +24715,7 @@
       <c r="A819" s="1"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
-      <c r="D819" s="46"/>
+      <c r="D819" s="45"/>
       <c r="E819" s="3"/>
       <c r="F819" s="3"/>
       <c r="G819" s="3"/>
@@ -24734,7 +24743,7 @@
       <c r="A820" s="1"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
-      <c r="D820" s="46"/>
+      <c r="D820" s="45"/>
       <c r="E820" s="3"/>
       <c r="F820" s="3"/>
       <c r="G820" s="3"/>
@@ -24762,7 +24771,7 @@
       <c r="A821" s="1"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
-      <c r="D821" s="46"/>
+      <c r="D821" s="45"/>
       <c r="E821" s="3"/>
       <c r="F821" s="3"/>
       <c r="G821" s="3"/>
@@ -24790,7 +24799,7 @@
       <c r="A822" s="1"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
-      <c r="D822" s="46"/>
+      <c r="D822" s="45"/>
       <c r="E822" s="3"/>
       <c r="F822" s="3"/>
       <c r="G822" s="3"/>
@@ -24818,7 +24827,7 @@
       <c r="A823" s="1"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
-      <c r="D823" s="46"/>
+      <c r="D823" s="45"/>
       <c r="E823" s="3"/>
       <c r="F823" s="3"/>
       <c r="G823" s="3"/>
@@ -24846,7 +24855,7 @@
       <c r="A824" s="1"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
-      <c r="D824" s="46"/>
+      <c r="D824" s="45"/>
       <c r="E824" s="3"/>
       <c r="F824" s="3"/>
       <c r="G824" s="3"/>
@@ -24874,7 +24883,7 @@
       <c r="A825" s="1"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
-      <c r="D825" s="46"/>
+      <c r="D825" s="45"/>
       <c r="E825" s="3"/>
       <c r="F825" s="3"/>
       <c r="G825" s="3"/>
@@ -24902,7 +24911,7 @@
       <c r="A826" s="1"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
-      <c r="D826" s="46"/>
+      <c r="D826" s="45"/>
       <c r="E826" s="3"/>
       <c r="F826" s="3"/>
       <c r="G826" s="3"/>
@@ -24930,7 +24939,7 @@
       <c r="A827" s="1"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
-      <c r="D827" s="46"/>
+      <c r="D827" s="45"/>
       <c r="E827" s="3"/>
       <c r="F827" s="3"/>
       <c r="G827" s="3"/>
@@ -24958,7 +24967,7 @@
       <c r="A828" s="1"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
-      <c r="D828" s="46"/>
+      <c r="D828" s="45"/>
       <c r="E828" s="3"/>
       <c r="F828" s="3"/>
       <c r="G828" s="3"/>
@@ -24986,7 +24995,7 @@
       <c r="A829" s="1"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
-      <c r="D829" s="46"/>
+      <c r="D829" s="45"/>
       <c r="E829" s="3"/>
       <c r="F829" s="3"/>
       <c r="G829" s="3"/>
@@ -25014,7 +25023,7 @@
       <c r="A830" s="1"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
-      <c r="D830" s="46"/>
+      <c r="D830" s="45"/>
       <c r="E830" s="3"/>
       <c r="F830" s="3"/>
       <c r="G830" s="3"/>
@@ -25042,7 +25051,7 @@
       <c r="A831" s="1"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
-      <c r="D831" s="46"/>
+      <c r="D831" s="45"/>
       <c r="E831" s="3"/>
       <c r="F831" s="3"/>
       <c r="G831" s="3"/>
@@ -25070,7 +25079,7 @@
       <c r="A832" s="1"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
-      <c r="D832" s="46"/>
+      <c r="D832" s="45"/>
       <c r="E832" s="3"/>
       <c r="F832" s="3"/>
       <c r="G832" s="3"/>
@@ -25098,7 +25107,7 @@
       <c r="A833" s="1"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
-      <c r="D833" s="46"/>
+      <c r="D833" s="45"/>
       <c r="E833" s="3"/>
       <c r="F833" s="3"/>
       <c r="G833" s="3"/>
@@ -25126,7 +25135,7 @@
       <c r="A834" s="1"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
-      <c r="D834" s="46"/>
+      <c r="D834" s="45"/>
       <c r="E834" s="3"/>
       <c r="F834" s="3"/>
       <c r="G834" s="3"/>
@@ -25154,7 +25163,7 @@
       <c r="A835" s="1"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
-      <c r="D835" s="46"/>
+      <c r="D835" s="45"/>
       <c r="E835" s="3"/>
       <c r="F835" s="3"/>
       <c r="G835" s="3"/>
@@ -25182,7 +25191,7 @@
       <c r="A836" s="1"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
-      <c r="D836" s="46"/>
+      <c r="D836" s="45"/>
       <c r="E836" s="3"/>
       <c r="F836" s="3"/>
       <c r="G836" s="3"/>
@@ -25210,7 +25219,7 @@
       <c r="A837" s="1"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
-      <c r="D837" s="46"/>
+      <c r="D837" s="45"/>
       <c r="E837" s="3"/>
       <c r="F837" s="3"/>
       <c r="G837" s="3"/>
@@ -25238,7 +25247,7 @@
       <c r="A838" s="1"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
-      <c r="D838" s="46"/>
+      <c r="D838" s="45"/>
       <c r="E838" s="3"/>
       <c r="F838" s="3"/>
       <c r="G838" s="3"/>
@@ -25266,7 +25275,7 @@
       <c r="A839" s="1"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
-      <c r="D839" s="46"/>
+      <c r="D839" s="45"/>
       <c r="E839" s="3"/>
       <c r="F839" s="3"/>
       <c r="G839" s="3"/>
@@ -25294,7 +25303,7 @@
       <c r="A840" s="1"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
-      <c r="D840" s="46"/>
+      <c r="D840" s="45"/>
       <c r="E840" s="3"/>
       <c r="F840" s="3"/>
       <c r="G840" s="3"/>
@@ -25322,7 +25331,7 @@
       <c r="A841" s="1"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
-      <c r="D841" s="46"/>
+      <c r="D841" s="45"/>
       <c r="E841" s="3"/>
       <c r="F841" s="3"/>
       <c r="G841" s="3"/>
@@ -25350,7 +25359,7 @@
       <c r="A842" s="1"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
-      <c r="D842" s="46"/>
+      <c r="D842" s="45"/>
       <c r="E842" s="3"/>
       <c r="F842" s="3"/>
       <c r="G842" s="3"/>
@@ -25378,7 +25387,7 @@
       <c r="A843" s="1"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
-      <c r="D843" s="46"/>
+      <c r="D843" s="45"/>
       <c r="E843" s="3"/>
       <c r="F843" s="3"/>
       <c r="G843" s="3"/>
@@ -25406,7 +25415,7 @@
       <c r="A844" s="1"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
-      <c r="D844" s="46"/>
+      <c r="D844" s="45"/>
       <c r="E844" s="3"/>
       <c r="F844" s="3"/>
       <c r="G844" s="3"/>
@@ -25434,7 +25443,7 @@
       <c r="A845" s="1"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
-      <c r="D845" s="46"/>
+      <c r="D845" s="45"/>
       <c r="E845" s="3"/>
       <c r="F845" s="3"/>
       <c r="G845" s="3"/>
@@ -25462,7 +25471,7 @@
       <c r="A846" s="1"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
-      <c r="D846" s="46"/>
+      <c r="D846" s="45"/>
       <c r="E846" s="3"/>
       <c r="F846" s="3"/>
       <c r="G846" s="3"/>
@@ -25490,7 +25499,7 @@
       <c r="A847" s="1"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
-      <c r="D847" s="46"/>
+      <c r="D847" s="45"/>
       <c r="E847" s="3"/>
       <c r="F847" s="3"/>
       <c r="G847" s="3"/>
@@ -25518,7 +25527,7 @@
       <c r="A848" s="1"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
-      <c r="D848" s="46"/>
+      <c r="D848" s="45"/>
       <c r="E848" s="3"/>
       <c r="F848" s="3"/>
       <c r="G848" s="3"/>
@@ -25546,7 +25555,7 @@
       <c r="A849" s="1"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
-      <c r="D849" s="46"/>
+      <c r="D849" s="45"/>
       <c r="E849" s="3"/>
       <c r="F849" s="3"/>
       <c r="G849" s="3"/>
@@ -25574,7 +25583,7 @@
       <c r="A850" s="1"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
-      <c r="D850" s="46"/>
+      <c r="D850" s="45"/>
       <c r="E850" s="3"/>
       <c r="F850" s="3"/>
       <c r="G850" s="3"/>
@@ -25602,7 +25611,7 @@
       <c r="A851" s="1"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
-      <c r="D851" s="46"/>
+      <c r="D851" s="45"/>
       <c r="E851" s="3"/>
       <c r="F851" s="3"/>
       <c r="G851" s="3"/>
@@ -25630,7 +25639,7 @@
       <c r="A852" s="1"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
-      <c r="D852" s="46"/>
+      <c r="D852" s="45"/>
       <c r="E852" s="3"/>
       <c r="F852" s="3"/>
       <c r="G852" s="3"/>
@@ -25658,7 +25667,7 @@
       <c r="A853" s="1"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
-      <c r="D853" s="46"/>
+      <c r="D853" s="45"/>
       <c r="E853" s="3"/>
       <c r="F853" s="3"/>
       <c r="G853" s="3"/>
@@ -25686,7 +25695,7 @@
       <c r="A854" s="1"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
-      <c r="D854" s="46"/>
+      <c r="D854" s="45"/>
       <c r="E854" s="3"/>
       <c r="F854" s="3"/>
       <c r="G854" s="3"/>
@@ -25714,7 +25723,7 @@
       <c r="A855" s="1"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
-      <c r="D855" s="46"/>
+      <c r="D855" s="45"/>
       <c r="E855" s="3"/>
       <c r="F855" s="3"/>
       <c r="G855" s="3"/>
@@ -25742,7 +25751,7 @@
       <c r="A856" s="1"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
-      <c r="D856" s="46"/>
+      <c r="D856" s="45"/>
       <c r="E856" s="3"/>
       <c r="F856" s="3"/>
       <c r="G856" s="3"/>
@@ -25770,7 +25779,7 @@
       <c r="A857" s="1"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
-      <c r="D857" s="46"/>
+      <c r="D857" s="45"/>
       <c r="E857" s="3"/>
       <c r="F857" s="3"/>
       <c r="G857" s="3"/>
@@ -25798,7 +25807,7 @@
       <c r="A858" s="1"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
-      <c r="D858" s="46"/>
+      <c r="D858" s="45"/>
       <c r="E858" s="3"/>
       <c r="F858" s="3"/>
       <c r="G858" s="3"/>
@@ -25826,7 +25835,7 @@
       <c r="A859" s="1"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
-      <c r="D859" s="46"/>
+      <c r="D859" s="45"/>
       <c r="E859" s="3"/>
       <c r="F859" s="3"/>
       <c r="G859" s="3"/>
@@ -25854,7 +25863,7 @@
       <c r="A860" s="1"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
-      <c r="D860" s="46"/>
+      <c r="D860" s="45"/>
       <c r="E860" s="3"/>
       <c r="F860" s="3"/>
       <c r="G860" s="3"/>
@@ -25882,7 +25891,7 @@
       <c r="A861" s="1"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
-      <c r="D861" s="46"/>
+      <c r="D861" s="45"/>
       <c r="E861" s="3"/>
       <c r="F861" s="3"/>
       <c r="G861" s="3"/>
@@ -25910,7 +25919,7 @@
       <c r="A862" s="1"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
-      <c r="D862" s="46"/>
+      <c r="D862" s="45"/>
       <c r="E862" s="3"/>
       <c r="F862" s="3"/>
       <c r="G862" s="3"/>
@@ -25938,7 +25947,7 @@
       <c r="A863" s="1"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
-      <c r="D863" s="46"/>
+      <c r="D863" s="45"/>
       <c r="E863" s="3"/>
       <c r="F863" s="3"/>
       <c r="G863" s="3"/>
@@ -25966,7 +25975,7 @@
       <c r="A864" s="1"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
-      <c r="D864" s="46"/>
+      <c r="D864" s="45"/>
       <c r="E864" s="3"/>
       <c r="F864" s="3"/>
       <c r="G864" s="3"/>
@@ -25994,7 +26003,7 @@
       <c r="A865" s="1"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
-      <c r="D865" s="46"/>
+      <c r="D865" s="45"/>
       <c r="E865" s="3"/>
       <c r="F865" s="3"/>
       <c r="G865" s="3"/>
@@ -26022,7 +26031,7 @@
       <c r="A866" s="1"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
-      <c r="D866" s="46"/>
+      <c r="D866" s="45"/>
       <c r="E866" s="3"/>
       <c r="F866" s="3"/>
       <c r="G866" s="3"/>
@@ -26050,7 +26059,7 @@
       <c r="A867" s="1"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
-      <c r="D867" s="46"/>
+      <c r="D867" s="45"/>
       <c r="E867" s="3"/>
       <c r="F867" s="3"/>
       <c r="G867" s="3"/>
@@ -26078,7 +26087,7 @@
       <c r="A868" s="1"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
-      <c r="D868" s="46"/>
+      <c r="D868" s="45"/>
       <c r="E868" s="3"/>
       <c r="F868" s="3"/>
       <c r="G868" s="3"/>
@@ -26106,7 +26115,7 @@
       <c r="A869" s="1"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
-      <c r="D869" s="46"/>
+      <c r="D869" s="45"/>
       <c r="E869" s="3"/>
       <c r="F869" s="3"/>
       <c r="G869" s="3"/>
@@ -26134,7 +26143,7 @@
       <c r="A870" s="1"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
-      <c r="D870" s="46"/>
+      <c r="D870" s="45"/>
       <c r="E870" s="3"/>
       <c r="F870" s="3"/>
       <c r="G870" s="3"/>
@@ -26162,7 +26171,7 @@
       <c r="A871" s="1"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
-      <c r="D871" s="46"/>
+      <c r="D871" s="45"/>
       <c r="E871" s="3"/>
       <c r="F871" s="3"/>
       <c r="G871" s="3"/>
@@ -26190,7 +26199,7 @@
       <c r="A872" s="1"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
-      <c r="D872" s="46"/>
+      <c r="D872" s="45"/>
       <c r="E872" s="3"/>
       <c r="F872" s="3"/>
       <c r="G872" s="3"/>
@@ -26218,7 +26227,7 @@
       <c r="A873" s="1"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
-      <c r="D873" s="46"/>
+      <c r="D873" s="45"/>
       <c r="E873" s="3"/>
       <c r="F873" s="3"/>
       <c r="G873" s="3"/>
@@ -26246,7 +26255,7 @@
       <c r="A874" s="1"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
-      <c r="D874" s="46"/>
+      <c r="D874" s="45"/>
       <c r="E874" s="3"/>
       <c r="F874" s="3"/>
       <c r="G874" s="3"/>
@@ -26274,7 +26283,7 @@
       <c r="A875" s="1"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
-      <c r="D875" s="46"/>
+      <c r="D875" s="45"/>
       <c r="E875" s="3"/>
       <c r="F875" s="3"/>
       <c r="G875" s="3"/>
@@ -26302,7 +26311,7 @@
       <c r="A876" s="1"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
-      <c r="D876" s="46"/>
+      <c r="D876" s="45"/>
       <c r="E876" s="3"/>
       <c r="F876" s="3"/>
       <c r="G876" s="3"/>
@@ -26330,7 +26339,7 @@
       <c r="A877" s="1"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
-      <c r="D877" s="46"/>
+      <c r="D877" s="45"/>
       <c r="E877" s="3"/>
       <c r="F877" s="3"/>
       <c r="G877" s="3"/>
@@ -26358,7 +26367,7 @@
       <c r="A878" s="1"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
-      <c r="D878" s="46"/>
+      <c r="D878" s="45"/>
       <c r="E878" s="3"/>
       <c r="F878" s="3"/>
       <c r="G878" s="3"/>
@@ -26386,7 +26395,7 @@
       <c r="A879" s="1"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
-      <c r="D879" s="46"/>
+      <c r="D879" s="45"/>
       <c r="E879" s="3"/>
       <c r="F879" s="3"/>
       <c r="G879" s="3"/>
@@ -26414,7 +26423,7 @@
       <c r="A880" s="1"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
-      <c r="D880" s="46"/>
+      <c r="D880" s="45"/>
       <c r="E880" s="3"/>
       <c r="F880" s="3"/>
       <c r="G880" s="3"/>
@@ -26442,7 +26451,7 @@
       <c r="A881" s="1"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
-      <c r="D881" s="46"/>
+      <c r="D881" s="45"/>
       <c r="E881" s="3"/>
       <c r="F881" s="3"/>
       <c r="G881" s="3"/>
@@ -26470,7 +26479,7 @@
       <c r="A882" s="1"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
-      <c r="D882" s="46"/>
+      <c r="D882" s="45"/>
       <c r="E882" s="3"/>
       <c r="F882" s="3"/>
       <c r="G882" s="3"/>
@@ -26498,7 +26507,7 @@
       <c r="A883" s="1"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
-      <c r="D883" s="46"/>
+      <c r="D883" s="45"/>
       <c r="E883" s="3"/>
       <c r="F883" s="3"/>
       <c r="G883" s="3"/>
@@ -26526,7 +26535,7 @@
       <c r="A884" s="1"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
-      <c r="D884" s="46"/>
+      <c r="D884" s="45"/>
       <c r="E884" s="3"/>
       <c r="F884" s="3"/>
       <c r="G884" s="3"/>
@@ -26554,7 +26563,7 @@
       <c r="A885" s="1"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
-      <c r="D885" s="46"/>
+      <c r="D885" s="45"/>
       <c r="E885" s="3"/>
       <c r="F885" s="3"/>
       <c r="G885" s="3"/>
@@ -26582,7 +26591,7 @@
       <c r="A886" s="1"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
-      <c r="D886" s="46"/>
+      <c r="D886" s="45"/>
       <c r="E886" s="3"/>
       <c r="F886" s="3"/>
       <c r="G886" s="3"/>
@@ -26610,7 +26619,7 @@
       <c r="A887" s="1"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
-      <c r="D887" s="46"/>
+      <c r="D887" s="45"/>
       <c r="E887" s="3"/>
       <c r="F887" s="3"/>
       <c r="G887" s="3"/>
@@ -26638,7 +26647,7 @@
       <c r="A888" s="1"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
-      <c r="D888" s="46"/>
+      <c r="D888" s="45"/>
       <c r="E888" s="3"/>
       <c r="F888" s="3"/>
       <c r="G888" s="3"/>
@@ -26666,7 +26675,7 @@
       <c r="A889" s="1"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
-      <c r="D889" s="46"/>
+      <c r="D889" s="45"/>
       <c r="E889" s="3"/>
       <c r="F889" s="3"/>
       <c r="G889" s="3"/>
@@ -26694,7 +26703,7 @@
       <c r="A890" s="1"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
-      <c r="D890" s="46"/>
+      <c r="D890" s="45"/>
       <c r="E890" s="3"/>
       <c r="F890" s="3"/>
       <c r="G890" s="3"/>
@@ -26722,7 +26731,7 @@
       <c r="A891" s="1"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
-      <c r="D891" s="46"/>
+      <c r="D891" s="45"/>
       <c r="E891" s="3"/>
       <c r="F891" s="3"/>
       <c r="G891" s="3"/>
@@ -26750,7 +26759,7 @@
       <c r="A892" s="1"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
-      <c r="D892" s="46"/>
+      <c r="D892" s="45"/>
       <c r="E892" s="3"/>
       <c r="F892" s="3"/>
       <c r="G892" s="3"/>
@@ -26778,7 +26787,7 @@
       <c r="A893" s="1"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
-      <c r="D893" s="46"/>
+      <c r="D893" s="45"/>
       <c r="E893" s="3"/>
       <c r="F893" s="3"/>
       <c r="G893" s="3"/>
@@ -26806,7 +26815,7 @@
       <c r="A894" s="1"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
-      <c r="D894" s="46"/>
+      <c r="D894" s="45"/>
       <c r="E894" s="3"/>
       <c r="F894" s="3"/>
       <c r="G894" s="3"/>
@@ -26834,7 +26843,7 @@
       <c r="A895" s="1"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
-      <c r="D895" s="46"/>
+      <c r="D895" s="45"/>
       <c r="E895" s="3"/>
       <c r="F895" s="3"/>
       <c r="G895" s="3"/>
@@ -26862,7 +26871,7 @@
       <c r="A896" s="1"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
-      <c r="D896" s="46"/>
+      <c r="D896" s="45"/>
       <c r="E896" s="3"/>
       <c r="F896" s="3"/>
       <c r="G896" s="3"/>
@@ -26890,7 +26899,7 @@
       <c r="A897" s="1"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
-      <c r="D897" s="46"/>
+      <c r="D897" s="45"/>
       <c r="E897" s="3"/>
       <c r="F897" s="3"/>
       <c r="G897" s="3"/>
@@ -26918,7 +26927,7 @@
       <c r="A898" s="1"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
-      <c r="D898" s="46"/>
+      <c r="D898" s="45"/>
       <c r="E898" s="3"/>
       <c r="F898" s="3"/>
       <c r="G898" s="3"/>
@@ -26946,7 +26955,7 @@
       <c r="A899" s="1"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
-      <c r="D899" s="46"/>
+      <c r="D899" s="45"/>
       <c r="E899" s="3"/>
       <c r="F899" s="3"/>
       <c r="G899" s="3"/>
@@ -26974,7 +26983,7 @@
       <c r="A900" s="1"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
-      <c r="D900" s="46"/>
+      <c r="D900" s="45"/>
       <c r="E900" s="3"/>
       <c r="F900" s="3"/>
       <c r="G900" s="3"/>
@@ -27002,7 +27011,7 @@
       <c r="A901" s="1"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
-      <c r="D901" s="46"/>
+      <c r="D901" s="45"/>
       <c r="E901" s="3"/>
       <c r="F901" s="3"/>
       <c r="G901" s="3"/>
@@ -27030,7 +27039,7 @@
       <c r="A902" s="1"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
-      <c r="D902" s="46"/>
+      <c r="D902" s="45"/>
       <c r="E902" s="3"/>
       <c r="F902" s="3"/>
       <c r="G902" s="3"/>
@@ -27058,7 +27067,7 @@
       <c r="A903" s="1"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
-      <c r="D903" s="46"/>
+      <c r="D903" s="45"/>
       <c r="E903" s="3"/>
       <c r="F903" s="3"/>
       <c r="G903" s="3"/>
@@ -27086,7 +27095,7 @@
       <c r="A904" s="1"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
-      <c r="D904" s="46"/>
+      <c r="D904" s="45"/>
       <c r="E904" s="3"/>
       <c r="F904" s="3"/>
       <c r="G904" s="3"/>
@@ -27114,7 +27123,7 @@
       <c r="A905" s="1"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
-      <c r="D905" s="46"/>
+      <c r="D905" s="45"/>
       <c r="E905" s="3"/>
       <c r="F905" s="3"/>
       <c r="G905" s="3"/>
@@ -27142,7 +27151,7 @@
       <c r="A906" s="1"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
-      <c r="D906" s="46"/>
+      <c r="D906" s="45"/>
       <c r="E906" s="3"/>
       <c r="F906" s="3"/>
       <c r="G906" s="3"/>
@@ -27170,7 +27179,7 @@
       <c r="A907" s="1"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
-      <c r="D907" s="46"/>
+      <c r="D907" s="45"/>
       <c r="E907" s="3"/>
       <c r="F907" s="3"/>
       <c r="G907" s="3"/>
@@ -27198,7 +27207,7 @@
       <c r="A908" s="1"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
-      <c r="D908" s="46"/>
+      <c r="D908" s="45"/>
       <c r="E908" s="3"/>
       <c r="F908" s="3"/>
       <c r="G908" s="3"/>
@@ -27226,7 +27235,7 @@
       <c r="A909" s="1"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
-      <c r="D909" s="46"/>
+      <c r="D909" s="45"/>
       <c r="E909" s="3"/>
       <c r="F909" s="3"/>
       <c r="G909" s="3"/>
@@ -27254,7 +27263,7 @@
       <c r="A910" s="1"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
-      <c r="D910" s="46"/>
+      <c r="D910" s="45"/>
       <c r="E910" s="3"/>
       <c r="F910" s="3"/>
       <c r="G910" s="3"/>
@@ -27282,7 +27291,7 @@
       <c r="A911" s="1"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
-      <c r="D911" s="46"/>
+      <c r="D911" s="45"/>
       <c r="E911" s="3"/>
       <c r="F911" s="3"/>
       <c r="G911" s="3"/>
@@ -27310,7 +27319,7 @@
       <c r="A912" s="1"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
-      <c r="D912" s="46"/>
+      <c r="D912" s="45"/>
       <c r="E912" s="3"/>
       <c r="F912" s="3"/>
       <c r="G912" s="3"/>
@@ -27338,7 +27347,7 @@
       <c r="A913" s="1"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
-      <c r="D913" s="46"/>
+      <c r="D913" s="45"/>
       <c r="E913" s="3"/>
       <c r="F913" s="3"/>
       <c r="G913" s="3"/>
@@ -27366,7 +27375,7 @@
       <c r="A914" s="1"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
-      <c r="D914" s="46"/>
+      <c r="D914" s="45"/>
       <c r="E914" s="3"/>
       <c r="F914" s="3"/>
       <c r="G914" s="3"/>
@@ -27394,7 +27403,7 @@
       <c r="A915" s="1"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
-      <c r="D915" s="46"/>
+      <c r="D915" s="45"/>
       <c r="E915" s="3"/>
       <c r="F915" s="3"/>
       <c r="G915" s="3"/>
@@ -27422,7 +27431,7 @@
       <c r="A916" s="1"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
-      <c r="D916" s="46"/>
+      <c r="D916" s="45"/>
       <c r="E916" s="3"/>
       <c r="F916" s="3"/>
       <c r="G916" s="3"/>
@@ -27450,7 +27459,7 @@
       <c r="A917" s="1"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
-      <c r="D917" s="46"/>
+      <c r="D917" s="45"/>
       <c r="E917" s="3"/>
       <c r="F917" s="3"/>
       <c r="G917" s="3"/>
@@ -27478,7 +27487,7 @@
       <c r="A918" s="1"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
-      <c r="D918" s="46"/>
+      <c r="D918" s="45"/>
       <c r="E918" s="3"/>
       <c r="F918" s="3"/>
       <c r="G918" s="3"/>
@@ -27506,7 +27515,7 @@
       <c r="A919" s="1"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
-      <c r="D919" s="46"/>
+      <c r="D919" s="45"/>
       <c r="E919" s="3"/>
       <c r="F919" s="3"/>
       <c r="G919" s="3"/>
@@ -27534,7 +27543,7 @@
       <c r="A920" s="1"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
-      <c r="D920" s="46"/>
+      <c r="D920" s="45"/>
       <c r="E920" s="3"/>
       <c r="F920" s="3"/>
       <c r="G920" s="3"/>
@@ -27562,7 +27571,7 @@
       <c r="A921" s="1"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
-      <c r="D921" s="46"/>
+      <c r="D921" s="45"/>
       <c r="E921" s="3"/>
       <c r="F921" s="3"/>
       <c r="G921" s="3"/>
@@ -27590,7 +27599,7 @@
       <c r="A922" s="1"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
-      <c r="D922" s="46"/>
+      <c r="D922" s="45"/>
       <c r="E922" s="3"/>
       <c r="F922" s="3"/>
       <c r="G922" s="3"/>
@@ -27618,7 +27627,7 @@
       <c r="A923" s="1"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
-      <c r="D923" s="46"/>
+      <c r="D923" s="45"/>
       <c r="E923" s="3"/>
       <c r="F923" s="3"/>
       <c r="G923" s="3"/>
@@ -27646,7 +27655,7 @@
       <c r="A924" s="1"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
-      <c r="D924" s="46"/>
+      <c r="D924" s="45"/>
       <c r="E924" s="3"/>
       <c r="F924" s="3"/>
       <c r="G924" s="3"/>
@@ -27674,7 +27683,7 @@
       <c r="A925" s="1"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
-      <c r="D925" s="46"/>
+      <c r="D925" s="45"/>
       <c r="E925" s="3"/>
       <c r="F925" s="3"/>
       <c r="G925" s="3"/>
@@ -27702,7 +27711,7 @@
       <c r="A926" s="1"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
-      <c r="D926" s="46"/>
+      <c r="D926" s="45"/>
       <c r="E926" s="3"/>
       <c r="F926" s="3"/>
       <c r="G926" s="3"/>
@@ -27730,7 +27739,7 @@
       <c r="A927" s="1"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
-      <c r="D927" s="46"/>
+      <c r="D927" s="45"/>
       <c r="E927" s="3"/>
       <c r="F927" s="3"/>
       <c r="G927" s="3"/>
@@ -27758,7 +27767,7 @@
       <c r="A928" s="1"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
-      <c r="D928" s="46"/>
+      <c r="D928" s="45"/>
       <c r="E928" s="3"/>
       <c r="F928" s="3"/>
       <c r="G928" s="3"/>
@@ -27786,7 +27795,7 @@
       <c r="A929" s="1"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
-      <c r="D929" s="46"/>
+      <c r="D929" s="45"/>
       <c r="E929" s="3"/>
       <c r="F929" s="3"/>
       <c r="G929" s="3"/>
@@ -27814,7 +27823,7 @@
       <c r="A930" s="1"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
-      <c r="D930" s="46"/>
+      <c r="D930" s="45"/>
       <c r="E930" s="3"/>
       <c r="F930" s="3"/>
       <c r="G930" s="3"/>
@@ -27842,7 +27851,7 @@
       <c r="A931" s="1"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
-      <c r="D931" s="46"/>
+      <c r="D931" s="45"/>
       <c r="E931" s="3"/>
       <c r="F931" s="3"/>
       <c r="G931" s="3"/>
@@ -27870,7 +27879,7 @@
       <c r="A932" s="1"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
-      <c r="D932" s="46"/>
+      <c r="D932" s="45"/>
       <c r="E932" s="3"/>
       <c r="F932" s="3"/>
       <c r="G932" s="3"/>
@@ -27898,7 +27907,7 @@
       <c r="A933" s="1"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
-      <c r="D933" s="46"/>
+      <c r="D933" s="45"/>
       <c r="E933" s="3"/>
       <c r="F933" s="3"/>
       <c r="G933" s="3"/>
@@ -27926,7 +27935,7 @@
       <c r="A934" s="1"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
-      <c r="D934" s="46"/>
+      <c r="D934" s="45"/>
       <c r="E934" s="3"/>
       <c r="F934" s="3"/>
       <c r="G934" s="3"/>
@@ -27954,7 +27963,7 @@
       <c r="A935" s="1"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
-      <c r="D935" s="46"/>
+      <c r="D935" s="45"/>
       <c r="E935" s="3"/>
       <c r="F935" s="3"/>
       <c r="G935" s="3"/>
@@ -27982,7 +27991,7 @@
       <c r="A936" s="1"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
-      <c r="D936" s="46"/>
+      <c r="D936" s="45"/>
       <c r="E936" s="3"/>
       <c r="F936" s="3"/>
       <c r="G936" s="3"/>
@@ -28010,7 +28019,7 @@
       <c r="A937" s="1"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
-      <c r="D937" s="46"/>
+      <c r="D937" s="45"/>
       <c r="E937" s="3"/>
       <c r="F937" s="3"/>
       <c r="G937" s="3"/>
@@ -28038,7 +28047,7 @@
       <c r="A938" s="1"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
-      <c r="D938" s="46"/>
+      <c r="D938" s="45"/>
       <c r="E938" s="3"/>
       <c r="F938" s="3"/>
       <c r="G938" s="3"/>
@@ -28066,7 +28075,7 @@
       <c r="A939" s="1"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
-      <c r="D939" s="46"/>
+      <c r="D939" s="45"/>
       <c r="E939" s="3"/>
       <c r="F939" s="3"/>
       <c r="G939" s="3"/>
@@ -28094,7 +28103,7 @@
       <c r="A940" s="1"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
-      <c r="D940" s="46"/>
+      <c r="D940" s="45"/>
       <c r="E940" s="3"/>
       <c r="F940" s="3"/>
       <c r="G940" s="3"/>
@@ -28122,7 +28131,7 @@
       <c r="A941" s="1"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
-      <c r="D941" s="46"/>
+      <c r="D941" s="45"/>
       <c r="E941" s="3"/>
       <c r="F941" s="3"/>
       <c r="G941" s="3"/>
@@ -28150,7 +28159,7 @@
       <c r="A942" s="1"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
-      <c r="D942" s="46"/>
+      <c r="D942" s="45"/>
       <c r="E942" s="3"/>
       <c r="F942" s="3"/>
       <c r="G942" s="3"/>
@@ -28178,7 +28187,7 @@
       <c r="A943" s="1"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
-      <c r="D943" s="46"/>
+      <c r="D943" s="45"/>
       <c r="E943" s="3"/>
       <c r="F943" s="3"/>
       <c r="G943" s="3"/>
@@ -28206,7 +28215,7 @@
       <c r="A944" s="1"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
-      <c r="D944" s="46"/>
+      <c r="D944" s="45"/>
       <c r="E944" s="3"/>
       <c r="F944" s="3"/>
       <c r="G944" s="3"/>
@@ -28234,7 +28243,7 @@
       <c r="A945" s="1"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
-      <c r="D945" s="46"/>
+      <c r="D945" s="45"/>
       <c r="E945" s="3"/>
       <c r="F945" s="3"/>
       <c r="G945" s="3"/>
@@ -28262,7 +28271,7 @@
       <c r="A946" s="1"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
-      <c r="D946" s="46"/>
+      <c r="D946" s="45"/>
       <c r="E946" s="3"/>
       <c r="F946" s="3"/>
       <c r="G946" s="3"/>
@@ -28290,7 +28299,7 @@
       <c r="A947" s="1"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
-      <c r="D947" s="46"/>
+      <c r="D947" s="45"/>
       <c r="E947" s="3"/>
       <c r="F947" s="3"/>
       <c r="G947" s="3"/>
@@ -28318,7 +28327,7 @@
       <c r="A948" s="1"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
-      <c r="D948" s="46"/>
+      <c r="D948" s="45"/>
       <c r="E948" s="3"/>
       <c r="F948" s="3"/>
       <c r="G948" s="3"/>
@@ -28346,7 +28355,7 @@
       <c r="A949" s="1"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
-      <c r="D949" s="46"/>
+      <c r="D949" s="45"/>
       <c r="E949" s="3"/>
       <c r="F949" s="3"/>
       <c r="G949" s="3"/>
@@ -28374,7 +28383,7 @@
       <c r="A950" s="1"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
-      <c r="D950" s="46"/>
+      <c r="D950" s="45"/>
       <c r="E950" s="3"/>
       <c r="F950" s="3"/>
       <c r="G950" s="3"/>
@@ -28402,7 +28411,7 @@
       <c r="A951" s="1"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
-      <c r="D951" s="46"/>
+      <c r="D951" s="45"/>
       <c r="E951" s="3"/>
       <c r="F951" s="3"/>
       <c r="G951" s="3"/>
@@ -28430,7 +28439,7 @@
       <c r="A952" s="1"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
-      <c r="D952" s="46"/>
+      <c r="D952" s="45"/>
       <c r="E952" s="3"/>
       <c r="F952" s="3"/>
       <c r="G952" s="3"/>
@@ -28458,7 +28467,7 @@
       <c r="A953" s="1"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
-      <c r="D953" s="46"/>
+      <c r="D953" s="45"/>
       <c r="E953" s="3"/>
       <c r="F953" s="3"/>
       <c r="G953" s="3"/>
@@ -28486,7 +28495,7 @@
       <c r="A954" s="1"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
-      <c r="D954" s="46"/>
+      <c r="D954" s="45"/>
       <c r="E954" s="3"/>
       <c r="F954" s="3"/>
       <c r="G954" s="3"/>
@@ -28514,7 +28523,7 @@
       <c r="A955" s="1"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
-      <c r="D955" s="46"/>
+      <c r="D955" s="45"/>
       <c r="E955" s="3"/>
       <c r="F955" s="3"/>
       <c r="G955" s="3"/>
@@ -28542,7 +28551,7 @@
       <c r="A956" s="1"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
-      <c r="D956" s="46"/>
+      <c r="D956" s="45"/>
       <c r="E956" s="3"/>
       <c r="F956" s="3"/>
       <c r="G956" s="3"/>
@@ -28570,7 +28579,7 @@
       <c r="A957" s="1"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
-      <c r="D957" s="46"/>
+      <c r="D957" s="45"/>
       <c r="E957" s="3"/>
       <c r="F957" s="3"/>
       <c r="G957" s="3"/>
@@ -28598,7 +28607,7 @@
       <c r="A958" s="1"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
-      <c r="D958" s="46"/>
+      <c r="D958" s="45"/>
       <c r="E958" s="3"/>
       <c r="F958" s="3"/>
       <c r="G958" s="3"/>
@@ -28626,7 +28635,7 @@
       <c r="A959" s="1"/>
       <c r="B959" s="3"/>
       <c r="C959" s="3"/>
-      <c r="D959" s="46"/>
+      <c r="D959" s="45"/>
       <c r="E959" s="3"/>
       <c r="F959" s="3"/>
       <c r="G959" s="3"/>
@@ -28654,7 +28663,7 @@
       <c r="A960" s="1"/>
       <c r="B960" s="3"/>
       <c r="C960" s="3"/>
-      <c r="D960" s="46"/>
+      <c r="D960" s="45"/>
       <c r="E960" s="3"/>
       <c r="F960" s="3"/>
       <c r="G960" s="3"/>
@@ -28682,7 +28691,7 @@
       <c r="A961" s="1"/>
       <c r="B961" s="3"/>
       <c r="C961" s="3"/>
-      <c r="D961" s="46"/>
+      <c r="D961" s="45"/>
       <c r="E961" s="3"/>
       <c r="F961" s="3"/>
       <c r="G961" s="3"/>
@@ -28710,7 +28719,7 @@
       <c r="A962" s="1"/>
       <c r="B962" s="3"/>
       <c r="C962" s="3"/>
-      <c r="D962" s="46"/>
+      <c r="D962" s="45"/>
       <c r="E962" s="3"/>
       <c r="F962" s="3"/>
       <c r="G962" s="3"/>
@@ -28738,7 +28747,7 @@
       <c r="A963" s="1"/>
       <c r="B963" s="3"/>
       <c r="C963" s="3"/>
-      <c r="D963" s="46"/>
+      <c r="D963" s="45"/>
       <c r="E963" s="3"/>
       <c r="F963" s="3"/>
       <c r="G963" s="3"/>
@@ -28766,7 +28775,7 @@
       <c r="A964" s="1"/>
       <c r="B964" s="3"/>
       <c r="C964" s="3"/>
-      <c r="D964" s="46"/>
+      <c r="D964" s="45"/>
       <c r="E964" s="3"/>
       <c r="F964" s="3"/>
       <c r="G964" s="3"/>
@@ -28794,7 +28803,7 @@
       <c r="A965" s="1"/>
       <c r="B965" s="3"/>
       <c r="C965" s="3"/>
-      <c r="D965" s="46"/>
+      <c r="D965" s="45"/>
       <c r="E965" s="3"/>
       <c r="F965" s="3"/>
       <c r="G965" s="3"/>
@@ -28822,7 +28831,7 @@
       <c r="A966" s="1"/>
       <c r="B966" s="3"/>
       <c r="C966" s="3"/>
-      <c r="D966" s="46"/>
+      <c r="D966" s="45"/>
       <c r="E966" s="3"/>
       <c r="F966" s="3"/>
       <c r="G966" s="3"/>
@@ -28850,7 +28859,7 @@
       <c r="A967" s="1"/>
       <c r="B967" s="3"/>
       <c r="C967" s="3"/>
-      <c r="D967" s="46"/>
+      <c r="D967" s="45"/>
       <c r="E967" s="3"/>
       <c r="F967" s="3"/>
       <c r="G967" s="3"/>
@@ -28878,7 +28887,7 @@
       <c r="A968" s="1"/>
       <c r="B968" s="3"/>
       <c r="C968" s="3"/>
-      <c r="D968" s="46"/>
+      <c r="D968" s="45"/>
       <c r="E968" s="3"/>
       <c r="F968" s="3"/>
       <c r="G968" s="3"/>
@@ -28906,7 +28915,7 @@
       <c r="A969" s="1"/>
       <c r="B969" s="3"/>
       <c r="C969" s="3"/>
-      <c r="D969" s="46"/>
+      <c r="D969" s="45"/>
       <c r="E969" s="3"/>
       <c r="F969" s="3"/>
       <c r="G969" s="3"/>
@@ -28934,7 +28943,7 @@
       <c r="A970" s="1"/>
       <c r="B970" s="3"/>
       <c r="C970" s="3"/>
-      <c r="D970" s="46"/>
+      <c r="D970" s="45"/>
       <c r="E970" s="3"/>
       <c r="F970" s="3"/>
       <c r="G970" s="3"/>
@@ -28962,7 +28971,7 @@
       <c r="A971" s="1"/>
       <c r="B971" s="3"/>
       <c r="C971" s="3"/>
-      <c r="D971" s="46"/>
+      <c r="D971" s="45"/>
       <c r="E971" s="3"/>
       <c r="F971" s="3"/>
       <c r="G971" s="3"/>
@@ -28990,7 +28999,7 @@
       <c r="A972" s="1"/>
       <c r="B972" s="3"/>
       <c r="C972" s="3"/>
-      <c r="D972" s="46"/>
+      <c r="D972" s="45"/>
       <c r="E972" s="3"/>
       <c r="F972" s="3"/>
       <c r="G972" s="3"/>
@@ -29018,7 +29027,7 @@
       <c r="A973" s="1"/>
       <c r="B973" s="3"/>
       <c r="C973" s="3"/>
-      <c r="D973" s="46"/>
+      <c r="D973" s="45"/>
       <c r="E973" s="3"/>
       <c r="F973" s="3"/>
       <c r="G973" s="3"/>
@@ -29046,7 +29055,7 @@
       <c r="A974" s="1"/>
       <c r="B974" s="3"/>
       <c r="C974" s="3"/>
-      <c r="D974" s="46"/>
+      <c r="D974" s="45"/>
       <c r="E974" s="3"/>
       <c r="F974" s="3"/>
       <c r="G974" s="3"/>
@@ -29074,7 +29083,7 @@
       <c r="A975" s="1"/>
       <c r="B975" s="3"/>
       <c r="C975" s="3"/>
-      <c r="D975" s="46"/>
+      <c r="D975" s="45"/>
       <c r="E975" s="3"/>
       <c r="F975" s="3"/>
       <c r="G975" s="3"/>
@@ -29102,7 +29111,7 @@
       <c r="A976" s="1"/>
       <c r="B976" s="3"/>
       <c r="C976" s="3"/>
-      <c r="D976" s="46"/>
+      <c r="D976" s="45"/>
       <c r="E976" s="3"/>
       <c r="F976" s="3"/>
       <c r="G976" s="3"/>
@@ -29130,7 +29139,7 @@
       <c r="A977" s="1"/>
       <c r="B977" s="3"/>
       <c r="C977" s="3"/>
-      <c r="D977" s="46"/>
+      <c r="D977" s="45"/>
       <c r="E977" s="3"/>
       <c r="F977" s="3"/>
       <c r="G977" s="3"/>
@@ -29158,7 +29167,7 @@
       <c r="A978" s="1"/>
       <c r="B978" s="3"/>
       <c r="C978" s="3"/>
-      <c r="D978" s="46"/>
+      <c r="D978" s="45"/>
       <c r="E978" s="3"/>
       <c r="F978" s="3"/>
       <c r="G978" s="3"/>
@@ -29186,7 +29195,7 @@
       <c r="A979" s="1"/>
       <c r="B979" s="3"/>
       <c r="C979" s="3"/>
-      <c r="D979" s="46"/>
+      <c r="D979" s="45"/>
       <c r="E979" s="3"/>
       <c r="F979" s="3"/>
       <c r="G979" s="3"/>
@@ -29214,7 +29223,7 @@
       <c r="A980" s="1"/>
       <c r="B980" s="3"/>
       <c r="C980" s="3"/>
-      <c r="D980" s="46"/>
+      <c r="D980" s="45"/>
       <c r="E980" s="3"/>
       <c r="F980" s="3"/>
       <c r="G980" s="3"/>
@@ -29242,7 +29251,7 @@
       <c r="A981" s="1"/>
       <c r="B981" s="3"/>
       <c r="C981" s="3"/>
-      <c r="D981" s="46"/>
+      <c r="D981" s="45"/>
       <c r="E981" s="3"/>
       <c r="F981" s="3"/>
       <c r="G981" s="3"/>
@@ -29270,7 +29279,7 @@
       <c r="A982" s="1"/>
       <c r="B982" s="3"/>
       <c r="C982" s="3"/>
-      <c r="D982" s="46"/>
+      <c r="D982" s="45"/>
       <c r="E982" s="3"/>
       <c r="F982" s="3"/>
       <c r="G982" s="3"/>
@@ -29298,7 +29307,7 @@
       <c r="A983" s="1"/>
       <c r="B983" s="3"/>
       <c r="C983" s="3"/>
-      <c r="D983" s="46"/>
+      <c r="D983" s="45"/>
       <c r="E983" s="3"/>
       <c r="F983" s="3"/>
       <c r="G983" s="3"/>
@@ -29326,7 +29335,7 @@
       <c r="A984" s="1"/>
       <c r="B984" s="3"/>
       <c r="C984" s="3"/>
-      <c r="D984" s="46"/>
+      <c r="D984" s="45"/>
       <c r="E984" s="3"/>
       <c r="F984" s="3"/>
       <c r="G984" s="3"/>
@@ -29354,7 +29363,7 @@
       <c r="A985" s="1"/>
       <c r="B985" s="3"/>
       <c r="C985" s="3"/>
-      <c r="D985" s="46"/>
+      <c r="D985" s="45"/>
       <c r="E985" s="3"/>
       <c r="F985" s="3"/>
       <c r="G985" s="3"/>
@@ -29382,7 +29391,7 @@
       <c r="A986" s="1"/>
       <c r="B986" s="3"/>
       <c r="C986" s="3"/>
-      <c r="D986" s="46"/>
+      <c r="D986" s="45"/>
       <c r="E986" s="3"/>
       <c r="F986" s="3"/>
       <c r="G986" s="3"/>
@@ -29410,7 +29419,7 @@
       <c r="A987" s="1"/>
       <c r="B987" s="3"/>
       <c r="C987" s="3"/>
-      <c r="D987" s="46"/>
+      <c r="D987" s="45"/>
       <c r="E987" s="3"/>
       <c r="F987" s="3"/>
       <c r="G987" s="3"/>
@@ -29438,7 +29447,7 @@
       <c r="A988" s="1"/>
       <c r="B988" s="3"/>
       <c r="C988" s="3"/>
-      <c r="D988" s="46"/>
+      <c r="D988" s="45"/>
       <c r="E988" s="3"/>
       <c r="F988" s="3"/>
       <c r="G988" s="3"/>
@@ -29466,7 +29475,7 @@
       <c r="A989" s="1"/>
       <c r="B989" s="3"/>
       <c r="C989" s="3"/>
-      <c r="D989" s="46"/>
+      <c r="D989" s="45"/>
       <c r="E989" s="3"/>
       <c r="F989" s="3"/>
       <c r="G989" s="3"/>
@@ -29494,7 +29503,7 @@
       <c r="A990" s="1"/>
       <c r="B990" s="3"/>
       <c r="C990" s="3"/>
-      <c r="D990" s="46"/>
+      <c r="D990" s="45"/>
       <c r="E990" s="3"/>
       <c r="F990" s="3"/>
       <c r="G990" s="3"/>
@@ -29522,7 +29531,7 @@
       <c r="A991" s="1"/>
       <c r="B991" s="3"/>
       <c r="C991" s="3"/>
-      <c r="D991" s="46"/>
+      <c r="D991" s="45"/>
       <c r="E991" s="3"/>
       <c r="F991" s="3"/>
       <c r="G991" s="3"/>
@@ -29550,7 +29559,7 @@
       <c r="A992" s="1"/>
       <c r="B992" s="3"/>
       <c r="C992" s="3"/>
-      <c r="D992" s="46"/>
+      <c r="D992" s="45"/>
       <c r="E992" s="3"/>
       <c r="F992" s="3"/>
       <c r="G992" s="3"/>
@@ -29578,7 +29587,7 @@
       <c r="A993" s="1"/>
       <c r="B993" s="3"/>
       <c r="C993" s="3"/>
-      <c r="D993" s="46"/>
+      <c r="D993" s="45"/>
       <c r="E993" s="3"/>
       <c r="F993" s="3"/>
       <c r="G993" s="3"/>
@@ -29606,7 +29615,7 @@
       <c r="A994" s="1"/>
       <c r="B994" s="3"/>
       <c r="C994" s="3"/>
-      <c r="D994" s="46"/>
+      <c r="D994" s="45"/>
       <c r="E994" s="3"/>
       <c r="F994" s="3"/>
       <c r="G994" s="3"/>
@@ -29634,7 +29643,7 @@
       <c r="A995" s="1"/>
       <c r="B995" s="3"/>
       <c r="C995" s="3"/>
-      <c r="D995" s="46"/>
+      <c r="D995" s="45"/>
       <c r="E995" s="3"/>
       <c r="F995" s="3"/>
       <c r="G995" s="3"/>
@@ -29662,7 +29671,7 @@
       <c r="A996" s="1"/>
       <c r="B996" s="3"/>
       <c r="C996" s="3"/>
-      <c r="D996" s="46"/>
+      <c r="D996" s="45"/>
       <c r="E996" s="3"/>
       <c r="F996" s="3"/>
       <c r="G996" s="3"/>
@@ -29690,7 +29699,7 @@
       <c r="A997" s="1"/>
       <c r="B997" s="3"/>
       <c r="C997" s="3"/>
-      <c r="D997" s="46"/>
+      <c r="D997" s="45"/>
       <c r="E997" s="3"/>
       <c r="F997" s="3"/>
       <c r="G997" s="3"/>
@@ -29718,7 +29727,7 @@
       <c r="A998" s="1"/>
       <c r="B998" s="3"/>
       <c r="C998" s="3"/>
-      <c r="D998" s="46"/>
+      <c r="D998" s="45"/>
       <c r="E998" s="3"/>
       <c r="F998" s="3"/>
       <c r="G998" s="3"/>
@@ -29746,7 +29755,7 @@
       <c r="A999" s="1"/>
       <c r="B999" s="3"/>
       <c r="C999" s="3"/>
-      <c r="D999" s="46"/>
+      <c r="D999" s="45"/>
       <c r="E999" s="3"/>
       <c r="F999" s="3"/>
       <c r="G999" s="3"/>
@@ -29774,7 +29783,7 @@
       <c r="A1000" s="1"/>
       <c r="B1000" s="3"/>
       <c r="C1000" s="3"/>
-      <c r="D1000" s="46"/>
+      <c r="D1000" s="45"/>
       <c r="E1000" s="3"/>
       <c r="F1000" s="3"/>
       <c r="G1000" s="3"/>
@@ -29802,7 +29811,7 @@
       <c r="A1001" s="1"/>
       <c r="B1001" s="3"/>
       <c r="C1001" s="3"/>
-      <c r="D1001" s="46"/>
+      <c r="D1001" s="45"/>
       <c r="E1001" s="3"/>
       <c r="F1001" s="3"/>
       <c r="G1001" s="3"/>
@@ -29830,7 +29839,7 @@
       <c r="A1002" s="1"/>
       <c r="B1002" s="3"/>
       <c r="C1002" s="3"/>
-      <c r="D1002" s="46"/>
+      <c r="D1002" s="45"/>
       <c r="E1002" s="3"/>
       <c r="F1002" s="3"/>
       <c r="G1002" s="3"/>
@@ -29858,7 +29867,7 @@
       <c r="A1003" s="1"/>
       <c r="B1003" s="3"/>
       <c r="C1003" s="3"/>
-      <c r="D1003" s="46"/>
+      <c r="D1003" s="45"/>
       <c r="E1003" s="3"/>
       <c r="F1003" s="3"/>
       <c r="G1003" s="3"/>
@@ -29886,7 +29895,7 @@
       <c r="A1004" s="1"/>
       <c r="B1004" s="3"/>
       <c r="C1004" s="3"/>
-      <c r="D1004" s="46"/>
+      <c r="D1004" s="45"/>
       <c r="E1004" s="3"/>
       <c r="F1004" s="3"/>
       <c r="G1004" s="3"/>
@@ -29914,7 +29923,7 @@
       <c r="A1005" s="1"/>
       <c r="B1005" s="3"/>
       <c r="C1005" s="3"/>
-      <c r="D1005" s="46"/>
+      <c r="D1005" s="45"/>
       <c r="E1005" s="3"/>
       <c r="F1005" s="3"/>
       <c r="G1005" s="3"/>
@@ -29942,7 +29951,7 @@
       <c r="A1006" s="1"/>
       <c r="B1006" s="3"/>
       <c r="C1006" s="3"/>
-      <c r="D1006" s="46"/>
+      <c r="D1006" s="45"/>
       <c r="E1006" s="3"/>
       <c r="F1006" s="3"/>
       <c r="G1006" s="3"/>
@@ -29970,7 +29979,7 @@
       <c r="A1007" s="1"/>
       <c r="B1007" s="3"/>
       <c r="C1007" s="3"/>
-      <c r="D1007" s="46"/>
+      <c r="D1007" s="45"/>
       <c r="E1007" s="3"/>
       <c r="F1007" s="3"/>
       <c r="G1007" s="3"/>
@@ -29998,7 +30007,7 @@
       <c r="A1008" s="1"/>
       <c r="B1008" s="3"/>
       <c r="C1008" s="3"/>
-      <c r="D1008" s="46"/>
+      <c r="D1008" s="45"/>
       <c r="E1008" s="3"/>
       <c r="F1008" s="3"/>
       <c r="G1008" s="3"/>
@@ -30026,7 +30035,7 @@
       <c r="A1009" s="1"/>
       <c r="B1009" s="3"/>
       <c r="C1009" s="3"/>
-      <c r="D1009" s="46"/>
+      <c r="D1009" s="45"/>
       <c r="E1009" s="3"/>
       <c r="F1009" s="3"/>
       <c r="G1009" s="3"/>
@@ -30054,7 +30063,7 @@
       <c r="A1010" s="1"/>
       <c r="B1010" s="3"/>
       <c r="C1010" s="3"/>
-      <c r="D1010" s="46"/>
+      <c r="D1010" s="45"/>
       <c r="E1010" s="3"/>
       <c r="F1010" s="3"/>
       <c r="G1010" s="3"/>
@@ -30082,7 +30091,7 @@
       <c r="A1011" s="1"/>
       <c r="B1011" s="3"/>
       <c r="C1011" s="3"/>
-      <c r="D1011" s="46"/>
+      <c r="D1011" s="45"/>
       <c r="E1011" s="3"/>
       <c r="F1011" s="3"/>
       <c r="G1011" s="3"/>
@@ -30110,7 +30119,7 @@
       <c r="A1012" s="1"/>
       <c r="B1012" s="3"/>
       <c r="C1012" s="3"/>
-      <c r="D1012" s="46"/>
+      <c r="D1012" s="45"/>
       <c r="E1012" s="3"/>
       <c r="F1012" s="3"/>
       <c r="G1012" s="3"/>
@@ -30138,7 +30147,7 @@
       <c r="A1013" s="1"/>
       <c r="B1013" s="3"/>
       <c r="C1013" s="3"/>
-      <c r="D1013" s="46"/>
+      <c r="D1013" s="45"/>
       <c r="E1013" s="3"/>
       <c r="F1013" s="3"/>
       <c r="G1013" s="3"/>
@@ -30166,7 +30175,7 @@
       <c r="A1014" s="1"/>
       <c r="B1014" s="3"/>
       <c r="C1014" s="3"/>
-      <c r="D1014" s="46"/>
+      <c r="D1014" s="45"/>
       <c r="E1014" s="3"/>
       <c r="F1014" s="3"/>
       <c r="G1014" s="3"/>
@@ -30194,7 +30203,7 @@
       <c r="A1015" s="1"/>
       <c r="B1015" s="3"/>
       <c r="C1015" s="3"/>
-      <c r="D1015" s="46"/>
+      <c r="D1015" s="45"/>
       <c r="E1015" s="3"/>
       <c r="F1015" s="3"/>
       <c r="G1015" s="3"/>
@@ -30222,7 +30231,7 @@
       <c r="A1016" s="1"/>
       <c r="B1016" s="3"/>
       <c r="C1016" s="3"/>
-      <c r="D1016" s="46"/>
+      <c r="D1016" s="45"/>
       <c r="E1016" s="3"/>
       <c r="F1016" s="3"/>
       <c r="G1016" s="3"/>
@@ -30250,7 +30259,7 @@
       <c r="A1017" s="1"/>
       <c r="B1017" s="3"/>
       <c r="C1017" s="3"/>
-      <c r="D1017" s="46"/>
+      <c r="D1017" s="45"/>
       <c r="E1017" s="3"/>
       <c r="F1017" s="3"/>
       <c r="G1017" s="3"/>
